--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -6,14 +6,15 @@
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase0_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Phase</t>
   </si>
@@ -39,9 +40,72 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>hours_of_sleep</t>
+  </si>
+  <si>
+    <t>fatigue</t>
+  </si>
+  <si>
+    <t>muscle_soreness</t>
+  </si>
+  <si>
+    <t>stress</t>
+  </si>
+  <si>
+    <t>knee_soreness</t>
+  </si>
+  <si>
+    <t>2025-10-16 16:01:45</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>2025-10-17 15:29:59</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>Passive Knee Flexion</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>Passive Knee Extension</t>
   </si>
   <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Swelling</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>2025-10-18 15:56:54</t>
+  </si>
+  <si>
+    <t>2025-10-18</t>
+  </si>
+  <si>
+    <t>Passive Knee Extension</t>
+  </si>
+  <si>
     <t>Left</t>
   </si>
   <si>
@@ -63,118 +127,67 @@
     <t>grade</t>
   </si>
   <si>
-    <t>Passive Knee Extension</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>degrees</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Quad Strength</t>
+    <t>Hamstring Strength</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>Swelling</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>grade</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Single Leg Calf Raises</t>
-  </si>
-  <si>
-    <t>reps</t>
-  </si>
-  <si>
-    <t>Single Leg Bridge</t>
-  </si>
-  <si>
-    <t>TrapBar Deadlift</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Hamstring Strength</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Swelling</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>grade</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Passive Knee Flexion</t>
-  </si>
-  <si>
-    <t>degrees</t>
-  </si>
-  <si>
-    <t>SL Balance (eyes open)</t>
-  </si>
-  <si>
-    <t>seconds</t>
-  </si>
-  <si>
-    <t>Side Bridge</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>seconds</t>
-  </si>
-  <si>
-    <t>NA</t>
+    <t>2025-10-20 10:27:18</t>
+  </si>
+  <si>
+    <t>2025-10-20</t>
+  </si>
+  <si>
+    <t>2025-10-28 16:24:15</t>
+  </si>
+  <si>
+    <t>2025-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Knee Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">degrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Knee Flexion</t>
   </si>
   <si>
     <t xml:space="preserve">Swelling</t>
   </si>
   <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
     <t xml:space="preserve">grade</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Quads Lag Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lag</t>
+    <t xml:space="preserve">Hamstring Strength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quad Strength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-29 09:14:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-30 09:10:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-30</t>
   </si>
 </sst>
 </file>
@@ -523,6 +536,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
+    <col min="2" max="2" width="18.33203125" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -557,25 +571,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45840</v>
+        <v>45947</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45927.490125505799</v>
+        <v>45947.704595950803</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -583,25 +597,25 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45840</v>
+        <v>45947</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>45927.490516910999</v>
+        <v>45947.704659476702</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -609,25 +623,25 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45840</v>
+        <v>45947</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45927.490788639901</v>
+        <v>45947.704952933702</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -635,25 +649,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45840</v>
+        <v>45947</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45927.4909419994</v>
+        <v>45947.705045544899</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -661,25 +675,25 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45840</v>
+        <v>45947</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45927.491116751298</v>
+        <v>45947.705211323802</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -687,25 +701,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45840</v>
+        <v>45947</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45927.4911578541</v>
+        <v>45947.705280315502</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +727,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45842</v>
+        <v>45948</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45927.491668830902</v>
+        <v>45948.664888072301</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -739,25 +753,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45842</v>
+        <v>45948</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>45927.4917209458</v>
+        <v>45948.664965998003</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -765,25 +779,25 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45842</v>
+        <v>45948</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45927.491815822999</v>
+        <v>45948.665130714297</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -791,25 +805,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45842</v>
+        <v>45948</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45927.4920079605</v>
+        <v>45948.665214019697</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -817,25 +831,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45842</v>
+        <v>45948</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45927.492063352503</v>
+        <v>45948.665349680203</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -843,25 +857,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45842</v>
+        <v>45948</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45927.492107304803</v>
+        <v>45948.665392863797</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -869,25 +883,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45844</v>
+        <v>45948</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45927.492365461701</v>
+        <v>45948.666299291603</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -895,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45844</v>
+        <v>45948</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45927.492532065502</v>
+        <v>45948.666350146101</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -921,25 +935,25 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45844</v>
+        <v>45950</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45927.492665429701</v>
+        <v>45950.435864299601</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -947,25 +961,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45844</v>
+        <v>45950</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45927.492723115298</v>
+        <v>45950.435907915002</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F17" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -973,25 +987,25 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45844</v>
+        <v>45950</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45927.492847078996</v>
+        <v>45950.436296253101</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -999,25 +1013,25 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45844</v>
+        <v>45950</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45927.493053176098</v>
+        <v>45950.436443767503</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -1025,25 +1039,25 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45846</v>
+        <v>45950</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45927.493249517698</v>
+        <v>45950.436589819903</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -1051,25 +1065,25 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45846</v>
+        <v>45950</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45927.493305844502</v>
+        <v>45950.436639752603</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -1077,25 +1091,25 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45846</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>45927.4933835626</v>
+        <v>45958</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>45958.6841577331</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -1103,25 +1117,25 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45846</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>45927.493485974999</v>
+        <v>45958</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>45958.684209632</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
@@ -1129,25 +1143,25 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45846</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>45927.493545001897</v>
+        <v>45958</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>45958.6843220897</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
@@ -1155,25 +1169,25 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45846</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>45927.493637593601</v>
+        <v>45958</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>45958.6843899895</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -1181,25 +1195,25 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>45939.549387366998</v>
+        <v>45958</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>45958.6845248028</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H26" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
@@ -1207,25 +1221,25 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>45939.549928508197</v>
+        <v>45958</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>45958.684905008</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
@@ -1233,467 +1247,379 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45939</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>45939.5879193078</v>
+        <v>45958</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>45958.6849681709</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>45944.538181515702</v>
+        <v>45958</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>45958.6850676984</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>45944.538667036002</v>
+        <v>45958</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>45958.6851665924</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>45944.539097769302</v>
+        <v>45958</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>45958.6853249762</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>45944.539161908397</v>
+        <v>45958</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>45958.6853876738</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>45944.5411305854</v>
+        <v>45959</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>45959.3855714235</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>45959.385909921</v>
+      </c>
+      <c r="E34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>45944.541474126003</v>
-      </c>
-      <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" t="n">
-        <v>110</v>
-      </c>
-      <c r="G34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>0</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>45944.549779750203</v>
-      </c>
-      <c r="E35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" t="n">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>45944.549835744998</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="F36" t="n">
-        <v>90</v>
-      </c>
-      <c r="G36" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>0</v>
-      </c>
-      <c r="B37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>45944.554524723499</v>
-      </c>
-      <c r="E37" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G37" t="s">
-        <v>37</v>
-      </c>
-      <c r="H37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>0</v>
-      </c>
-      <c r="B38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>45944.5545722057</v>
-      </c>
-      <c r="E38" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>37</v>
-      </c>
-      <c r="H38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>45944.554870663203</v>
-      </c>
-      <c r="E39" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" t="n">
-        <v>120</v>
-      </c>
-      <c r="G39" t="s">
-        <v>41</v>
-      </c>
-      <c r="H39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>45944.554918218302</v>
-      </c>
-      <c r="E40" t="s">
-        <v>39</v>
-      </c>
-      <c r="F40" t="n">
-        <v>125</v>
-      </c>
-      <c r="G40" t="s">
-        <v>41</v>
-      </c>
-      <c r="H40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="B41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>45944.555027820497</v>
-      </c>
-      <c r="E41" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" t="n">
-        <v>30</v>
-      </c>
-      <c r="G41" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="B42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>45944.5550978479</v>
-      </c>
-      <c r="E42" t="s">
-        <v>39</v>
-      </c>
-      <c r="F42" t="n">
-        <v>45</v>
-      </c>
-      <c r="G42" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="B43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>45944.556061638999</v>
-      </c>
-      <c r="E43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" t="n">
-        <v>30</v>
-      </c>
-      <c r="G43" t="s">
-        <v>46</v>
-      </c>
-      <c r="H43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>0</v>
-      </c>
-      <c r="B44" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>45944.55742558</v>
-      </c>
-      <c r="E44" t="s">
-        <v>49</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>50</v>
-      </c>
-      <c r="H44" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>45944.5582584667</v>
-      </c>
-      <c r="E45" t="s">
-        <v>49</v>
-      </c>
-      <c r="F45" t="n">
+      <c r="G8" t="n">
         <v>2</v>
-      </c>
-      <c r="G45" t="s">
-        <v>53</v>
-      </c>
-      <c r="H45" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Phase</t>
   </si>
@@ -188,6 +188,30 @@
   </si>
   <si>
     <t xml:space="preserve">2025-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-04 11:38:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-10 13:05:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-13 09:14:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-15 10:37:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-15</t>
   </si>
 </sst>
 </file>
@@ -1424,6 +1448,630 @@
         <v>46</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>45960.4918017123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>45960.4919608843</v>
+      </c>
+      <c r="E36" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" t="n">
+        <v>125</v>
+      </c>
+      <c r="G36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>45960.4920141178</v>
+      </c>
+      <c r="E37" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" t="n">
+        <v>128</v>
+      </c>
+      <c r="G37" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>45960.4925225785</v>
+      </c>
+      <c r="E38" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" t="n">
+        <v>72</v>
+      </c>
+      <c r="G38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>45960.4925716453</v>
+      </c>
+      <c r="E39" t="s">
+        <v>47</v>
+      </c>
+      <c r="F39" t="n">
+        <v>92</v>
+      </c>
+      <c r="G39" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>45960.4926435316</v>
+      </c>
+      <c r="E40" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" t="n">
+        <v>74</v>
+      </c>
+      <c r="G40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>45960.4927002549</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" t="n">
+        <v>90</v>
+      </c>
+      <c r="G41" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>45965.4856571388</v>
+      </c>
+      <c r="E42" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>45965.485844847</v>
+      </c>
+      <c r="E43" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>45965.4858909899</v>
+      </c>
+      <c r="E44" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" t="n">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>45965.4859684859</v>
+      </c>
+      <c r="E45" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" t="n">
+        <v>87</v>
+      </c>
+      <c r="G45" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>45965.4860019557</v>
+      </c>
+      <c r="E46" t="s">
+        <v>47</v>
+      </c>
+      <c r="F46" t="n">
+        <v>89</v>
+      </c>
+      <c r="G46" t="s">
+        <v>52</v>
+      </c>
+      <c r="H46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>45965.486250549</v>
+      </c>
+      <c r="E47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" t="n">
+        <v>50</v>
+      </c>
+      <c r="G47" t="s">
+        <v>52</v>
+      </c>
+      <c r="H47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>45965.4862924926</v>
+      </c>
+      <c r="E48" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" t="n">
+        <v>52</v>
+      </c>
+      <c r="G48" t="s">
+        <v>52</v>
+      </c>
+      <c r="H48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>45965.4863773124</v>
+      </c>
+      <c r="E49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" t="n">
+        <v>54</v>
+      </c>
+      <c r="G49" t="s">
+        <v>52</v>
+      </c>
+      <c r="H49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>45965.4864046392</v>
+      </c>
+      <c r="E50" t="s">
+        <v>47</v>
+      </c>
+      <c r="F50" t="n">
+        <v>56</v>
+      </c>
+      <c r="G50" t="s">
+        <v>52</v>
+      </c>
+      <c r="H50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>45974.4113670867</v>
+      </c>
+      <c r="E51" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>45974.4114167009</v>
+      </c>
+      <c r="E52" t="s">
+        <v>47</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>45975.5379412316</v>
+      </c>
+      <c r="E53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="s">
+        <v>50</v>
+      </c>
+      <c r="H53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>45975.5381579989</v>
+      </c>
+      <c r="E54" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>50</v>
+      </c>
+      <c r="H54" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>45975.5442618365</v>
+      </c>
+      <c r="E55" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="s">
+        <v>45</v>
+      </c>
+      <c r="H55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>45975.5443030501</v>
+      </c>
+      <c r="E56" t="s">
+        <v>47</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H56" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>45975.5445395892</v>
+      </c>
+      <c r="E57" t="s">
+        <v>44</v>
+      </c>
+      <c r="F57" t="n">
+        <v>110</v>
+      </c>
+      <c r="G57" t="s">
+        <v>45</v>
+      </c>
+      <c r="H57" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>45975.5445756684</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" t="n">
+        <v>125</v>
+      </c>
+      <c r="G58" t="s">
+        <v>45</v>
+      </c>
+      <c r="H58" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1622,6 +2270,98 @@
         <v>2</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Phase</t>
   </si>
@@ -212,6 +212,18 @@
   </si>
   <si>
     <t xml:space="preserve">2025-11-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-28 15:43:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quads Lag Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lag</t>
   </si>
 </sst>
 </file>
@@ -2072,6 +2084,188 @@
         <v>46</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>45989.6574192781</v>
+      </c>
+      <c r="E59" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>49</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>45989.657464727</v>
+      </c>
+      <c r="E60" t="s">
+        <v>47</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>50</v>
+      </c>
+      <c r="H60" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>45989.6576588542</v>
+      </c>
+      <c r="E61" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>45</v>
+      </c>
+      <c r="H61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>45989.6577252929</v>
+      </c>
+      <c r="E62" t="s">
+        <v>47</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>45</v>
+      </c>
+      <c r="H62" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>45989.6578791573</v>
+      </c>
+      <c r="E63" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" t="n">
+        <v>117</v>
+      </c>
+      <c r="G63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H63" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>45989.6579185131</v>
+      </c>
+      <c r="E64" t="s">
+        <v>47</v>
+      </c>
+      <c r="F64" t="n">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
+        <v>45</v>
+      </c>
+      <c r="H64" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>45989.658742764</v>
+      </c>
+      <c r="E65" t="s">
+        <v>44</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>69</v>
+      </c>
+      <c r="H65" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2362,6 +2556,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>Phase</t>
   </si>
@@ -145,79 +145,241 @@
     <t>2025-10-28</t>
   </si>
   <si>
+    <t>Passive Knee Extension</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Passive Knee Flexion</t>
+  </si>
+  <si>
+    <t>Swelling</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>Hamstring Strength</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Quad Strength</t>
+  </si>
+  <si>
+    <t>2025-10-29 09:14:48</t>
+  </si>
+  <si>
+    <t>2025-10-29</t>
+  </si>
+  <si>
+    <t>2025-10-30 09:10:47</t>
+  </si>
+  <si>
+    <t>2025-10-30</t>
+  </si>
+  <si>
+    <t>2025-11-04 11:38:40</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-10 13:05:52</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-13 09:14:49</t>
+  </si>
+  <si>
+    <t>2025-11-13</t>
+  </si>
+  <si>
+    <t>2025-11-15 10:37:56</t>
+  </si>
+  <si>
+    <t>2025-11-15</t>
+  </si>
+  <si>
+    <t>2025-11-28 15:43:42</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>Quads Lag Test</t>
+  </si>
+  <si>
+    <t>lag</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:48:30</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:50:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:51:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:51:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:51:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:51:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:51:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:52:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:52:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:52:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:52:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:53:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:53:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:53:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:53:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:53:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:54:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:54:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:54:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:54:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 13:54:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swelling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Knee Flexion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">degrees</t>
+  </si>
+  <si>
     <t xml:space="preserve">Passive Knee Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">degrees</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Knee Flexion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamstring Strength</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quad Strength</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-29 09:14:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-30 09:10:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-04 11:38:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-10 13:05:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-13 09:14:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-15 10:37:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-28 15:43:42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-28</t>
   </si>
   <si>
     <t xml:space="preserve">Quads Lag Test</t>
@@ -1132,7 +1294,7 @@
       <c r="C22" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="2" t="n">
         <v>45958.6841577331</v>
       </c>
       <c r="E22" t="s">
@@ -1158,8 +1320,8 @@
       <c r="C23" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>45958.684209632</v>
+      <c r="D23" s="2" t="n">
+        <v>45958.684209632003</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
@@ -1184,8 +1346,8 @@
       <c r="C24" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>45958.6843220897</v>
+      <c r="D24" s="2" t="n">
+        <v>45958.684322089699</v>
       </c>
       <c r="E24" t="s">
         <v>44</v>
@@ -1210,8 +1372,8 @@
       <c r="C25" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>45958.6843899895</v>
+      <c r="D25" s="2" t="n">
+        <v>45958.684389989503</v>
       </c>
       <c r="E25" t="s">
         <v>47</v>
@@ -1236,8 +1398,8 @@
       <c r="C26" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>45958.6845248028</v>
+      <c r="D26" s="2" t="n">
+        <v>45958.684524802797</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
@@ -1262,8 +1424,8 @@
       <c r="C27" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>45958.684905008</v>
+      <c r="D27" s="2" t="n">
+        <v>45958.684905007998</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
@@ -1288,8 +1450,8 @@
       <c r="C28" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D28" s="3" t="n">
-        <v>45958.6849681709</v>
+      <c r="D28" s="2" t="n">
+        <v>45958.684968170899</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
@@ -1314,8 +1476,8 @@
       <c r="C29" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>45958.6850676984</v>
+      <c r="D29" s="2" t="n">
+        <v>45958.685067698403</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
@@ -1340,8 +1502,8 @@
       <c r="C30" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>45958.6851665924</v>
+      <c r="D30" s="2" t="n">
+        <v>45958.685166592397</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
@@ -1366,8 +1528,8 @@
       <c r="C31" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>45958.6853249762</v>
+      <c r="D31" s="2" t="n">
+        <v>45958.685324976199</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
@@ -1392,8 +1554,8 @@
       <c r="C32" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>45958.6853876738</v>
+      <c r="D32" s="2" t="n">
+        <v>45958.685387673802</v>
       </c>
       <c r="E32" t="s">
         <v>44</v>
@@ -1418,8 +1580,8 @@
       <c r="C33" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>45959.3855714235</v>
+      <c r="D33" s="2" t="n">
+        <v>45959.385571423503</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
@@ -1444,8 +1606,8 @@
       <c r="C34" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>45959.385909921</v>
+      <c r="D34" s="2" t="n">
+        <v>45959.385909921002</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
@@ -1470,8 +1632,8 @@
       <c r="C35" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D35" s="3" t="n">
-        <v>45960.4918017123</v>
+      <c r="D35" s="2" t="n">
+        <v>45960.491801712298</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1496,8 +1658,8 @@
       <c r="C36" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>45960.4919608843</v>
+      <c r="D36" s="2" t="n">
+        <v>45960.491960884297</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
@@ -1522,8 +1684,8 @@
       <c r="C37" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>45960.4920141178</v>
+      <c r="D37" s="2" t="n">
+        <v>45960.492014117801</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
@@ -1548,8 +1710,8 @@
       <c r="C38" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>45960.4925225785</v>
+      <c r="D38" s="2" t="n">
+        <v>45960.492522578497</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
@@ -1574,7 +1736,7 @@
       <c r="C39" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="2" t="n">
         <v>45960.4925716453</v>
       </c>
       <c r="E39" t="s">
@@ -1600,8 +1762,8 @@
       <c r="C40" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>45960.4926435316</v>
+      <c r="D40" s="2" t="n">
+        <v>45960.492643531601</v>
       </c>
       <c r="E40" t="s">
         <v>44</v>
@@ -1626,8 +1788,8 @@
       <c r="C41" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>45960.4927002549</v>
+      <c r="D41" s="2" t="n">
+        <v>45960.492700254901</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
@@ -1652,8 +1814,8 @@
       <c r="C42" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>45965.4856571388</v>
+      <c r="D42" s="2" t="n">
+        <v>45965.485657138801</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
@@ -1678,8 +1840,8 @@
       <c r="C43" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>45965.485844847</v>
+      <c r="D43" s="2" t="n">
+        <v>45965.485844846997</v>
       </c>
       <c r="E43" t="s">
         <v>44</v>
@@ -1704,8 +1866,8 @@
       <c r="C44" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>45965.4858909899</v>
+      <c r="D44" s="2" t="n">
+        <v>45965.485890989898</v>
       </c>
       <c r="E44" t="s">
         <v>44</v>
@@ -1730,8 +1892,8 @@
       <c r="C45" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>45965.4859684859</v>
+      <c r="D45" s="2" t="n">
+        <v>45965.485968485897</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
@@ -1756,8 +1918,8 @@
       <c r="C46" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>45965.4860019557</v>
+      <c r="D46" s="2" t="n">
+        <v>45965.486001955702</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
@@ -1782,8 +1944,8 @@
       <c r="C47" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>45965.486250549</v>
+      <c r="D47" s="2" t="n">
+        <v>45965.486250549002</v>
       </c>
       <c r="E47" t="s">
         <v>44</v>
@@ -1808,8 +1970,8 @@
       <c r="C48" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D48" s="3" t="n">
-        <v>45965.4862924926</v>
+      <c r="D48" s="2" t="n">
+        <v>45965.486292492598</v>
       </c>
       <c r="E48" t="s">
         <v>44</v>
@@ -1834,8 +1996,8 @@
       <c r="C49" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D49" s="3" t="n">
-        <v>45965.4863773124</v>
+      <c r="D49" s="2" t="n">
+        <v>45965.486377312402</v>
       </c>
       <c r="E49" t="s">
         <v>47</v>
@@ -1860,8 +2022,8 @@
       <c r="C50" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>45965.4864046392</v>
+      <c r="D50" s="2" t="n">
+        <v>45965.486404639203</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
@@ -1886,8 +2048,8 @@
       <c r="C51" s="1" t="n">
         <v>45974</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>45974.4113670867</v>
+      <c r="D51" s="2" t="n">
+        <v>45974.411367086701</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
@@ -1912,8 +2074,8 @@
       <c r="C52" s="1" t="n">
         <v>45974</v>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>45974.4114167009</v>
+      <c r="D52" s="2" t="n">
+        <v>45974.411416700903</v>
       </c>
       <c r="E52" t="s">
         <v>47</v>
@@ -1938,8 +2100,8 @@
       <c r="C53" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D53" s="3" t="n">
-        <v>45975.5379412316</v>
+      <c r="D53" s="2" t="n">
+        <v>45975.537941231603</v>
       </c>
       <c r="E53" t="s">
         <v>44</v>
@@ -1964,8 +2126,8 @@
       <c r="C54" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>45975.5381579989</v>
+      <c r="D54" s="2" t="n">
+        <v>45975.538157998897</v>
       </c>
       <c r="E54" t="s">
         <v>47</v>
@@ -1990,8 +2152,8 @@
       <c r="C55" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D55" s="3" t="n">
-        <v>45975.5442618365</v>
+      <c r="D55" s="2" t="n">
+        <v>45975.544261836498</v>
       </c>
       <c r="E55" t="s">
         <v>44</v>
@@ -2016,8 +2178,8 @@
       <c r="C56" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D56" s="3" t="n">
-        <v>45975.5443030501</v>
+      <c r="D56" s="2" t="n">
+        <v>45975.544303050097</v>
       </c>
       <c r="E56" t="s">
         <v>47</v>
@@ -2042,8 +2204,8 @@
       <c r="C57" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D57" s="3" t="n">
-        <v>45975.5445395892</v>
+      <c r="D57" s="2" t="n">
+        <v>45975.544539589202</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
@@ -2068,8 +2230,8 @@
       <c r="C58" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>45975.5445756684</v>
+      <c r="D58" s="2" t="n">
+        <v>45975.544575668398</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
@@ -2094,8 +2256,8 @@
       <c r="C59" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D59" s="3" t="n">
-        <v>45989.6574192781</v>
+      <c r="D59" s="2" t="n">
+        <v>45989.657419278097</v>
       </c>
       <c r="E59" t="s">
         <v>44</v>
@@ -2120,8 +2282,8 @@
       <c r="C60" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>45989.657464727</v>
+      <c r="D60" s="2" t="n">
+        <v>45989.657464727003</v>
       </c>
       <c r="E60" t="s">
         <v>47</v>
@@ -2146,8 +2308,8 @@
       <c r="C61" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>45989.6576588542</v>
+      <c r="D61" s="2" t="n">
+        <v>45989.657658854201</v>
       </c>
       <c r="E61" t="s">
         <v>44</v>
@@ -2172,8 +2334,8 @@
       <c r="C62" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>45989.6577252929</v>
+      <c r="D62" s="2" t="n">
+        <v>45989.657725292898</v>
       </c>
       <c r="E62" t="s">
         <v>47</v>
@@ -2198,8 +2360,8 @@
       <c r="C63" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D63" s="3" t="n">
-        <v>45989.6578791573</v>
+      <c r="D63" s="2" t="n">
+        <v>45989.657879157297</v>
       </c>
       <c r="E63" t="s">
         <v>44</v>
@@ -2224,8 +2386,8 @@
       <c r="C64" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>45989.6579185131</v>
+      <c r="D64" s="2" t="n">
+        <v>45989.657918513098</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
@@ -2250,8 +2412,8 @@
       <c r="C65" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>45989.658742764</v>
+      <c r="D65" s="2" t="n">
+        <v>45989.658742763997</v>
       </c>
       <c r="E65" t="s">
         <v>44</v>
@@ -2264,6 +2426,760 @@
       </c>
       <c r="H65" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46030.597367625</v>
+      </c>
+      <c r="E66" t="s">
+        <v>115</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>116</v>
+      </c>
+      <c r="H66" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>46030.5974293517</v>
+      </c>
+      <c r="E67" t="s">
+        <v>118</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>116</v>
+      </c>
+      <c r="H67" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>119</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>46030.5977688181</v>
+      </c>
+      <c r="E68" t="s">
+        <v>115</v>
+      </c>
+      <c r="F68" t="n">
+        <v>120</v>
+      </c>
+      <c r="G68" t="s">
+        <v>120</v>
+      </c>
+      <c r="H68" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>46030.5978192446</v>
+      </c>
+      <c r="E69" t="s">
+        <v>118</v>
+      </c>
+      <c r="F69" t="n">
+        <v>125</v>
+      </c>
+      <c r="G69" t="s">
+        <v>120</v>
+      </c>
+      <c r="H69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>46030.5981109887</v>
+      </c>
+      <c r="E70" t="s">
+        <v>115</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="s">
+        <v>120</v>
+      </c>
+      <c r="H70" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46030.5981652692</v>
+      </c>
+      <c r="E71" t="s">
+        <v>118</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>120</v>
+      </c>
+      <c r="H71" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>122</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46030.5985355347</v>
+      </c>
+      <c r="E72" t="s">
+        <v>115</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
+        <v>123</v>
+      </c>
+      <c r="H72" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46030.5987297306</v>
+      </c>
+      <c r="E73" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>116</v>
+      </c>
+      <c r="H73" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>46030.5988043645</v>
+      </c>
+      <c r="E74" t="s">
+        <v>118</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>116</v>
+      </c>
+      <c r="H74" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>46030.5989522356</v>
+      </c>
+      <c r="E75" t="s">
+        <v>115</v>
+      </c>
+      <c r="F75" t="n">
+        <v>122</v>
+      </c>
+      <c r="G75" t="s">
+        <v>120</v>
+      </c>
+      <c r="H75" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>119</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>46030.5989977875</v>
+      </c>
+      <c r="E76" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" t="n">
+        <v>127</v>
+      </c>
+      <c r="G76" t="s">
+        <v>120</v>
+      </c>
+      <c r="H76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>46030.5991297031</v>
+      </c>
+      <c r="E77" t="s">
+        <v>115</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>120</v>
+      </c>
+      <c r="H77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="s">
+        <v>121</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>46030.5991857636</v>
+      </c>
+      <c r="E78" t="s">
+        <v>118</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>120</v>
+      </c>
+      <c r="H78" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>46030.5994614402</v>
+      </c>
+      <c r="E79" t="s">
+        <v>118</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="s">
+        <v>123</v>
+      </c>
+      <c r="H79" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>46030.6009521206</v>
+      </c>
+      <c r="E80" t="s">
+        <v>115</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="s">
+        <v>123</v>
+      </c>
+      <c r="H80" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>46030.6013620996</v>
+      </c>
+      <c r="E81" t="s">
+        <v>115</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>116</v>
+      </c>
+      <c r="H81" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>46030.6013972678</v>
+      </c>
+      <c r="E82" t="s">
+        <v>118</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>116</v>
+      </c>
+      <c r="H82" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="s">
+        <v>119</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>46030.6016646995</v>
+      </c>
+      <c r="E83" t="s">
+        <v>115</v>
+      </c>
+      <c r="F83" t="n">
+        <v>124</v>
+      </c>
+      <c r="G83" t="s">
+        <v>120</v>
+      </c>
+      <c r="H83" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="B84" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46030.6017078499</v>
+      </c>
+      <c r="E84" t="s">
+        <v>118</v>
+      </c>
+      <c r="F84" t="n">
+        <v>125</v>
+      </c>
+      <c r="G84" t="s">
+        <v>120</v>
+      </c>
+      <c r="H84" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1</v>
+      </c>
+      <c r="B85" t="s">
+        <v>121</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>46030.6018805031</v>
+      </c>
+      <c r="E85" t="s">
+        <v>115</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>120</v>
+      </c>
+      <c r="H85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>46030.601922228</v>
+      </c>
+      <c r="E86" t="s">
+        <v>118</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>120</v>
+      </c>
+      <c r="H86" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>122</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>46030.6020150284</v>
+      </c>
+      <c r="E87" t="s">
+        <v>115</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>123</v>
+      </c>
+      <c r="H87" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" t="s">
+        <v>114</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>46030.6023252397</v>
+      </c>
+      <c r="E88" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>116</v>
+      </c>
+      <c r="H88" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="B89" t="s">
+        <v>114</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>46030.6023644629</v>
+      </c>
+      <c r="E89" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>116</v>
+      </c>
+      <c r="H89" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>119</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>46030.6024327473</v>
+      </c>
+      <c r="E90" t="s">
+        <v>115</v>
+      </c>
+      <c r="F90" t="n">
+        <v>125</v>
+      </c>
+      <c r="G90" t="s">
+        <v>120</v>
+      </c>
+      <c r="H90" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>46030.6024742455</v>
+      </c>
+      <c r="E91" t="s">
+        <v>118</v>
+      </c>
+      <c r="F91" t="n">
+        <v>125</v>
+      </c>
+      <c r="G91" t="s">
+        <v>120</v>
+      </c>
+      <c r="H91" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>121</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>46030.6025831763</v>
+      </c>
+      <c r="E92" t="s">
+        <v>115</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>120</v>
+      </c>
+      <c r="H92" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="B93" t="s">
+        <v>121</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>46030.6026202654</v>
+      </c>
+      <c r="E93" t="s">
+        <v>118</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
+        <v>120</v>
+      </c>
+      <c r="H93" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B94" t="s">
+        <v>122</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>46030.6027079642</v>
+      </c>
+      <c r="E94" t="s">
+        <v>115</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
+        <v>123</v>
+      </c>
+      <c r="H94" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2579,6 +3495,512 @@
         <v>2</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
   <si>
     <t>Phase</t>
   </si>
@@ -232,160 +232,199 @@
     <t>2025-12-01</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-01-08 13:50:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:51:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:51:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:51:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:51:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:51:57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:52:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:52:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:52:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:52:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:53:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:53:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:53:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:53:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:53:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:54:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:54:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:54:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:54:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08 13:54:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-08</t>
+    <t>2026-01-08 13:50:53</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:51:03</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:51:15</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:51:28</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:51:46</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:51:57</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:52:08</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:52:18</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:52:28</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:52:49</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:53:00</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:53:09</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:53:18</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:53:29</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:53:43</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:53:54</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:54:03</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:54:13</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:54:22</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:54:35</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:54:52</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>Swelling</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Passive Knee Flexion</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>Passive Knee Extension</t>
+  </si>
+  <si>
+    <t>Quads Lag Test</t>
+  </si>
+  <si>
+    <t>lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-12 10:36:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Knee Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">degrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Knee Flexion</t>
   </si>
   <si>
     <t xml:space="preserve">Swelling</t>
   </si>
   <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
     <t xml:space="preserve">grade</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Knee Flexion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">degrees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Knee Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quads Lag Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lag</t>
+    <t xml:space="preserve">Single Leg Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Calf Raises</t>
   </si>
 </sst>
 </file>
@@ -2438,7 +2477,7 @@
       <c r="C66" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="2" t="n">
         <v>46030.597367625</v>
       </c>
       <c r="E66" t="s">
@@ -2464,8 +2503,8 @@
       <c r="C67" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>46030.5974293517</v>
+      <c r="D67" s="2" t="n">
+        <v>46030.597429351699</v>
       </c>
       <c r="E67" t="s">
         <v>118</v>
@@ -2490,8 +2529,8 @@
       <c r="C68" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D68" s="3" t="n">
-        <v>46030.5977688181</v>
+      <c r="D68" s="2" t="n">
+        <v>46030.597768818101</v>
       </c>
       <c r="E68" t="s">
         <v>115</v>
@@ -2516,8 +2555,8 @@
       <c r="C69" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D69" s="3" t="n">
-        <v>46030.5978192446</v>
+      <c r="D69" s="2" t="n">
+        <v>46030.597819244598</v>
       </c>
       <c r="E69" t="s">
         <v>118</v>
@@ -2542,7 +2581,7 @@
       <c r="C70" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="2" t="n">
         <v>46030.5981109887</v>
       </c>
       <c r="E70" t="s">
@@ -2568,8 +2607,8 @@
       <c r="C71" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D71" s="3" t="n">
-        <v>46030.5981652692</v>
+      <c r="D71" s="2" t="n">
+        <v>46030.598165269199</v>
       </c>
       <c r="E71" t="s">
         <v>118</v>
@@ -2594,7 +2633,7 @@
       <c r="C72" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="2" t="n">
         <v>46030.5985355347</v>
       </c>
       <c r="E72" t="s">
@@ -2620,8 +2659,8 @@
       <c r="C73" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D73" s="3" t="n">
-        <v>46030.5987297306</v>
+      <c r="D73" s="2" t="n">
+        <v>46030.598729730598</v>
       </c>
       <c r="E73" t="s">
         <v>115</v>
@@ -2646,8 +2685,8 @@
       <c r="C74" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D74" s="3" t="n">
-        <v>46030.5988043645</v>
+      <c r="D74" s="2" t="n">
+        <v>46030.598804364497</v>
       </c>
       <c r="E74" t="s">
         <v>118</v>
@@ -2672,8 +2711,8 @@
       <c r="C75" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D75" s="3" t="n">
-        <v>46030.5989522356</v>
+      <c r="D75" s="2" t="n">
+        <v>46030.598952235603</v>
       </c>
       <c r="E75" t="s">
         <v>115</v>
@@ -2698,7 +2737,7 @@
       <c r="C76" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="2" t="n">
         <v>46030.5989977875</v>
       </c>
       <c r="E76" t="s">
@@ -2724,7 +2763,7 @@
       <c r="C77" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="2" t="n">
         <v>46030.5991297031</v>
       </c>
       <c r="E77" t="s">
@@ -2750,8 +2789,8 @@
       <c r="C78" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>46030.5991857636</v>
+      <c r="D78" s="2" t="n">
+        <v>46030.599185763604</v>
       </c>
       <c r="E78" t="s">
         <v>118</v>
@@ -2776,8 +2815,8 @@
       <c r="C79" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D79" s="3" t="n">
-        <v>46030.5994614402</v>
+      <c r="D79" s="2" t="n">
+        <v>46030.599461440201</v>
       </c>
       <c r="E79" t="s">
         <v>118</v>
@@ -2802,7 +2841,7 @@
       <c r="C80" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="2" t="n">
         <v>46030.6009521206</v>
       </c>
       <c r="E80" t="s">
@@ -2828,8 +2867,8 @@
       <c r="C81" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D81" s="3" t="n">
-        <v>46030.6013620996</v>
+      <c r="D81" s="2" t="n">
+        <v>46030.601362099602</v>
       </c>
       <c r="E81" t="s">
         <v>115</v>
@@ -2854,8 +2893,8 @@
       <c r="C82" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D82" s="3" t="n">
-        <v>46030.6013972678</v>
+      <c r="D82" s="2" t="n">
+        <v>46030.601397267797</v>
       </c>
       <c r="E82" t="s">
         <v>118</v>
@@ -2880,8 +2919,8 @@
       <c r="C83" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D83" s="3" t="n">
-        <v>46030.6016646995</v>
+      <c r="D83" s="2" t="n">
+        <v>46030.601664699498</v>
       </c>
       <c r="E83" t="s">
         <v>115</v>
@@ -2906,8 +2945,8 @@
       <c r="C84" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D84" s="3" t="n">
-        <v>46030.6017078499</v>
+      <c r="D84" s="2" t="n">
+        <v>46030.601707849899</v>
       </c>
       <c r="E84" t="s">
         <v>118</v>
@@ -2932,8 +2971,8 @@
       <c r="C85" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D85" s="3" t="n">
-        <v>46030.6018805031</v>
+      <c r="D85" s="2" t="n">
+        <v>46030.601880503098</v>
       </c>
       <c r="E85" t="s">
         <v>115</v>
@@ -2958,8 +2997,8 @@
       <c r="C86" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D86" s="3" t="n">
-        <v>46030.601922228</v>
+      <c r="D86" s="2" t="n">
+        <v>46030.601922228001</v>
       </c>
       <c r="E86" t="s">
         <v>118</v>
@@ -2984,8 +3023,8 @@
       <c r="C87" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D87" s="3" t="n">
-        <v>46030.6020150284</v>
+      <c r="D87" s="2" t="n">
+        <v>46030.602015028402</v>
       </c>
       <c r="E87" t="s">
         <v>115</v>
@@ -3010,8 +3049,8 @@
       <c r="C88" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D88" s="3" t="n">
-        <v>46030.6023252397</v>
+      <c r="D88" s="2" t="n">
+        <v>46030.602325239699</v>
       </c>
       <c r="E88" t="s">
         <v>115</v>
@@ -3036,8 +3075,8 @@
       <c r="C89" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D89" s="3" t="n">
-        <v>46030.6023644629</v>
+      <c r="D89" s="2" t="n">
+        <v>46030.602364462902</v>
       </c>
       <c r="E89" t="s">
         <v>118</v>
@@ -3062,8 +3101,8 @@
       <c r="C90" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D90" s="3" t="n">
-        <v>46030.6024327473</v>
+      <c r="D90" s="2" t="n">
+        <v>46030.602432747299</v>
       </c>
       <c r="E90" t="s">
         <v>115</v>
@@ -3088,8 +3127,8 @@
       <c r="C91" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D91" s="3" t="n">
-        <v>46030.6024742455</v>
+      <c r="D91" s="2" t="n">
+        <v>46030.602474245497</v>
       </c>
       <c r="E91" t="s">
         <v>118</v>
@@ -3114,8 +3153,8 @@
       <c r="C92" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D92" s="3" t="n">
-        <v>46030.6025831763</v>
+      <c r="D92" s="2" t="n">
+        <v>46030.602583176304</v>
       </c>
       <c r="E92" t="s">
         <v>115</v>
@@ -3140,8 +3179,8 @@
       <c r="C93" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D93" s="3" t="n">
-        <v>46030.6026202654</v>
+      <c r="D93" s="2" t="n">
+        <v>46030.602620265403</v>
       </c>
       <c r="E93" t="s">
         <v>118</v>
@@ -3166,8 +3205,8 @@
       <c r="C94" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D94" s="3" t="n">
-        <v>46030.6027079642</v>
+      <c r="D94" s="2" t="n">
+        <v>46030.602707964201</v>
       </c>
       <c r="E94" t="s">
         <v>115</v>
@@ -3180,6 +3219,240 @@
       </c>
       <c r="H94" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2</v>
+      </c>
+      <c r="B95" t="s">
+        <v>126</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>46034.4424002813</v>
+      </c>
+      <c r="E95" t="s">
+        <v>127</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>128</v>
+      </c>
+      <c r="H95" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>126</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>46034.442454999</v>
+      </c>
+      <c r="E96" t="s">
+        <v>130</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>128</v>
+      </c>
+      <c r="H96" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>46034.4425439726</v>
+      </c>
+      <c r="E97" t="s">
+        <v>127</v>
+      </c>
+      <c r="F97" t="n">
+        <v>126</v>
+      </c>
+      <c r="G97" t="s">
+        <v>128</v>
+      </c>
+      <c r="H97" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2</v>
+      </c>
+      <c r="B98" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>46034.4425948175</v>
+      </c>
+      <c r="E98" t="s">
+        <v>130</v>
+      </c>
+      <c r="F98" t="n">
+        <v>126</v>
+      </c>
+      <c r="G98" t="s">
+        <v>128</v>
+      </c>
+      <c r="H98" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2</v>
+      </c>
+      <c r="B99" t="s">
+        <v>132</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>46034.4427237583</v>
+      </c>
+      <c r="E99" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>133</v>
+      </c>
+      <c r="H99" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>134</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>46034.442922526</v>
+      </c>
+      <c r="E100" t="s">
+        <v>127</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7</v>
+      </c>
+      <c r="G100" t="s">
+        <v>135</v>
+      </c>
+      <c r="H100" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" t="s">
+        <v>134</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>46034.4429738446</v>
+      </c>
+      <c r="E101" t="s">
+        <v>130</v>
+      </c>
+      <c r="F101" t="n">
+        <v>15</v>
+      </c>
+      <c r="G101" t="s">
+        <v>135</v>
+      </c>
+      <c r="H101" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>46034.4436375739</v>
+      </c>
+      <c r="E102" t="s">
+        <v>127</v>
+      </c>
+      <c r="F102" t="n">
+        <v>5</v>
+      </c>
+      <c r="G102" t="s">
+        <v>135</v>
+      </c>
+      <c r="H102" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>46034.4436979918</v>
+      </c>
+      <c r="E103" t="s">
+        <v>130</v>
+      </c>
+      <c r="F103" t="n">
+        <v>13</v>
+      </c>
+      <c r="G103" t="s">
+        <v>135</v>
+      </c>
+      <c r="H103" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4001,6 +4274,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="141">
   <si>
     <t>Phase</t>
   </si>
@@ -425,6 +425,21 @@
   </si>
   <si>
     <t xml:space="preserve">Single Leg Calf Raises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ankle Dorsiflexion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm</t>
   </si>
 </sst>
 </file>
@@ -3455,6 +3470,84 @@
         <v>129</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" t="s">
+        <v>137</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>46034.5392887065</v>
+      </c>
+      <c r="E104" t="s">
+        <v>138</v>
+      </c>
+      <c r="F104" t="n">
+        <v>40</v>
+      </c>
+      <c r="G104" t="s">
+        <v>139</v>
+      </c>
+      <c r="H104" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2</v>
+      </c>
+      <c r="B105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>46034.5661824204</v>
+      </c>
+      <c r="E105" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" t="n">
+        <v>6</v>
+      </c>
+      <c r="G105" t="s">
+        <v>141</v>
+      </c>
+      <c r="H105" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>140</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>46034.5662473904</v>
+      </c>
+      <c r="E106" t="s">
+        <v>130</v>
+      </c>
+      <c r="F106" t="n">
+        <v>15</v>
+      </c>
+      <c r="G106" t="s">
+        <v>141</v>
+      </c>
+      <c r="H106" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
   <si>
     <t>Phase</t>
   </si>
@@ -440,6 +440,30 @@
   </si>
   <si>
     <t xml:space="preserve">cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-13 13:19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-15 12:17:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-16 16:01:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seconds</t>
   </si>
 </sst>
 </file>
@@ -3548,6 +3572,214 @@
         <v>129</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2</v>
+      </c>
+      <c r="B107" t="s">
+        <v>134</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>46038.6692860279</v>
+      </c>
+      <c r="E107" t="s">
+        <v>127</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9</v>
+      </c>
+      <c r="G107" t="s">
+        <v>135</v>
+      </c>
+      <c r="H107" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" t="s">
+        <v>134</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>46038.6693706211</v>
+      </c>
+      <c r="E108" t="s">
+        <v>130</v>
+      </c>
+      <c r="F108" t="n">
+        <v>17</v>
+      </c>
+      <c r="G108" t="s">
+        <v>135</v>
+      </c>
+      <c r="H108" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>46038.6695542673</v>
+      </c>
+      <c r="E109" t="s">
+        <v>127</v>
+      </c>
+      <c r="F109" t="n">
+        <v>7</v>
+      </c>
+      <c r="G109" t="s">
+        <v>135</v>
+      </c>
+      <c r="H109" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>136</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>46038.6696276505</v>
+      </c>
+      <c r="E110" t="s">
+        <v>130</v>
+      </c>
+      <c r="F110" t="n">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>135</v>
+      </c>
+      <c r="H110" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>140</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>46038.6698742878</v>
+      </c>
+      <c r="E111" t="s">
+        <v>127</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8</v>
+      </c>
+      <c r="G111" t="s">
+        <v>141</v>
+      </c>
+      <c r="H111" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B112" t="s">
+        <v>140</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>46038.6699281527</v>
+      </c>
+      <c r="E112" t="s">
+        <v>130</v>
+      </c>
+      <c r="F112" t="n">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s">
+        <v>141</v>
+      </c>
+      <c r="H112" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2</v>
+      </c>
+      <c r="B113" t="s">
+        <v>148</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>46038.6707992843</v>
+      </c>
+      <c r="E113" t="s">
+        <v>127</v>
+      </c>
+      <c r="F113" t="n">
+        <v>30</v>
+      </c>
+      <c r="G113" t="s">
+        <v>149</v>
+      </c>
+      <c r="H113" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2</v>
+      </c>
+      <c r="B114" t="s">
+        <v>148</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>46038.6708369735</v>
+      </c>
+      <c r="E114" t="s">
+        <v>130</v>
+      </c>
+      <c r="F114" t="n">
+        <v>30</v>
+      </c>
+      <c r="G114" t="s">
+        <v>149</v>
+      </c>
+      <c r="H114" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4390,6 +4622,75 @@
         <v>3</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>146</v>
+      </c>
+      <c r="B39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -1,20 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_3C96CC80BAAC2631FFEDC1AFD891A03B6D085004" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FF6090A-D48B-6D4D-9BE8-A4AC728480F3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase_data" sheetId="1" r:id="rId1"/>
+    <sheet name="daily" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="158">
   <si>
     <t>Phase</t>
   </si>
@@ -388,93 +395,116 @@
     <t>lag</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-01-12 10:36:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Knee Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">degrees</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Knee Flexion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Calf Raises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrapBar Deadlift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ankle Dorsiflexion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-13 13:19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-15 12:17:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-16 16:01:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seconds</t>
+    <t>2026-01-12 10:36:40</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>Passive Knee Extension</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Passive Knee Flexion</t>
+  </si>
+  <si>
+    <t>Swelling</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>Single Leg Bridge</t>
+  </si>
+  <si>
+    <t>reps</t>
+  </si>
+  <si>
+    <t>Single Leg Calf Raises</t>
+  </si>
+  <si>
+    <t>TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t>DL</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Ankle Dorsiflexion</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>2026-01-13 13:19:50</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-01-15 12:17:59</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-01-16 16:01:37</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>Side Bridge</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>2026-01-19 14:47:11</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>2026-01-20 08:38:02</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>Single Leg Balance (Eyes Open)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Postero-Medial)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Postero-Lateral)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -486,6 +516,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -508,11 +539,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -808,15 +838,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H134"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.33203125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -842,23 +872,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>45947</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>45947.704595950803</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
@@ -868,23 +898,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>45947</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>45947.704659476702</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
@@ -894,23 +924,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1">
         <v>45947</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>45947.704952933702</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>100</v>
       </c>
       <c r="G4" t="s">
@@ -920,23 +950,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>45947</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>45947.705045544899</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>130</v>
       </c>
       <c r="G5" t="s">
@@ -946,23 +976,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>45947</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>45947.705211323802</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" t="s">
@@ -972,23 +1002,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1">
         <v>45947</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>45947.705280315502</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
@@ -998,23 +1028,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>0</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="1">
         <v>45948</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>45948.664888072301</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
@@ -1024,23 +1054,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="1">
         <v>45948</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>45948.664965998003</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
@@ -1050,23 +1080,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>0</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="1">
         <v>45948</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>45948.665130714297</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>105</v>
       </c>
       <c r="G10" t="s">
@@ -1076,23 +1106,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>0</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="1">
         <v>45948</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>45948.665214019697</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>128</v>
       </c>
       <c r="G11" t="s">
@@ -1102,23 +1132,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>0</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="1">
         <v>45948</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>45948.665349680203</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0</v>
       </c>
       <c r="G12" t="s">
@@ -1128,23 +1158,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>0</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="1">
         <v>45948</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2">
         <v>45948.665392863797</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
@@ -1154,23 +1184,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>0</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="1">
         <v>45948</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>45948.666299291603</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>45</v>
       </c>
       <c r="G14" t="s">
@@ -1180,23 +1210,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="1">
         <v>45948</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="2">
         <v>45948.666350146101</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>60</v>
       </c>
       <c r="G15" t="s">
@@ -1206,23 +1236,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>0</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="1">
         <v>45950</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2">
         <v>45950.435864299601</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" t="s">
@@ -1232,23 +1262,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>0</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="1">
         <v>45950</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2">
         <v>45950.435907915002</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0</v>
       </c>
       <c r="G17" t="s">
@@ -1258,23 +1288,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>0</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="1">
         <v>45950</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2">
         <v>45950.436296253101</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
@@ -1284,23 +1314,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>0</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="1">
         <v>45950</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="2">
         <v>45950.436443767503</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>118</v>
       </c>
       <c r="G19" t="s">
@@ -1310,23 +1340,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>0</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="1">
         <v>45950</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2">
         <v>45950.436589819903</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>47</v>
       </c>
       <c r="G20" t="s">
@@ -1336,23 +1366,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>0</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="1">
         <v>45950</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="2">
         <v>45950.436639752603</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>59</v>
       </c>
       <c r="G21" t="s">
@@ -1362,23 +1392,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="1">
         <v>45958</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="2">
         <v>45958.6841577331</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
@@ -1388,23 +1418,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>0</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="1">
         <v>45958</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2">
         <v>45958.684209632003</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" t="s">
@@ -1414,23 +1444,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>0</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="1">
         <v>45958</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="2">
         <v>45958.684322089699</v>
       </c>
       <c r="E24" t="s">
         <v>44</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>121</v>
       </c>
       <c r="G24" t="s">
@@ -1440,23 +1470,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="1">
         <v>45958</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="2">
         <v>45958.684389989503</v>
       </c>
       <c r="E25" t="s">
         <v>47</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>130</v>
       </c>
       <c r="G25" t="s">
@@ -1466,23 +1496,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>0</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="1">
         <v>45958</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="2">
         <v>45958.684524802797</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
@@ -1492,23 +1522,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>0</v>
       </c>
       <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="1">
         <v>45958</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="2">
         <v>45958.684905007998</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>59</v>
       </c>
       <c r="G27" t="s">
@@ -1518,23 +1548,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>0</v>
       </c>
       <c r="B28" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="1">
         <v>45958</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="2">
         <v>45958.684968170899</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>48</v>
       </c>
       <c r="G28" t="s">
@@ -1544,23 +1574,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>0</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="1">
         <v>45958</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="2">
         <v>45958.685067698403</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>95</v>
       </c>
       <c r="G29" t="s">
@@ -1570,23 +1600,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>0</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="1">
         <v>45958</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="2">
         <v>45958.685166592397</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>64</v>
       </c>
       <c r="G30" t="s">
@@ -1596,23 +1626,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>0</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="1">
         <v>45958</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="2">
         <v>45958.685324976199</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>93</v>
       </c>
       <c r="G31" t="s">
@@ -1622,23 +1652,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>0</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="1">
         <v>45958</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="2">
         <v>45958.685387673802</v>
       </c>
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>62</v>
       </c>
       <c r="G32" t="s">
@@ -1648,23 +1678,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>0</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="1">
         <v>45959</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="2">
         <v>45959.385571423503</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" t="s">
@@ -1674,23 +1704,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>0</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="1">
         <v>45959</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="2">
         <v>45959.385909921002</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
@@ -1700,23 +1730,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="1">
         <v>45960</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="2">
         <v>45960.491801712298</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>0</v>
       </c>
       <c r="G35" t="s">
@@ -1726,23 +1756,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>0</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="1">
         <v>45960</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="2">
         <v>45960.491960884297</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>125</v>
       </c>
       <c r="G36" t="s">
@@ -1752,23 +1782,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>0</v>
       </c>
       <c r="B37" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="1">
         <v>45960</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="2">
         <v>45960.492014117801</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>128</v>
       </c>
       <c r="G37" t="s">
@@ -1778,23 +1808,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="1">
         <v>45960</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="2">
         <v>45960.492522578497</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>72</v>
       </c>
       <c r="G38" t="s">
@@ -1804,23 +1834,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39">
         <v>0</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="1">
         <v>45960</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="2">
         <v>45960.4925716453</v>
       </c>
       <c r="E39" t="s">
         <v>47</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>92</v>
       </c>
       <c r="G39" t="s">
@@ -1830,23 +1860,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>0</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="1">
         <v>45960</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="2">
         <v>45960.492643531601</v>
       </c>
       <c r="E40" t="s">
         <v>44</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>74</v>
       </c>
       <c r="G40" t="s">
@@ -1856,23 +1886,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>0</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="1">
         <v>45960</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="2">
         <v>45960.492700254901</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>90</v>
       </c>
       <c r="G41" t="s">
@@ -1882,23 +1912,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>0</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="1">
         <v>45965</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="2">
         <v>45965.485657138801</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
@@ -1908,23 +1938,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43">
         <v>0</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="1">
         <v>45965</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="2">
         <v>45965.485844846997</v>
       </c>
       <c r="E43" t="s">
         <v>44</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>80</v>
       </c>
       <c r="G43" t="s">
@@ -1934,23 +1964,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44">
         <v>0</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="1">
         <v>45965</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="2">
         <v>45965.485890989898</v>
       </c>
       <c r="E44" t="s">
         <v>44</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>82</v>
       </c>
       <c r="G44" t="s">
@@ -1960,23 +1990,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>0</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="1">
         <v>45965</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="2">
         <v>45965.485968485897</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>87</v>
       </c>
       <c r="G45" t="s">
@@ -1986,23 +2016,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>0</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="1">
         <v>45965</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="2">
         <v>45965.486001955702</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>89</v>
       </c>
       <c r="G46" t="s">
@@ -2012,23 +2042,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>0</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="1">
         <v>45965</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="2">
         <v>45965.486250549002</v>
       </c>
       <c r="E47" t="s">
         <v>44</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>50</v>
       </c>
       <c r="G47" t="s">
@@ -2038,23 +2068,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>0</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="1">
         <v>45965</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="2">
         <v>45965.486292492598</v>
       </c>
       <c r="E48" t="s">
         <v>44</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>52</v>
       </c>
       <c r="G48" t="s">
@@ -2064,23 +2094,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49">
         <v>0</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="1">
         <v>45965</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="2">
         <v>45965.486377312402</v>
       </c>
       <c r="E49" t="s">
         <v>47</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>54</v>
       </c>
       <c r="G49" t="s">
@@ -2090,23 +2120,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50">
         <v>0</v>
       </c>
       <c r="B50" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="1">
         <v>45965</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="2">
         <v>45965.486404639203</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>56</v>
       </c>
       <c r="G50" t="s">
@@ -2116,23 +2146,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51">
         <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="1">
         <v>45974</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="2">
         <v>45974.411367086701</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>3</v>
       </c>
       <c r="G51" t="s">
@@ -2142,23 +2172,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="1">
         <v>45974</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="2">
         <v>45974.411416700903</v>
       </c>
       <c r="E52" t="s">
         <v>47</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
@@ -2168,23 +2198,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="1">
         <v>45975</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="2">
         <v>45975.537941231603</v>
       </c>
       <c r="E53" t="s">
         <v>44</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>2</v>
       </c>
       <c r="G53" t="s">
@@ -2194,23 +2224,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>1</v>
       </c>
       <c r="B54" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="1">
         <v>45975</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="2">
         <v>45975.538157998897</v>
       </c>
       <c r="E54" t="s">
         <v>47</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
@@ -2220,23 +2250,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="1">
         <v>45975</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="2">
         <v>45975.544261836498</v>
       </c>
       <c r="E55" t="s">
         <v>44</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>5</v>
       </c>
       <c r="G55" t="s">
@@ -2246,23 +2276,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56">
         <v>1</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="1">
         <v>45975</v>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="2">
         <v>45975.544303050097</v>
       </c>
       <c r="E56" t="s">
         <v>47</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
@@ -2272,23 +2302,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>1</v>
       </c>
       <c r="B57" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="1">
         <v>45975</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="2">
         <v>45975.544539589202</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>110</v>
       </c>
       <c r="G57" t="s">
@@ -2298,23 +2328,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58">
         <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="1">
         <v>45975</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="2">
         <v>45975.544575668398</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>125</v>
       </c>
       <c r="G58" t="s">
@@ -2324,23 +2354,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59">
         <v>1</v>
       </c>
       <c r="B59" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="1">
         <v>45989</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="2">
         <v>45989.657419278097</v>
       </c>
       <c r="E59" t="s">
         <v>44</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
@@ -2350,23 +2380,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60">
         <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="1">
         <v>45989</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="2">
         <v>45989.657464727003</v>
       </c>
       <c r="E60" t="s">
         <v>47</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>0</v>
       </c>
       <c r="G60" t="s">
@@ -2376,23 +2406,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61">
         <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="1">
         <v>45989</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="2">
         <v>45989.657658854201</v>
       </c>
       <c r="E61" t="s">
         <v>44</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
@@ -2402,23 +2432,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="1">
         <v>45989</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="2">
         <v>45989.657725292898</v>
       </c>
       <c r="E62" t="s">
         <v>47</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
@@ -2428,23 +2458,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>1</v>
       </c>
       <c r="B63" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="1">
         <v>45989</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="2">
         <v>45989.657879157297</v>
       </c>
       <c r="E63" t="s">
         <v>44</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>117</v>
       </c>
       <c r="G63" t="s">
@@ -2454,23 +2484,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64">
         <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="1">
         <v>45989</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="2">
         <v>45989.657918513098</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>126</v>
       </c>
       <c r="G64" t="s">
@@ -2480,23 +2510,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65">
         <v>1</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="1">
         <v>45989</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="2">
         <v>45989.658742763997</v>
       </c>
       <c r="E65" t="s">
         <v>44</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>2</v>
       </c>
       <c r="G65" t="s">
@@ -2506,23 +2536,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66">
         <v>1</v>
       </c>
       <c r="B66" t="s">
         <v>114</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="1">
         <v>45996</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="2">
         <v>46030.597367625</v>
       </c>
       <c r="E66" t="s">
         <v>115</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
@@ -2532,23 +2562,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67">
         <v>1</v>
       </c>
       <c r="B67" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="1">
         <v>45996</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="2">
         <v>46030.597429351699</v>
       </c>
       <c r="E67" t="s">
         <v>118</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
@@ -2558,23 +2588,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68">
         <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>119</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="1">
         <v>45996</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="2">
         <v>46030.597768818101</v>
       </c>
       <c r="E68" t="s">
         <v>115</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>120</v>
       </c>
       <c r="G68" t="s">
@@ -2584,23 +2614,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69">
         <v>1</v>
       </c>
       <c r="B69" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="1">
         <v>45996</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="2">
         <v>46030.597819244598</v>
       </c>
       <c r="E69" t="s">
         <v>118</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>125</v>
       </c>
       <c r="G69" t="s">
@@ -2610,23 +2640,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70">
         <v>1</v>
       </c>
       <c r="B70" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="1">
         <v>45996</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="2">
         <v>46030.5981109887</v>
       </c>
       <c r="E70" t="s">
         <v>115</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>2</v>
       </c>
       <c r="G70" t="s">
@@ -2636,23 +2666,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71">
         <v>1</v>
       </c>
       <c r="B71" t="s">
         <v>121</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="1">
         <v>45996</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="2">
         <v>46030.598165269199</v>
       </c>
       <c r="E71" t="s">
         <v>118</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" t="s">
@@ -2662,23 +2692,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72">
         <v>1</v>
       </c>
       <c r="B72" t="s">
         <v>122</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="1">
         <v>45996</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="2">
         <v>46030.5985355347</v>
       </c>
       <c r="E72" t="s">
         <v>115</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
@@ -2688,23 +2718,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73">
         <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="1">
         <v>46003</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="2">
         <v>46030.598729730598</v>
       </c>
       <c r="E73" t="s">
         <v>115</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
@@ -2714,23 +2744,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74">
         <v>1</v>
       </c>
       <c r="B74" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="1">
         <v>46003</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="2">
         <v>46030.598804364497</v>
       </c>
       <c r="E74" t="s">
         <v>118</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>0</v>
       </c>
       <c r="G74" t="s">
@@ -2740,23 +2770,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75">
         <v>1</v>
       </c>
       <c r="B75" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="1">
         <v>46003</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="2">
         <v>46030.598952235603</v>
       </c>
       <c r="E75" t="s">
         <v>115</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>122</v>
       </c>
       <c r="G75" t="s">
@@ -2766,23 +2796,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76">
         <v>1</v>
       </c>
       <c r="B76" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="C76" s="1">
         <v>46003</v>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="2">
         <v>46030.5989977875</v>
       </c>
       <c r="E76" t="s">
         <v>118</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>127</v>
       </c>
       <c r="G76" t="s">
@@ -2792,23 +2822,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77">
         <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>121</v>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C77" s="1">
         <v>46003</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="2">
         <v>46030.5991297031</v>
       </c>
       <c r="E77" t="s">
         <v>115</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
@@ -2818,23 +2848,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78">
         <v>1</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
       </c>
-      <c r="C78" s="1" t="n">
+      <c r="C78" s="1">
         <v>46003</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="2">
         <v>46030.599185763604</v>
       </c>
       <c r="E78" t="s">
         <v>118</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>0</v>
       </c>
       <c r="G78" t="s">
@@ -2844,23 +2874,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79">
         <v>1</v>
       </c>
       <c r="B79" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="1" t="n">
+      <c r="C79" s="1">
         <v>46003</v>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="2">
         <v>46030.599461440201</v>
       </c>
       <c r="E79" t="s">
         <v>118</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
@@ -2870,23 +2900,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80">
         <v>1</v>
       </c>
       <c r="B80" t="s">
         <v>122</v>
       </c>
-      <c r="C80" s="1" t="n">
+      <c r="C80" s="1">
         <v>46003</v>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="2">
         <v>46030.6009521206</v>
       </c>
       <c r="E80" t="s">
         <v>115</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
@@ -2896,23 +2926,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81">
         <v>1</v>
       </c>
       <c r="B81" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="1" t="n">
+      <c r="C81" s="1">
         <v>46010</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="2">
         <v>46030.601362099602</v>
       </c>
       <c r="E81" t="s">
         <v>115</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
@@ -2922,23 +2952,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82">
         <v>1</v>
       </c>
       <c r="B82" t="s">
         <v>114</v>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="C82" s="1">
         <v>46010</v>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="2">
         <v>46030.601397267797</v>
       </c>
       <c r="E82" t="s">
         <v>118</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>0</v>
       </c>
       <c r="G82" t="s">
@@ -2948,23 +2978,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83">
         <v>1</v>
       </c>
       <c r="B83" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="1" t="n">
+      <c r="C83" s="1">
         <v>46010</v>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="2">
         <v>46030.601664699498</v>
       </c>
       <c r="E83" t="s">
         <v>115</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>124</v>
       </c>
       <c r="G83" t="s">
@@ -2974,23 +3004,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84">
         <v>1</v>
       </c>
       <c r="B84" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="1" t="n">
+      <c r="C84" s="1">
         <v>46010</v>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="2">
         <v>46030.601707849899</v>
       </c>
       <c r="E84" t="s">
         <v>118</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>125</v>
       </c>
       <c r="G84" t="s">
@@ -3000,23 +3030,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85">
         <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>121</v>
       </c>
-      <c r="C85" s="1" t="n">
+      <c r="C85" s="1">
         <v>46010</v>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="2">
         <v>46030.601880503098</v>
       </c>
       <c r="E85" t="s">
         <v>115</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" t="s">
@@ -3026,23 +3056,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86">
         <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>121</v>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="C86" s="1">
         <v>46010</v>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="2">
         <v>46030.601922228001</v>
       </c>
       <c r="E86" t="s">
         <v>118</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
@@ -3052,23 +3082,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87">
         <v>1</v>
       </c>
       <c r="B87" t="s">
         <v>122</v>
       </c>
-      <c r="C87" s="1" t="n">
+      <c r="C87" s="1">
         <v>46010</v>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="2">
         <v>46030.602015028402</v>
       </c>
       <c r="E87" t="s">
         <v>115</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
@@ -3078,23 +3108,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88">
         <v>1</v>
       </c>
       <c r="B88" t="s">
         <v>114</v>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="C88" s="1">
         <v>46022</v>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="2">
         <v>46030.602325239699</v>
       </c>
       <c r="E88" t="s">
         <v>115</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>0</v>
       </c>
       <c r="G88" t="s">
@@ -3104,23 +3134,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89">
         <v>1</v>
       </c>
       <c r="B89" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="1" t="n">
+      <c r="C89" s="1">
         <v>46022</v>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="2">
         <v>46030.602364462902</v>
       </c>
       <c r="E89" t="s">
         <v>118</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>0</v>
       </c>
       <c r="G89" t="s">
@@ -3130,23 +3160,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90">
         <v>1</v>
       </c>
       <c r="B90" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="1" t="n">
+      <c r="C90" s="1">
         <v>46022</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="2">
         <v>46030.602432747299</v>
       </c>
       <c r="E90" t="s">
         <v>115</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>125</v>
       </c>
       <c r="G90" t="s">
@@ -3156,23 +3186,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91">
         <v>1</v>
       </c>
       <c r="B91" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="1" t="n">
+      <c r="C91" s="1">
         <v>46022</v>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="2">
         <v>46030.602474245497</v>
       </c>
       <c r="E91" t="s">
         <v>118</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>125</v>
       </c>
       <c r="G91" t="s">
@@ -3182,23 +3212,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92">
         <v>1</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
       </c>
-      <c r="C92" s="1" t="n">
+      <c r="C92" s="1">
         <v>46022</v>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" s="2">
         <v>46030.602583176304</v>
       </c>
       <c r="E92" t="s">
         <v>115</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>0</v>
       </c>
       <c r="G92" t="s">
@@ -3208,23 +3238,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93">
         <v>1</v>
       </c>
       <c r="B93" t="s">
         <v>121</v>
       </c>
-      <c r="C93" s="1" t="n">
+      <c r="C93" s="1">
         <v>46022</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="2">
         <v>46030.602620265403</v>
       </c>
       <c r="E93" t="s">
         <v>118</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>0</v>
       </c>
       <c r="G93" t="s">
@@ -3234,23 +3264,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94">
         <v>1</v>
       </c>
       <c r="B94" t="s">
         <v>122</v>
       </c>
-      <c r="C94" s="1" t="n">
+      <c r="C94" s="1">
         <v>46022</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="2">
         <v>46030.602707964201</v>
       </c>
       <c r="E94" t="s">
         <v>115</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>0</v>
       </c>
       <c r="G94" t="s">
@@ -3260,23 +3290,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95">
         <v>2</v>
       </c>
       <c r="B95" t="s">
         <v>126</v>
       </c>
-      <c r="C95" s="1" t="n">
+      <c r="C95" s="1">
         <v>46034</v>
       </c>
-      <c r="D95" s="3" t="n">
-        <v>46034.4424002813</v>
+      <c r="D95" s="2">
+        <v>46034.442400281303</v>
       </c>
       <c r="E95" t="s">
         <v>127</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" t="s">
@@ -3286,23 +3316,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96">
         <v>2</v>
       </c>
       <c r="B96" t="s">
         <v>126</v>
       </c>
-      <c r="C96" s="1" t="n">
+      <c r="C96" s="1">
         <v>46034</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="2">
         <v>46034.442454999</v>
       </c>
       <c r="E96" t="s">
         <v>130</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>0</v>
       </c>
       <c r="G96" t="s">
@@ -3312,23 +3342,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97">
         <v>2</v>
       </c>
       <c r="B97" t="s">
         <v>131</v>
       </c>
-      <c r="C97" s="1" t="n">
+      <c r="C97" s="1">
         <v>46034</v>
       </c>
-      <c r="D97" s="3" t="n">
-        <v>46034.4425439726</v>
+      <c r="D97" s="2">
+        <v>46034.442543972596</v>
       </c>
       <c r="E97" t="s">
         <v>127</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>126</v>
       </c>
       <c r="G97" t="s">
@@ -3338,23 +3368,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98">
         <v>2</v>
       </c>
       <c r="B98" t="s">
         <v>131</v>
       </c>
-      <c r="C98" s="1" t="n">
+      <c r="C98" s="1">
         <v>46034</v>
       </c>
-      <c r="D98" s="3" t="n">
-        <v>46034.4425948175</v>
+      <c r="D98" s="2">
+        <v>46034.442594817498</v>
       </c>
       <c r="E98" t="s">
         <v>130</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>126</v>
       </c>
       <c r="G98" t="s">
@@ -3364,23 +3394,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99">
         <v>2</v>
       </c>
       <c r="B99" t="s">
         <v>132</v>
       </c>
-      <c r="C99" s="1" t="n">
+      <c r="C99" s="1">
         <v>46034</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="2">
         <v>46034.4427237583</v>
       </c>
       <c r="E99" t="s">
         <v>127</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>0</v>
       </c>
       <c r="G99" t="s">
@@ -3390,23 +3420,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100">
         <v>2</v>
       </c>
       <c r="B100" t="s">
         <v>134</v>
       </c>
-      <c r="C100" s="1" t="n">
+      <c r="C100" s="1">
         <v>46034</v>
       </c>
-      <c r="D100" s="3" t="n">
-        <v>46034.442922526</v>
+      <c r="D100" s="2">
+        <v>46034.442922526003</v>
       </c>
       <c r="E100" t="s">
         <v>127</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>7</v>
       </c>
       <c r="G100" t="s">
@@ -3416,23 +3446,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101">
         <v>2</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
       </c>
-      <c r="C101" s="1" t="n">
+      <c r="C101" s="1">
         <v>46034</v>
       </c>
-      <c r="D101" s="3" t="n">
-        <v>46034.4429738446</v>
+      <c r="D101" s="2">
+        <v>46034.442973844598</v>
       </c>
       <c r="E101" t="s">
         <v>130</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>15</v>
       </c>
       <c r="G101" t="s">
@@ -3442,23 +3472,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102">
         <v>2</v>
       </c>
       <c r="B102" t="s">
         <v>136</v>
       </c>
-      <c r="C102" s="1" t="n">
+      <c r="C102" s="1">
         <v>46034</v>
       </c>
-      <c r="D102" s="3" t="n">
-        <v>46034.4436375739</v>
+      <c r="D102" s="2">
+        <v>46034.443637573902</v>
       </c>
       <c r="E102" t="s">
         <v>127</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>5</v>
       </c>
       <c r="G102" t="s">
@@ -3468,23 +3498,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103">
         <v>2</v>
       </c>
       <c r="B103" t="s">
         <v>136</v>
       </c>
-      <c r="C103" s="1" t="n">
+      <c r="C103" s="1">
         <v>46034</v>
       </c>
-      <c r="D103" s="3" t="n">
-        <v>46034.4436979918</v>
+      <c r="D103" s="2">
+        <v>46034.443697991803</v>
       </c>
       <c r="E103" t="s">
         <v>130</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>13</v>
       </c>
       <c r="G103" t="s">
@@ -3494,23 +3524,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104">
         <v>2</v>
       </c>
       <c r="B104" t="s">
         <v>137</v>
       </c>
-      <c r="C104" s="1" t="n">
+      <c r="C104" s="1">
         <v>46034</v>
       </c>
-      <c r="D104" s="3" t="n">
-        <v>46034.5392887065</v>
+      <c r="D104" s="2">
+        <v>46034.539288706503</v>
       </c>
       <c r="E104" t="s">
         <v>138</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>40</v>
       </c>
       <c r="G104" t="s">
@@ -3520,23 +3550,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105">
         <v>2</v>
       </c>
       <c r="B105" t="s">
         <v>140</v>
       </c>
-      <c r="C105" s="1" t="n">
+      <c r="C105" s="1">
         <v>46034</v>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="D105" s="2">
         <v>46034.5661824204</v>
       </c>
       <c r="E105" t="s">
         <v>127</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>6</v>
       </c>
       <c r="G105" t="s">
@@ -3546,23 +3576,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106">
         <v>2</v>
       </c>
       <c r="B106" t="s">
         <v>140</v>
       </c>
-      <c r="C106" s="1" t="n">
+      <c r="C106" s="1">
         <v>46034</v>
       </c>
-      <c r="D106" s="3" t="n">
-        <v>46034.5662473904</v>
+      <c r="D106" s="2">
+        <v>46034.566247390401</v>
       </c>
       <c r="E106" t="s">
         <v>130</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>15</v>
       </c>
       <c r="G106" t="s">
@@ -3572,23 +3602,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107">
         <v>2</v>
       </c>
       <c r="B107" t="s">
         <v>134</v>
       </c>
-      <c r="C107" s="1" t="n">
+      <c r="C107" s="1">
         <v>46038</v>
       </c>
-      <c r="D107" s="3" t="n">
+      <c r="D107" s="2">
         <v>46038.6692860279</v>
       </c>
       <c r="E107" t="s">
         <v>127</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>9</v>
       </c>
       <c r="G107" t="s">
@@ -3598,23 +3628,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108">
         <v>2</v>
       </c>
       <c r="B108" t="s">
         <v>134</v>
       </c>
-      <c r="C108" s="1" t="n">
+      <c r="C108" s="1">
         <v>46038</v>
       </c>
-      <c r="D108" s="3" t="n">
-        <v>46038.6693706211</v>
+      <c r="D108" s="2">
+        <v>46038.669370621101</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>17</v>
       </c>
       <c r="G108" t="s">
@@ -3624,23 +3654,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109">
         <v>2</v>
       </c>
       <c r="B109" t="s">
         <v>136</v>
       </c>
-      <c r="C109" s="1" t="n">
+      <c r="C109" s="1">
         <v>46038</v>
       </c>
-      <c r="D109" s="3" t="n">
-        <v>46038.6695542673</v>
+      <c r="D109" s="2">
+        <v>46038.669554267297</v>
       </c>
       <c r="E109" t="s">
         <v>127</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>7</v>
       </c>
       <c r="G109" t="s">
@@ -3650,23 +3680,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110">
         <v>2</v>
       </c>
       <c r="B110" t="s">
         <v>136</v>
       </c>
-      <c r="C110" s="1" t="n">
+      <c r="C110" s="1">
         <v>46038</v>
       </c>
-      <c r="D110" s="3" t="n">
-        <v>46038.6696276505</v>
+      <c r="D110" s="2">
+        <v>46038.669627650503</v>
       </c>
       <c r="E110" t="s">
         <v>130</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>14</v>
       </c>
       <c r="G110" t="s">
@@ -3676,23 +3706,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111">
         <v>2</v>
       </c>
       <c r="B111" t="s">
         <v>140</v>
       </c>
-      <c r="C111" s="1" t="n">
+      <c r="C111" s="1">
         <v>46038</v>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="D111" s="2">
         <v>46038.6698742878</v>
       </c>
       <c r="E111" t="s">
         <v>127</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>8</v>
       </c>
       <c r="G111" t="s">
@@ -3702,23 +3732,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112">
         <v>2</v>
       </c>
       <c r="B112" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="1" t="n">
+      <c r="C112" s="1">
         <v>46038</v>
       </c>
-      <c r="D112" s="3" t="n">
-        <v>46038.6699281527</v>
+      <c r="D112" s="2">
+        <v>46038.669928152704</v>
       </c>
       <c r="E112" t="s">
         <v>130</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>15</v>
       </c>
       <c r="G112" t="s">
@@ -3728,23 +3758,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113">
         <v>2</v>
       </c>
       <c r="B113" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="1" t="n">
+      <c r="C113" s="1">
         <v>46038</v>
       </c>
-      <c r="D113" s="3" t="n">
+      <c r="D113" s="2">
         <v>46038.6707992843</v>
       </c>
       <c r="E113" t="s">
         <v>127</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>30</v>
       </c>
       <c r="G113" t="s">
@@ -3754,29 +3784,549 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114">
         <v>2</v>
       </c>
       <c r="B114" t="s">
         <v>148</v>
       </c>
-      <c r="C114" s="1" t="n">
+      <c r="C114" s="1">
         <v>46038</v>
       </c>
-      <c r="D114" s="3" t="n">
-        <v>46038.6708369735</v>
+      <c r="D114" s="2">
+        <v>46038.670836973499</v>
       </c>
       <c r="E114" t="s">
         <v>130</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>30</v>
       </c>
       <c r="G114" t="s">
         <v>149</v>
       </c>
       <c r="H114" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D115" s="2">
+        <v>46042.360163172401</v>
+      </c>
+      <c r="E115" t="s">
+        <v>127</v>
+      </c>
+      <c r="F115">
+        <v>30</v>
+      </c>
+      <c r="G115" t="s">
+        <v>149</v>
+      </c>
+      <c r="H115" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>2</v>
+      </c>
+      <c r="B116" t="s">
+        <v>154</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D116" s="2">
+        <v>46042.360217777801</v>
+      </c>
+      <c r="E116" t="s">
+        <v>130</v>
+      </c>
+      <c r="F116">
+        <v>45</v>
+      </c>
+      <c r="G116" t="s">
+        <v>149</v>
+      </c>
+      <c r="H116" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>2</v>
+      </c>
+      <c r="B117" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D117" s="2">
+        <v>46042.361174106802</v>
+      </c>
+      <c r="E117" t="s">
+        <v>127</v>
+      </c>
+      <c r="F117">
+        <v>50</v>
+      </c>
+      <c r="G117" t="s">
+        <v>141</v>
+      </c>
+      <c r="H117" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>2</v>
+      </c>
+      <c r="B118" t="s">
+        <v>155</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D118" s="2">
+        <v>46042.361259715202</v>
+      </c>
+      <c r="E118" t="s">
+        <v>127</v>
+      </c>
+      <c r="F118">
+        <v>52</v>
+      </c>
+      <c r="G118" t="s">
+        <v>141</v>
+      </c>
+      <c r="H118" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>2</v>
+      </c>
+      <c r="B119" t="s">
+        <v>155</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D119" s="2">
+        <v>46042.361303134297</v>
+      </c>
+      <c r="E119" t="s">
+        <v>127</v>
+      </c>
+      <c r="F119">
+        <v>53</v>
+      </c>
+      <c r="G119" t="s">
+        <v>141</v>
+      </c>
+      <c r="H119" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>2</v>
+      </c>
+      <c r="B120" t="s">
+        <v>155</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D120" s="2">
+        <v>46042.361404144598</v>
+      </c>
+      <c r="E120" t="s">
+        <v>130</v>
+      </c>
+      <c r="F120">
+        <v>60</v>
+      </c>
+      <c r="G120" t="s">
+        <v>141</v>
+      </c>
+      <c r="H120" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>2</v>
+      </c>
+      <c r="B121" t="s">
+        <v>155</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D121" s="2">
+        <v>46042.361443357302</v>
+      </c>
+      <c r="E121" t="s">
+        <v>130</v>
+      </c>
+      <c r="F121">
+        <v>61</v>
+      </c>
+      <c r="G121" t="s">
+        <v>141</v>
+      </c>
+      <c r="H121" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>2</v>
+      </c>
+      <c r="B122" t="s">
+        <v>155</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D122" s="2">
+        <v>46042.361489097799</v>
+      </c>
+      <c r="E122" t="s">
+        <v>130</v>
+      </c>
+      <c r="F122">
+        <v>64</v>
+      </c>
+      <c r="G122" t="s">
+        <v>141</v>
+      </c>
+      <c r="H122" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>2</v>
+      </c>
+      <c r="B123" t="s">
+        <v>156</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D123" s="2">
+        <v>46042.361928238002</v>
+      </c>
+      <c r="E123" t="s">
+        <v>127</v>
+      </c>
+      <c r="F123">
+        <v>90.5</v>
+      </c>
+      <c r="G123" t="s">
+        <v>141</v>
+      </c>
+      <c r="H123" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>156</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D124" s="2">
+        <v>46042.362212514498</v>
+      </c>
+      <c r="E124" t="s">
+        <v>127</v>
+      </c>
+      <c r="F124">
+        <v>93</v>
+      </c>
+      <c r="G124" t="s">
+        <v>141</v>
+      </c>
+      <c r="H124" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>2</v>
+      </c>
+      <c r="B125" t="s">
+        <v>156</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D125" s="2">
+        <v>46042.362270635203</v>
+      </c>
+      <c r="E125" t="s">
+        <v>127</v>
+      </c>
+      <c r="F125">
+        <v>91.5</v>
+      </c>
+      <c r="G125" t="s">
+        <v>141</v>
+      </c>
+      <c r="H125" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>156</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D126" s="2">
+        <v>46042.362343741297</v>
+      </c>
+      <c r="E126" t="s">
+        <v>130</v>
+      </c>
+      <c r="F126">
+        <v>99.5</v>
+      </c>
+      <c r="G126" t="s">
+        <v>141</v>
+      </c>
+      <c r="H126" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>156</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D127" s="2">
+        <v>46042.362396041899</v>
+      </c>
+      <c r="E127" t="s">
+        <v>130</v>
+      </c>
+      <c r="F127">
+        <v>100.5</v>
+      </c>
+      <c r="G127" t="s">
+        <v>141</v>
+      </c>
+      <c r="H127" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>156</v>
+      </c>
+      <c r="C128" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D128" s="2">
+        <v>46042.362431900103</v>
+      </c>
+      <c r="E128" t="s">
+        <v>130</v>
+      </c>
+      <c r="F128">
+        <v>101</v>
+      </c>
+      <c r="G128" t="s">
+        <v>141</v>
+      </c>
+      <c r="H128" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>157</v>
+      </c>
+      <c r="C129" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D129" s="2">
+        <v>46042.362576904197</v>
+      </c>
+      <c r="E129" t="s">
+        <v>127</v>
+      </c>
+      <c r="F129">
+        <v>79</v>
+      </c>
+      <c r="G129" t="s">
+        <v>141</v>
+      </c>
+      <c r="H129" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>2</v>
+      </c>
+      <c r="B130" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D130" s="2">
+        <v>46042.3626157908</v>
+      </c>
+      <c r="E130" t="s">
+        <v>127</v>
+      </c>
+      <c r="F130">
+        <v>82.5</v>
+      </c>
+      <c r="G130" t="s">
+        <v>141</v>
+      </c>
+      <c r="H130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>2</v>
+      </c>
+      <c r="B131" t="s">
+        <v>157</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D131" s="2">
+        <v>46042.362653184799</v>
+      </c>
+      <c r="E131" t="s">
+        <v>127</v>
+      </c>
+      <c r="F131">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s">
+        <v>141</v>
+      </c>
+      <c r="H131" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>2</v>
+      </c>
+      <c r="B132" t="s">
+        <v>157</v>
+      </c>
+      <c r="C132" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D132" s="2">
+        <v>46042.362854254898</v>
+      </c>
+      <c r="E132" t="s">
+        <v>130</v>
+      </c>
+      <c r="F132">
+        <v>89.5</v>
+      </c>
+      <c r="G132" t="s">
+        <v>141</v>
+      </c>
+      <c r="H132" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>2</v>
+      </c>
+      <c r="B133" t="s">
+        <v>157</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D133" s="2">
+        <v>46042.362889967699</v>
+      </c>
+      <c r="E133" t="s">
+        <v>130</v>
+      </c>
+      <c r="F133">
+        <v>92</v>
+      </c>
+      <c r="G133" t="s">
+        <v>141</v>
+      </c>
+      <c r="H133" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>2</v>
+      </c>
+      <c r="B134" t="s">
+        <v>157</v>
+      </c>
+      <c r="C134" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D134" s="2">
+        <v>46042.362965286797</v>
+      </c>
+      <c r="E134" t="s">
+        <v>130</v>
+      </c>
+      <c r="F134">
+        <v>91.5</v>
+      </c>
+      <c r="G134" t="s">
+        <v>141</v>
+      </c>
+      <c r="H134" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3787,14 +4337,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3817,877 +4367,923 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>6.5</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>56</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>58</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>6.5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>60</v>
       </c>
       <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>8.5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>62</v>
       </c>
       <c r="B11" t="s">
         <v>63</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>8</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>64</v>
       </c>
       <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>8</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>72</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>7</v>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>7</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>8.5</v>
       </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
         <v>3</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>80</v>
       </c>
       <c r="B19" t="s">
         <v>81</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>9</v>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
         <v>3</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20" t="s">
         <v>83</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>7.5</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>3</v>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
         <v>4</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>8.5</v>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>87</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>7.5</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>6.5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
         <v>3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>91</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>7.5</v>
       </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>7</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>95</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>9</v>
       </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>8</v>
       </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>8</v>
       </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>103</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>8.5</v>
       </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>7.5</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="G31" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>7.5</v>
       </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
         <v>3</v>
       </c>
-      <c r="G32" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>7</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>3</v>
       </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>111</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>7</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>4</v>
       </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>113</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>7</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>3</v>
       </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
         <v>3</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>3</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>124</v>
       </c>
       <c r="B36" t="s">
         <v>125</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>8</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>3</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>3</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>143</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>6.5</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>144</v>
       </c>
       <c r="B38" t="s">
         <v>145</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>7.5</v>
       </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
         <v>4</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>3</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>146</v>
       </c>
       <c r="B39" t="s">
         <v>147</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>6</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>4</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40">
+        <v>7.5</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
         <v>2</v>
       </c>
     </row>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3C96CC80BAAC2631FFEDC1AFD891A03B6D085004" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FF6090A-D48B-6D4D-9BE8-A4AC728480F3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase_data" sheetId="1" r:id="rId1"/>
-    <sheet name="daily" sheetId="2" r:id="rId2"/>
+    <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t>Phase</t>
   </si>
@@ -410,7 +403,7 @@
     <t>degrees</t>
   </si>
   <si>
-    <t/>
+    <t>NA</t>
   </si>
   <si>
     <t>Right</t>
@@ -495,16 +488,62 @@
   </si>
   <si>
     <t>Y-Balance (Postero-Lateral)</t>
+  </si>
+  <si>
+    <t>2026-01-21 14:49:46</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-23 10:42:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reps</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Calf Raises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Rise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ankle Dorsiflexion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Balance (Eyes Closed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seconds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -516,7 +555,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -539,10 +577,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -838,15 +877,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H134"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="39.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -872,23 +911,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="2" t="n">
         <v>45947.704595950803</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="s">
@@ -898,23 +937,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>45947.704659476702</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="s">
@@ -924,23 +963,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="2" t="n">
         <v>45947.704952933702</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="s">
@@ -950,23 +989,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" t="n">
         <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="2" t="n">
         <v>45947.705045544899</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>130</v>
       </c>
       <c r="G5" t="s">
@@ -976,23 +1015,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" t="n">
         <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>45947.705211323802</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="s">
@@ -1002,23 +1041,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" t="n">
         <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="2" t="n">
         <v>45947.705280315502</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" t="s">
@@ -1028,23 +1067,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>0</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="2" t="n">
         <v>45948.664888072301</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="s">
@@ -1054,23 +1093,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="2" t="n">
         <v>45948.664965998003</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="s">
@@ -1080,23 +1119,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" t="n">
         <v>0</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="2" t="n">
         <v>45948.665130714297</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>105</v>
       </c>
       <c r="G10" t="s">
@@ -1106,23 +1145,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" t="n">
         <v>0</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="n">
         <v>45948.665214019697</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>128</v>
       </c>
       <c r="G11" t="s">
@@ -1132,23 +1171,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" t="n">
         <v>0</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="n">
         <v>45948.665349680203</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="s">
@@ -1158,23 +1197,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" t="n">
         <v>0</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="2" t="n">
         <v>45948.665392863797</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="s">
@@ -1184,23 +1223,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="14">
+      <c r="A14" t="n">
         <v>0</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="2" t="n">
         <v>45948.666299291603</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>45</v>
       </c>
       <c r="G14" t="s">
@@ -1210,23 +1249,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" t="n">
         <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="2" t="n">
         <v>45948.666350146101</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="s">
@@ -1236,23 +1275,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="16">
+      <c r="A16" t="n">
         <v>0</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="2" t="n">
         <v>45950.435864299601</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="s">
@@ -1262,23 +1301,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="17">
+      <c r="A17" t="n">
         <v>0</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="2" t="n">
         <v>45950.435907915002</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="s">
@@ -1288,23 +1327,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="18">
+      <c r="A18" t="n">
         <v>0</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="2" t="n">
         <v>45950.436296253101</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="s">
@@ -1314,23 +1353,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="19">
+      <c r="A19" t="n">
         <v>0</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="2" t="n">
         <v>45950.436443767503</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>118</v>
       </c>
       <c r="G19" t="s">
@@ -1340,23 +1379,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="20">
+      <c r="A20" t="n">
         <v>0</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="2" t="n">
         <v>45950.436589819903</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>47</v>
       </c>
       <c r="G20" t="s">
@@ -1366,23 +1405,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21">
+    <row r="21">
+      <c r="A21" t="n">
         <v>0</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="2" t="n">
         <v>45950.436639752603</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>59</v>
       </c>
       <c r="G21" t="s">
@@ -1392,23 +1431,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22">
+    <row r="22">
+      <c r="A22" t="n">
         <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="2" t="n">
         <v>45958.6841577331</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="s">
@@ -1418,23 +1457,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23">
+    <row r="23">
+      <c r="A23" t="n">
         <v>0</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="2" t="n">
         <v>45958.684209632003</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="s">
@@ -1444,23 +1483,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24">
+    <row r="24">
+      <c r="A24" t="n">
         <v>0</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="2" t="n">
         <v>45958.684322089699</v>
       </c>
       <c r="E24" t="s">
         <v>44</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>121</v>
       </c>
       <c r="G24" t="s">
@@ -1470,23 +1509,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25">
+    <row r="25">
+      <c r="A25" t="n">
         <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="2" t="n">
         <v>45958.684389989503</v>
       </c>
       <c r="E25" t="s">
         <v>47</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>130</v>
       </c>
       <c r="G25" t="s">
@@ -1496,23 +1535,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26">
+    <row r="26">
+      <c r="A26" t="n">
         <v>0</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="2" t="n">
         <v>45958.684524802797</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="s">
@@ -1522,23 +1561,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27">
+    <row r="27">
+      <c r="A27" t="n">
         <v>0</v>
       </c>
       <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="2" t="n">
         <v>45958.684905007998</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>59</v>
       </c>
       <c r="G27" t="s">
@@ -1548,23 +1587,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="28">
+      <c r="A28" t="n">
         <v>0</v>
       </c>
       <c r="B28" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="2" t="n">
         <v>45958.684968170899</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>48</v>
       </c>
       <c r="G28" t="s">
@@ -1574,23 +1613,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="29">
+      <c r="A29" t="n">
         <v>0</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="2" t="n">
         <v>45958.685067698403</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>95</v>
       </c>
       <c r="G29" t="s">
@@ -1600,23 +1639,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="30">
+      <c r="A30" t="n">
         <v>0</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="2" t="n">
         <v>45958.685166592397</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>64</v>
       </c>
       <c r="G30" t="s">
@@ -1626,23 +1665,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31">
+    <row r="31">
+      <c r="A31" t="n">
         <v>0</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="2" t="n">
         <v>45958.685324976199</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>93</v>
       </c>
       <c r="G31" t="s">
@@ -1652,23 +1691,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32">
+      <c r="A32" t="n">
         <v>0</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="2" t="n">
         <v>45958.685387673802</v>
       </c>
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>62</v>
       </c>
       <c r="G32" t="s">
@@ -1678,23 +1717,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33">
+    <row r="33">
+      <c r="A33" t="n">
         <v>0</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="2" t="n">
         <v>45959.385571423503</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="s">
@@ -1704,23 +1743,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="34">
+      <c r="A34" t="n">
         <v>0</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="2" t="n">
         <v>45959.385909921002</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="s">
@@ -1730,23 +1769,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="35">
+      <c r="A35" t="n">
         <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="2" t="n">
         <v>45960.491801712298</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="s">
@@ -1756,23 +1795,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="36">
+      <c r="A36" t="n">
         <v>0</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="2" t="n">
         <v>45960.491960884297</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>125</v>
       </c>
       <c r="G36" t="s">
@@ -1782,23 +1821,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="37">
+      <c r="A37" t="n">
         <v>0</v>
       </c>
       <c r="B37" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="2" t="n">
         <v>45960.492014117801</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>128</v>
       </c>
       <c r="G37" t="s">
@@ -1808,23 +1847,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="38">
+      <c r="A38" t="n">
         <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="2" t="n">
         <v>45960.492522578497</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>72</v>
       </c>
       <c r="G38" t="s">
@@ -1834,23 +1873,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39">
+    <row r="39">
+      <c r="A39" t="n">
         <v>0</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="2" t="n">
         <v>45960.4925716453</v>
       </c>
       <c r="E39" t="s">
         <v>47</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>92</v>
       </c>
       <c r="G39" t="s">
@@ -1860,23 +1899,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40">
+    <row r="40">
+      <c r="A40" t="n">
         <v>0</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="2" t="n">
         <v>45960.492643531601</v>
       </c>
       <c r="E40" t="s">
         <v>44</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>74</v>
       </c>
       <c r="G40" t="s">
@@ -1886,23 +1925,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41">
+    <row r="41">
+      <c r="A41" t="n">
         <v>0</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="2" t="n">
         <v>45960.492700254901</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>90</v>
       </c>
       <c r="G41" t="s">
@@ -1912,23 +1951,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42">
+    <row r="42">
+      <c r="A42" t="n">
         <v>0</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="2" t="n">
         <v>45965.485657138801</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="s">
@@ -1938,23 +1977,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43">
+    <row r="43">
+      <c r="A43" t="n">
         <v>0</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="2" t="n">
         <v>45965.485844846997</v>
       </c>
       <c r="E43" t="s">
         <v>44</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>80</v>
       </c>
       <c r="G43" t="s">
@@ -1964,23 +2003,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44">
+    <row r="44">
+      <c r="A44" t="n">
         <v>0</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="2" t="n">
         <v>45965.485890989898</v>
       </c>
       <c r="E44" t="s">
         <v>44</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>82</v>
       </c>
       <c r="G44" t="s">
@@ -1990,23 +2029,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45">
+    <row r="45">
+      <c r="A45" t="n">
         <v>0</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="2" t="n">
         <v>45965.485968485897</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="n">
         <v>87</v>
       </c>
       <c r="G45" t="s">
@@ -2016,23 +2055,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46">
+    <row r="46">
+      <c r="A46" t="n">
         <v>0</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="2" t="n">
         <v>45965.486001955702</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="n">
         <v>89</v>
       </c>
       <c r="G46" t="s">
@@ -2042,23 +2081,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47">
+    <row r="47">
+      <c r="A47" t="n">
         <v>0</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="2" t="n">
         <v>45965.486250549002</v>
       </c>
       <c r="E47" t="s">
         <v>44</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="n">
         <v>50</v>
       </c>
       <c r="G47" t="s">
@@ -2068,23 +2107,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48">
+    <row r="48">
+      <c r="A48" t="n">
         <v>0</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="2" t="n">
         <v>45965.486292492598</v>
       </c>
       <c r="E48" t="s">
         <v>44</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="n">
         <v>52</v>
       </c>
       <c r="G48" t="s">
@@ -2094,23 +2133,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49">
+    <row r="49">
+      <c r="A49" t="n">
         <v>0</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="2" t="n">
         <v>45965.486377312402</v>
       </c>
       <c r="E49" t="s">
         <v>47</v>
       </c>
-      <c r="F49">
+      <c r="F49" t="n">
         <v>54</v>
       </c>
       <c r="G49" t="s">
@@ -2120,23 +2159,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50">
+    <row r="50">
+      <c r="A50" t="n">
         <v>0</v>
       </c>
       <c r="B50" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="2" t="n">
         <v>45965.486404639203</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
       </c>
-      <c r="F50">
+      <c r="F50" t="n">
         <v>56</v>
       </c>
       <c r="G50" t="s">
@@ -2146,23 +2185,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51">
+    <row r="51">
+      <c r="A51" t="n">
         <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="1" t="n">
         <v>45974</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="2" t="n">
         <v>45974.411367086701</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="n">
         <v>3</v>
       </c>
       <c r="G51" t="s">
@@ -2172,23 +2211,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52">
+    <row r="52">
+      <c r="A52" t="n">
         <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="1" t="n">
         <v>45974</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="2" t="n">
         <v>45974.411416700903</v>
       </c>
       <c r="E52" t="s">
         <v>47</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="s">
@@ -2198,23 +2237,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53">
+    <row r="53">
+      <c r="A53" t="n">
         <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="2" t="n">
         <v>45975.537941231603</v>
       </c>
       <c r="E53" t="s">
         <v>44</v>
       </c>
-      <c r="F53">
+      <c r="F53" t="n">
         <v>2</v>
       </c>
       <c r="G53" t="s">
@@ -2224,23 +2263,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54">
+    <row r="54">
+      <c r="A54" t="n">
         <v>1</v>
       </c>
       <c r="B54" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="2" t="n">
         <v>45975.538157998897</v>
       </c>
       <c r="E54" t="s">
         <v>47</v>
       </c>
-      <c r="F54">
+      <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="s">
@@ -2250,23 +2289,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55">
+    <row r="55">
+      <c r="A55" t="n">
         <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="2" t="n">
         <v>45975.544261836498</v>
       </c>
       <c r="E55" t="s">
         <v>44</v>
       </c>
-      <c r="F55">
+      <c r="F55" t="n">
         <v>5</v>
       </c>
       <c r="G55" t="s">
@@ -2276,23 +2315,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56">
+    <row r="56">
+      <c r="A56" t="n">
         <v>1</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="2" t="n">
         <v>45975.544303050097</v>
       </c>
       <c r="E56" t="s">
         <v>47</v>
       </c>
-      <c r="F56">
+      <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="s">
@@ -2302,23 +2341,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57">
+    <row r="57">
+      <c r="A57" t="n">
         <v>1</v>
       </c>
       <c r="B57" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="2" t="n">
         <v>45975.544539589202</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
       </c>
-      <c r="F57">
+      <c r="F57" t="n">
         <v>110</v>
       </c>
       <c r="G57" t="s">
@@ -2328,23 +2367,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58">
+    <row r="58">
+      <c r="A58" t="n">
         <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="2" t="n">
         <v>45975.544575668398</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="n">
         <v>125</v>
       </c>
       <c r="G58" t="s">
@@ -2354,23 +2393,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59">
+    <row r="59">
+      <c r="A59" t="n">
         <v>1</v>
       </c>
       <c r="B59" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="2" t="n">
         <v>45989.657419278097</v>
       </c>
       <c r="E59" t="s">
         <v>44</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="s">
@@ -2380,23 +2419,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60">
+    <row r="60">
+      <c r="A60" t="n">
         <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="2" t="n">
         <v>45989.657464727003</v>
       </c>
       <c r="E60" t="s">
         <v>47</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="s">
@@ -2406,23 +2445,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61">
+    <row r="61">
+      <c r="A61" t="n">
         <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="2" t="n">
         <v>45989.657658854201</v>
       </c>
       <c r="E61" t="s">
         <v>44</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="n">
         <v>2</v>
       </c>
       <c r="G61" t="s">
@@ -2432,23 +2471,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62">
+    <row r="62">
+      <c r="A62" t="n">
         <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="2" t="n">
         <v>45989.657725292898</v>
       </c>
       <c r="E62" t="s">
         <v>47</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="s">
@@ -2458,23 +2497,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63">
+    <row r="63">
+      <c r="A63" t="n">
         <v>1</v>
       </c>
       <c r="B63" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="2" t="n">
         <v>45989.657879157297</v>
       </c>
       <c r="E63" t="s">
         <v>44</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="n">
         <v>117</v>
       </c>
       <c r="G63" t="s">
@@ -2484,23 +2523,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64">
+    <row r="64">
+      <c r="A64" t="n">
         <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="2" t="n">
         <v>45989.657918513098</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="n">
         <v>126</v>
       </c>
       <c r="G64" t="s">
@@ -2510,23 +2549,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65">
+    <row r="65">
+      <c r="A65" t="n">
         <v>1</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="2" t="n">
         <v>45989.658742763997</v>
       </c>
       <c r="E65" t="s">
         <v>44</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="n">
         <v>2</v>
       </c>
       <c r="G65" t="s">
@@ -2536,23 +2575,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66">
+    <row r="66">
+      <c r="A66" t="n">
         <v>1</v>
       </c>
       <c r="B66" t="s">
         <v>114</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="2" t="n">
         <v>46030.597367625</v>
       </c>
       <c r="E66" t="s">
         <v>115</v>
       </c>
-      <c r="F66">
+      <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="s">
@@ -2562,23 +2601,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67">
+    <row r="67">
+      <c r="A67" t="n">
         <v>1</v>
       </c>
       <c r="B67" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="2" t="n">
         <v>46030.597429351699</v>
       </c>
       <c r="E67" t="s">
         <v>118</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="s">
@@ -2588,23 +2627,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68">
+    <row r="68">
+      <c r="A68" t="n">
         <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>119</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="2" t="n">
         <v>46030.597768818101</v>
       </c>
       <c r="E68" t="s">
         <v>115</v>
       </c>
-      <c r="F68">
+      <c r="F68" t="n">
         <v>120</v>
       </c>
       <c r="G68" t="s">
@@ -2614,23 +2653,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69">
+    <row r="69">
+      <c r="A69" t="n">
         <v>1</v>
       </c>
       <c r="B69" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="2" t="n">
         <v>46030.597819244598</v>
       </c>
       <c r="E69" t="s">
         <v>118</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="n">
         <v>125</v>
       </c>
       <c r="G69" t="s">
@@ -2640,23 +2679,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70">
+    <row r="70">
+      <c r="A70" t="n">
         <v>1</v>
       </c>
       <c r="B70" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="2" t="n">
         <v>46030.5981109887</v>
       </c>
       <c r="E70" t="s">
         <v>115</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="n">
         <v>2</v>
       </c>
       <c r="G70" t="s">
@@ -2666,23 +2705,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71">
+    <row r="71">
+      <c r="A71" t="n">
         <v>1</v>
       </c>
       <c r="B71" t="s">
         <v>121</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="2" t="n">
         <v>46030.598165269199</v>
       </c>
       <c r="E71" t="s">
         <v>118</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="s">
@@ -2692,23 +2731,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72">
+    <row r="72">
+      <c r="A72" t="n">
         <v>1</v>
       </c>
       <c r="B72" t="s">
         <v>122</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="2" t="n">
         <v>46030.5985355347</v>
       </c>
       <c r="E72" t="s">
         <v>115</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="s">
@@ -2718,23 +2757,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73">
+    <row r="73">
+      <c r="A73" t="n">
         <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="2" t="n">
         <v>46030.598729730598</v>
       </c>
       <c r="E73" t="s">
         <v>115</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="s">
@@ -2744,23 +2783,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74">
+    <row r="74">
+      <c r="A74" t="n">
         <v>1</v>
       </c>
       <c r="B74" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="2" t="n">
         <v>46030.598804364497</v>
       </c>
       <c r="E74" t="s">
         <v>118</v>
       </c>
-      <c r="F74">
+      <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="s">
@@ -2770,23 +2809,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75">
+    <row r="75">
+      <c r="A75" t="n">
         <v>1</v>
       </c>
       <c r="B75" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="2" t="n">
         <v>46030.598952235603</v>
       </c>
       <c r="E75" t="s">
         <v>115</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="n">
         <v>122</v>
       </c>
       <c r="G75" t="s">
@@ -2796,23 +2835,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76">
+    <row r="76">
+      <c r="A76" t="n">
         <v>1</v>
       </c>
       <c r="B76" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="2" t="n">
         <v>46030.5989977875</v>
       </c>
       <c r="E76" t="s">
         <v>118</v>
       </c>
-      <c r="F76">
+      <c r="F76" t="n">
         <v>127</v>
       </c>
       <c r="G76" t="s">
@@ -2822,23 +2861,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77">
+    <row r="77">
+      <c r="A77" t="n">
         <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>121</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="2" t="n">
         <v>46030.5991297031</v>
       </c>
       <c r="E77" t="s">
         <v>115</v>
       </c>
-      <c r="F77">
+      <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="s">
@@ -2848,23 +2887,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78">
+    <row r="78">
+      <c r="A78" t="n">
         <v>1</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="2" t="n">
         <v>46030.599185763604</v>
       </c>
       <c r="E78" t="s">
         <v>118</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="s">
@@ -2874,23 +2913,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79">
+    <row r="79">
+      <c r="A79" t="n">
         <v>1</v>
       </c>
       <c r="B79" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="2" t="n">
         <v>46030.599461440201</v>
       </c>
       <c r="E79" t="s">
         <v>118</v>
       </c>
-      <c r="F79">
+      <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="s">
@@ -2900,23 +2939,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80">
+    <row r="80">
+      <c r="A80" t="n">
         <v>1</v>
       </c>
       <c r="B80" t="s">
         <v>122</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="2" t="n">
         <v>46030.6009521206</v>
       </c>
       <c r="E80" t="s">
         <v>115</v>
       </c>
-      <c r="F80">
+      <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="s">
@@ -2926,23 +2965,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81">
+    <row r="81">
+      <c r="A81" t="n">
         <v>1</v>
       </c>
       <c r="B81" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="2" t="n">
         <v>46030.601362099602</v>
       </c>
       <c r="E81" t="s">
         <v>115</v>
       </c>
-      <c r="F81">
+      <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="s">
@@ -2952,23 +2991,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82">
+    <row r="82">
+      <c r="A82" t="n">
         <v>1</v>
       </c>
       <c r="B82" t="s">
         <v>114</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="2" t="n">
         <v>46030.601397267797</v>
       </c>
       <c r="E82" t="s">
         <v>118</v>
       </c>
-      <c r="F82">
+      <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="s">
@@ -2978,23 +3017,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83">
+    <row r="83">
+      <c r="A83" t="n">
         <v>1</v>
       </c>
       <c r="B83" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="2" t="n">
         <v>46030.601664699498</v>
       </c>
       <c r="E83" t="s">
         <v>115</v>
       </c>
-      <c r="F83">
+      <c r="F83" t="n">
         <v>124</v>
       </c>
       <c r="G83" t="s">
@@ -3004,23 +3043,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84">
+    <row r="84">
+      <c r="A84" t="n">
         <v>1</v>
       </c>
       <c r="B84" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="2" t="n">
         <v>46030.601707849899</v>
       </c>
       <c r="E84" t="s">
         <v>118</v>
       </c>
-      <c r="F84">
+      <c r="F84" t="n">
         <v>125</v>
       </c>
       <c r="G84" t="s">
@@ -3030,23 +3069,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85">
+    <row r="85">
+      <c r="A85" t="n">
         <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>121</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="2" t="n">
         <v>46030.601880503098</v>
       </c>
       <c r="E85" t="s">
         <v>115</v>
       </c>
-      <c r="F85">
+      <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="s">
@@ -3056,23 +3095,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86">
+    <row r="86">
+      <c r="A86" t="n">
         <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>121</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="2" t="n">
         <v>46030.601922228001</v>
       </c>
       <c r="E86" t="s">
         <v>118</v>
       </c>
-      <c r="F86">
+      <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="s">
@@ -3082,23 +3121,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87">
+    <row r="87">
+      <c r="A87" t="n">
         <v>1</v>
       </c>
       <c r="B87" t="s">
         <v>122</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="2" t="n">
         <v>46030.602015028402</v>
       </c>
       <c r="E87" t="s">
         <v>115</v>
       </c>
-      <c r="F87">
+      <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="s">
@@ -3108,23 +3147,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88">
+    <row r="88">
+      <c r="A88" t="n">
         <v>1</v>
       </c>
       <c r="B88" t="s">
         <v>114</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="2" t="n">
         <v>46030.602325239699</v>
       </c>
       <c r="E88" t="s">
         <v>115</v>
       </c>
-      <c r="F88">
+      <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="s">
@@ -3134,23 +3173,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89">
+    <row r="89">
+      <c r="A89" t="n">
         <v>1</v>
       </c>
       <c r="B89" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="2" t="n">
         <v>46030.602364462902</v>
       </c>
       <c r="E89" t="s">
         <v>118</v>
       </c>
-      <c r="F89">
+      <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="s">
@@ -3160,23 +3199,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90">
+    <row r="90">
+      <c r="A90" t="n">
         <v>1</v>
       </c>
       <c r="B90" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="2" t="n">
         <v>46030.602432747299</v>
       </c>
       <c r="E90" t="s">
         <v>115</v>
       </c>
-      <c r="F90">
+      <c r="F90" t="n">
         <v>125</v>
       </c>
       <c r="G90" t="s">
@@ -3186,23 +3225,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91">
+    <row r="91">
+      <c r="A91" t="n">
         <v>1</v>
       </c>
       <c r="B91" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C91" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="2" t="n">
         <v>46030.602474245497</v>
       </c>
       <c r="E91" t="s">
         <v>118</v>
       </c>
-      <c r="F91">
+      <c r="F91" t="n">
         <v>125</v>
       </c>
       <c r="G91" t="s">
@@ -3212,23 +3251,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92">
+    <row r="92">
+      <c r="A92" t="n">
         <v>1</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="2" t="n">
         <v>46030.602583176304</v>
       </c>
       <c r="E92" t="s">
         <v>115</v>
       </c>
-      <c r="F92">
+      <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="s">
@@ -3238,23 +3277,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93">
+    <row r="93">
+      <c r="A93" t="n">
         <v>1</v>
       </c>
       <c r="B93" t="s">
         <v>121</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="2" t="n">
         <v>46030.602620265403</v>
       </c>
       <c r="E93" t="s">
         <v>118</v>
       </c>
-      <c r="F93">
+      <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="s">
@@ -3264,23 +3303,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94">
+    <row r="94">
+      <c r="A94" t="n">
         <v>1</v>
       </c>
       <c r="B94" t="s">
         <v>122</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="2" t="n">
         <v>46030.602707964201</v>
       </c>
       <c r="E94" t="s">
         <v>115</v>
       </c>
-      <c r="F94">
+      <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="s">
@@ -3290,23 +3329,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95">
+    <row r="95">
+      <c r="A95" t="n">
         <v>2</v>
       </c>
       <c r="B95" t="s">
         <v>126</v>
       </c>
-      <c r="C95" s="1">
+      <c r="C95" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="2" t="n">
         <v>46034.442400281303</v>
       </c>
       <c r="E95" t="s">
         <v>127</v>
       </c>
-      <c r="F95">
+      <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="s">
@@ -3316,23 +3355,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96">
+    <row r="96">
+      <c r="A96" t="n">
         <v>2</v>
       </c>
       <c r="B96" t="s">
         <v>126</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="2" t="n">
         <v>46034.442454999</v>
       </c>
       <c r="E96" t="s">
         <v>130</v>
       </c>
-      <c r="F96">
+      <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="s">
@@ -3342,23 +3381,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97">
+    <row r="97">
+      <c r="A97" t="n">
         <v>2</v>
       </c>
       <c r="B97" t="s">
         <v>131</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="2" t="n">
         <v>46034.442543972596</v>
       </c>
       <c r="E97" t="s">
         <v>127</v>
       </c>
-      <c r="F97">
+      <c r="F97" t="n">
         <v>126</v>
       </c>
       <c r="G97" t="s">
@@ -3368,23 +3407,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98">
+    <row r="98">
+      <c r="A98" t="n">
         <v>2</v>
       </c>
       <c r="B98" t="s">
         <v>131</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="2" t="n">
         <v>46034.442594817498</v>
       </c>
       <c r="E98" t="s">
         <v>130</v>
       </c>
-      <c r="F98">
+      <c r="F98" t="n">
         <v>126</v>
       </c>
       <c r="G98" t="s">
@@ -3394,23 +3433,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99">
+    <row r="99">
+      <c r="A99" t="n">
         <v>2</v>
       </c>
       <c r="B99" t="s">
         <v>132</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="2" t="n">
         <v>46034.4427237583</v>
       </c>
       <c r="E99" t="s">
         <v>127</v>
       </c>
-      <c r="F99">
+      <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="s">
@@ -3420,23 +3459,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100">
+    <row r="100">
+      <c r="A100" t="n">
         <v>2</v>
       </c>
       <c r="B100" t="s">
         <v>134</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="2" t="n">
         <v>46034.442922526003</v>
       </c>
       <c r="E100" t="s">
         <v>127</v>
       </c>
-      <c r="F100">
+      <c r="F100" t="n">
         <v>7</v>
       </c>
       <c r="G100" t="s">
@@ -3446,23 +3485,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101">
+    <row r="101">
+      <c r="A101" t="n">
         <v>2</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C101" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="2" t="n">
         <v>46034.442973844598</v>
       </c>
       <c r="E101" t="s">
         <v>130</v>
       </c>
-      <c r="F101">
+      <c r="F101" t="n">
         <v>15</v>
       </c>
       <c r="G101" t="s">
@@ -3472,23 +3511,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" t="n">
         <v>2</v>
       </c>
       <c r="B102" t="s">
         <v>136</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="2" t="n">
         <v>46034.443637573902</v>
       </c>
       <c r="E102" t="s">
         <v>127</v>
       </c>
-      <c r="F102">
+      <c r="F102" t="n">
         <v>5</v>
       </c>
       <c r="G102" t="s">
@@ -3498,23 +3537,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103">
+    <row r="103">
+      <c r="A103" t="n">
         <v>2</v>
       </c>
       <c r="B103" t="s">
         <v>136</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C103" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="2" t="n">
         <v>46034.443697991803</v>
       </c>
       <c r="E103" t="s">
         <v>130</v>
       </c>
-      <c r="F103">
+      <c r="F103" t="n">
         <v>13</v>
       </c>
       <c r="G103" t="s">
@@ -3524,23 +3563,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104">
+    <row r="104">
+      <c r="A104" t="n">
         <v>2</v>
       </c>
       <c r="B104" t="s">
         <v>137</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="2" t="n">
         <v>46034.539288706503</v>
       </c>
       <c r="E104" t="s">
         <v>138</v>
       </c>
-      <c r="F104">
+      <c r="F104" t="n">
         <v>40</v>
       </c>
       <c r="G104" t="s">
@@ -3550,23 +3589,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105">
+    <row r="105">
+      <c r="A105" t="n">
         <v>2</v>
       </c>
       <c r="B105" t="s">
         <v>140</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C105" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="2" t="n">
         <v>46034.5661824204</v>
       </c>
       <c r="E105" t="s">
         <v>127</v>
       </c>
-      <c r="F105">
+      <c r="F105" t="n">
         <v>6</v>
       </c>
       <c r="G105" t="s">
@@ -3576,23 +3615,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106">
+    <row r="106">
+      <c r="A106" t="n">
         <v>2</v>
       </c>
       <c r="B106" t="s">
         <v>140</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="2" t="n">
         <v>46034.566247390401</v>
       </c>
       <c r="E106" t="s">
         <v>130</v>
       </c>
-      <c r="F106">
+      <c r="F106" t="n">
         <v>15</v>
       </c>
       <c r="G106" t="s">
@@ -3602,23 +3641,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107">
+    <row r="107">
+      <c r="A107" t="n">
         <v>2</v>
       </c>
       <c r="B107" t="s">
         <v>134</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="2" t="n">
         <v>46038.6692860279</v>
       </c>
       <c r="E107" t="s">
         <v>127</v>
       </c>
-      <c r="F107">
+      <c r="F107" t="n">
         <v>9</v>
       </c>
       <c r="G107" t="s">
@@ -3628,23 +3667,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108">
+    <row r="108">
+      <c r="A108" t="n">
         <v>2</v>
       </c>
       <c r="B108" t="s">
         <v>134</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C108" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="2" t="n">
         <v>46038.669370621101</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
       </c>
-      <c r="F108">
+      <c r="F108" t="n">
         <v>17</v>
       </c>
       <c r="G108" t="s">
@@ -3654,23 +3693,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109">
+    <row r="109">
+      <c r="A109" t="n">
         <v>2</v>
       </c>
       <c r="B109" t="s">
         <v>136</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C109" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="2" t="n">
         <v>46038.669554267297</v>
       </c>
       <c r="E109" t="s">
         <v>127</v>
       </c>
-      <c r="F109">
+      <c r="F109" t="n">
         <v>7</v>
       </c>
       <c r="G109" t="s">
@@ -3680,23 +3719,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110">
+    <row r="110">
+      <c r="A110" t="n">
         <v>2</v>
       </c>
       <c r="B110" t="s">
         <v>136</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="2" t="n">
         <v>46038.669627650503</v>
       </c>
       <c r="E110" t="s">
         <v>130</v>
       </c>
-      <c r="F110">
+      <c r="F110" t="n">
         <v>14</v>
       </c>
       <c r="G110" t="s">
@@ -3706,23 +3745,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111">
+    <row r="111">
+      <c r="A111" t="n">
         <v>2</v>
       </c>
       <c r="B111" t="s">
         <v>140</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="2" t="n">
         <v>46038.6698742878</v>
       </c>
       <c r="E111" t="s">
         <v>127</v>
       </c>
-      <c r="F111">
+      <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="s">
@@ -3732,23 +3771,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112">
+    <row r="112">
+      <c r="A112" t="n">
         <v>2</v>
       </c>
       <c r="B112" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="2" t="n">
         <v>46038.669928152704</v>
       </c>
       <c r="E112" t="s">
         <v>130</v>
       </c>
-      <c r="F112">
+      <c r="F112" t="n">
         <v>15</v>
       </c>
       <c r="G112" t="s">
@@ -3758,23 +3797,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113">
+    <row r="113">
+      <c r="A113" t="n">
         <v>2</v>
       </c>
       <c r="B113" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C113" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="2" t="n">
         <v>46038.6707992843</v>
       </c>
       <c r="E113" t="s">
         <v>127</v>
       </c>
-      <c r="F113">
+      <c r="F113" t="n">
         <v>30</v>
       </c>
       <c r="G113" t="s">
@@ -3784,23 +3823,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114">
+    <row r="114">
+      <c r="A114" t="n">
         <v>2</v>
       </c>
       <c r="B114" t="s">
         <v>148</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="2" t="n">
         <v>46038.670836973499</v>
       </c>
       <c r="E114" t="s">
         <v>130</v>
       </c>
-      <c r="F114">
+      <c r="F114" t="n">
         <v>30</v>
       </c>
       <c r="G114" t="s">
@@ -3810,23 +3849,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115">
+    <row r="115">
+      <c r="A115" t="n">
         <v>2</v>
       </c>
       <c r="B115" t="s">
         <v>154</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="2" t="n">
         <v>46042.360163172401</v>
       </c>
       <c r="E115" t="s">
         <v>127</v>
       </c>
-      <c r="F115">
+      <c r="F115" t="n">
         <v>30</v>
       </c>
       <c r="G115" t="s">
@@ -3836,23 +3875,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116">
+    <row r="116">
+      <c r="A116" t="n">
         <v>2</v>
       </c>
       <c r="B116" t="s">
         <v>154</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="2" t="n">
         <v>46042.360217777801</v>
       </c>
       <c r="E116" t="s">
         <v>130</v>
       </c>
-      <c r="F116">
+      <c r="F116" t="n">
         <v>45</v>
       </c>
       <c r="G116" t="s">
@@ -3862,24 +3901,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117">
+    <row r="117">
+      <c r="A117" t="n">
         <v>2</v>
       </c>
       <c r="B117" t="s">
         <v>155</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="2" t="n">
         <v>46042.361174106802</v>
       </c>
       <c r="E117" t="s">
         <v>127</v>
       </c>
-      <c r="F117">
-        <v>50</v>
+      <c r="F117" t="n">
+        <v>40</v>
       </c>
       <c r="G117" t="s">
         <v>141</v>
@@ -3888,24 +3927,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118">
+    <row r="118">
+      <c r="A118" t="n">
         <v>2</v>
       </c>
       <c r="B118" t="s">
         <v>155</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="2" t="n">
         <v>46042.361259715202</v>
       </c>
       <c r="E118" t="s">
         <v>127</v>
       </c>
-      <c r="F118">
-        <v>52</v>
+      <c r="F118" t="n">
+        <v>38</v>
       </c>
       <c r="G118" t="s">
         <v>141</v>
@@ -3914,24 +3953,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119">
+    <row r="119">
+      <c r="A119" t="n">
         <v>2</v>
       </c>
       <c r="B119" t="s">
         <v>155</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="2" t="n">
         <v>46042.361303134297</v>
       </c>
       <c r="E119" t="s">
         <v>127</v>
       </c>
-      <c r="F119">
-        <v>53</v>
+      <c r="F119" t="n">
+        <v>38</v>
       </c>
       <c r="G119" t="s">
         <v>141</v>
@@ -3940,23 +3979,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120">
+    <row r="120">
+      <c r="A120" t="n">
         <v>2</v>
       </c>
       <c r="B120" t="s">
         <v>155</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C120" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="2" t="n">
         <v>46042.361404144598</v>
       </c>
       <c r="E120" t="s">
         <v>130</v>
       </c>
-      <c r="F120">
+      <c r="F120" t="n">
         <v>60</v>
       </c>
       <c r="G120" t="s">
@@ -3966,23 +4005,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121">
+    <row r="121">
+      <c r="A121" t="n">
         <v>2</v>
       </c>
       <c r="B121" t="s">
         <v>155</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C121" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="2" t="n">
         <v>46042.361443357302</v>
       </c>
       <c r="E121" t="s">
         <v>130</v>
       </c>
-      <c r="F121">
+      <c r="F121" t="n">
         <v>61</v>
       </c>
       <c r="G121" t="s">
@@ -3992,23 +4031,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122">
+    <row r="122">
+      <c r="A122" t="n">
         <v>2</v>
       </c>
       <c r="B122" t="s">
         <v>155</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C122" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="2" t="n">
         <v>46042.361489097799</v>
       </c>
       <c r="E122" t="s">
         <v>130</v>
       </c>
-      <c r="F122">
+      <c r="F122" t="n">
         <v>64</v>
       </c>
       <c r="G122" t="s">
@@ -4018,24 +4057,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123">
+    <row r="123">
+      <c r="A123" t="n">
         <v>2</v>
       </c>
       <c r="B123" t="s">
         <v>156</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C123" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="2" t="n">
         <v>46042.361928238002</v>
       </c>
       <c r="E123" t="s">
         <v>127</v>
       </c>
-      <c r="F123">
-        <v>90.5</v>
+      <c r="F123" t="n">
+        <v>80</v>
       </c>
       <c r="G123" t="s">
         <v>141</v>
@@ -4044,24 +4083,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124">
+    <row r="124">
+      <c r="A124" t="n">
         <v>2</v>
       </c>
       <c r="B124" t="s">
         <v>156</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C124" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="2" t="n">
         <v>46042.362212514498</v>
       </c>
       <c r="E124" t="s">
         <v>127</v>
       </c>
-      <c r="F124">
-        <v>93</v>
+      <c r="F124" t="n">
+        <v>78.5</v>
       </c>
       <c r="G124" t="s">
         <v>141</v>
@@ -4070,24 +4109,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125">
+    <row r="125">
+      <c r="A125" t="n">
         <v>2</v>
       </c>
       <c r="B125" t="s">
         <v>156</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C125" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="2" t="n">
         <v>46042.362270635203</v>
       </c>
       <c r="E125" t="s">
         <v>127</v>
       </c>
-      <c r="F125">
-        <v>91.5</v>
+      <c r="F125" t="n">
+        <v>81.5</v>
       </c>
       <c r="G125" t="s">
         <v>141</v>
@@ -4096,23 +4135,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126">
+    <row r="126">
+      <c r="A126" t="n">
         <v>2</v>
       </c>
       <c r="B126" t="s">
         <v>156</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="2" t="n">
         <v>46042.362343741297</v>
       </c>
       <c r="E126" t="s">
         <v>130</v>
       </c>
-      <c r="F126">
+      <c r="F126" t="n">
         <v>99.5</v>
       </c>
       <c r="G126" t="s">
@@ -4122,23 +4161,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127">
+    <row r="127">
+      <c r="A127" t="n">
         <v>2</v>
       </c>
       <c r="B127" t="s">
         <v>156</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="2" t="n">
         <v>46042.362396041899</v>
       </c>
       <c r="E127" t="s">
         <v>130</v>
       </c>
-      <c r="F127">
+      <c r="F127" t="n">
         <v>100.5</v>
       </c>
       <c r="G127" t="s">
@@ -4148,23 +4187,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128">
+    <row r="128">
+      <c r="A128" t="n">
         <v>2</v>
       </c>
       <c r="B128" t="s">
         <v>156</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="2" t="n">
         <v>46042.362431900103</v>
       </c>
       <c r="E128" t="s">
         <v>130</v>
       </c>
-      <c r="F128">
+      <c r="F128" t="n">
         <v>101</v>
       </c>
       <c r="G128" t="s">
@@ -4174,24 +4213,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129">
+    <row r="129">
+      <c r="A129" t="n">
         <v>2</v>
       </c>
       <c r="B129" t="s">
         <v>157</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="2" t="n">
         <v>46042.362576904197</v>
       </c>
       <c r="E129" t="s">
         <v>127</v>
       </c>
-      <c r="F129">
-        <v>79</v>
+      <c r="F129" t="n">
+        <v>65</v>
       </c>
       <c r="G129" t="s">
         <v>141</v>
@@ -4200,24 +4239,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130">
+    <row r="130">
+      <c r="A130" t="n">
         <v>2</v>
       </c>
       <c r="B130" t="s">
         <v>157</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="2" t="n">
         <v>46042.3626157908</v>
       </c>
       <c r="E130" t="s">
         <v>127</v>
       </c>
-      <c r="F130">
-        <v>82.5</v>
+      <c r="F130" t="n">
+        <v>66.5</v>
       </c>
       <c r="G130" t="s">
         <v>141</v>
@@ -4226,24 +4265,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131">
+    <row r="131">
+      <c r="A131" t="n">
         <v>2</v>
       </c>
       <c r="B131" t="s">
         <v>157</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="2" t="n">
         <v>46042.362653184799</v>
       </c>
       <c r="E131" t="s">
         <v>127</v>
       </c>
-      <c r="F131">
-        <v>81</v>
+      <c r="F131" t="n">
+        <v>68.5</v>
       </c>
       <c r="G131" t="s">
         <v>141</v>
@@ -4252,23 +4291,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132">
+    <row r="132">
+      <c r="A132" t="n">
         <v>2</v>
       </c>
       <c r="B132" t="s">
         <v>157</v>
       </c>
-      <c r="C132" s="1">
+      <c r="C132" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="2" t="n">
         <v>46042.362854254898</v>
       </c>
       <c r="E132" t="s">
         <v>130</v>
       </c>
-      <c r="F132">
+      <c r="F132" t="n">
         <v>89.5</v>
       </c>
       <c r="G132" t="s">
@@ -4278,23 +4317,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133">
+    <row r="133">
+      <c r="A133" t="n">
         <v>2</v>
       </c>
       <c r="B133" t="s">
         <v>157</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C133" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="2" t="n">
         <v>46042.362889967699</v>
       </c>
       <c r="E133" t="s">
         <v>130</v>
       </c>
-      <c r="F133">
+      <c r="F133" t="n">
         <v>92</v>
       </c>
       <c r="G133" t="s">
@@ -4304,23 +4343,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134">
+    <row r="134">
+      <c r="A134" t="n">
         <v>2</v>
       </c>
       <c r="B134" t="s">
         <v>157</v>
       </c>
-      <c r="C134" s="1">
+      <c r="C134" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="2" t="n">
         <v>46042.362965286797</v>
       </c>
       <c r="E134" t="s">
         <v>130</v>
       </c>
-      <c r="F134">
+      <c r="F134" t="n">
         <v>91.5</v>
       </c>
       <c r="G134" t="s">
@@ -4328,6 +4367,266 @@
       </c>
       <c r="H134" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2</v>
+      </c>
+      <c r="B135" t="s">
+        <v>162</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>46045.4466951266</v>
+      </c>
+      <c r="E135" t="s">
+        <v>163</v>
+      </c>
+      <c r="F135" t="n">
+        <v>12</v>
+      </c>
+      <c r="G135" t="s">
+        <v>164</v>
+      </c>
+      <c r="H135" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2</v>
+      </c>
+      <c r="B136" t="s">
+        <v>162</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>46045.4467432926</v>
+      </c>
+      <c r="E136" t="s">
+        <v>166</v>
+      </c>
+      <c r="F136" t="n">
+        <v>19</v>
+      </c>
+      <c r="G136" t="s">
+        <v>164</v>
+      </c>
+      <c r="H136" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2</v>
+      </c>
+      <c r="B137" t="s">
+        <v>167</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>46045.4469611491</v>
+      </c>
+      <c r="E137" t="s">
+        <v>163</v>
+      </c>
+      <c r="F137" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" t="s">
+        <v>164</v>
+      </c>
+      <c r="H137" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2</v>
+      </c>
+      <c r="B138" t="s">
+        <v>167</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>46045.4469929935</v>
+      </c>
+      <c r="E138" t="s">
+        <v>166</v>
+      </c>
+      <c r="F138" t="n">
+        <v>15</v>
+      </c>
+      <c r="G138" t="s">
+        <v>164</v>
+      </c>
+      <c r="H138" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" t="s">
+        <v>168</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>46045.4472388466</v>
+      </c>
+      <c r="E139" t="s">
+        <v>163</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H139" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2</v>
+      </c>
+      <c r="B140" t="s">
+        <v>168</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>46045.4472716892</v>
+      </c>
+      <c r="E140" t="s">
+        <v>166</v>
+      </c>
+      <c r="F140" t="n">
+        <v>8</v>
+      </c>
+      <c r="G140" t="s">
+        <v>164</v>
+      </c>
+      <c r="H140" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" t="s">
+        <v>169</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>46045.4475711992</v>
+      </c>
+      <c r="E141" t="s">
+        <v>163</v>
+      </c>
+      <c r="F141" t="n">
+        <v>10</v>
+      </c>
+      <c r="G141" t="s">
+        <v>170</v>
+      </c>
+      <c r="H141" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2</v>
+      </c>
+      <c r="B142" t="s">
+        <v>169</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>46045.4476158369</v>
+      </c>
+      <c r="E142" t="s">
+        <v>166</v>
+      </c>
+      <c r="F142" t="n">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s">
+        <v>170</v>
+      </c>
+      <c r="H142" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2</v>
+      </c>
+      <c r="B143" t="s">
+        <v>171</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>46045.4481392084</v>
+      </c>
+      <c r="E143" t="s">
+        <v>163</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3</v>
+      </c>
+      <c r="G143" t="s">
+        <v>172</v>
+      </c>
+      <c r="H143" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>171</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>46045.4481779641</v>
+      </c>
+      <c r="E144" t="s">
+        <v>166</v>
+      </c>
+      <c r="F144" t="n">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>172</v>
+      </c>
+      <c r="H144" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4337,14 +4636,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4367,923 +4666,969 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>6.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>9</v>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>7.5</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>6.5</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>56</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>58</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>6.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>60</v>
       </c>
       <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>8.5</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>62</v>
       </c>
       <c r="B11" t="s">
         <v>63</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>64</v>
       </c>
       <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>7</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>72</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>8</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>7</v>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>7</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>8.5</v>
       </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>80</v>
       </c>
       <c r="B19" t="s">
         <v>81</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>9</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20" t="s">
         <v>83</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>7.5</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" t="s">
         <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>8.5</v>
       </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>87</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>7.5</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>6.5</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>3</v>
       </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23">
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24" t="s">
         <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>91</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>7.5</v>
       </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>7</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>4</v>
       </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>95</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>9</v>
       </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>9</v>
       </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
         <v>3</v>
       </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>8</v>
       </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
         <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>8</v>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>103</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>8.5</v>
       </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>2</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
         <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>7.5</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>3</v>
       </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="F31">
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>7.5</v>
       </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="F32">
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
         <v>3</v>
       </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>7</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>111</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>7</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>4</v>
       </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
         <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>113</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>7</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="F35">
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36" t="s">
         <v>124</v>
       </c>
       <c r="B36" t="s">
         <v>125</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>8</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>4</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>3</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37" t="s">
         <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>143</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>6.5</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>3</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>3</v>
       </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
         <v>144</v>
       </c>
       <c r="B38" t="s">
         <v>145</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="n">
         <v>7.5</v>
       </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38">
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>3</v>
       </c>
-      <c r="G38">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39" t="s">
         <v>146</v>
       </c>
       <c r="B39" t="s">
         <v>147</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="n">
         <v>6</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>4</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
         <v>150</v>
       </c>
       <c r="B40" t="s">
         <v>151</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="n">
         <v>7.5</v>
       </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40">
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
         <v>3</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>4</v>
       </c>
-      <c r="G40">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41" t="s">
         <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>153</v>
       </c>
-      <c r="C41">
+      <c r="C41" t="n">
         <v>5</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>3</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>4</v>
       </c>
-      <c r="G41">
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
         <v>2</v>
       </c>
     </row>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Phase</t>
   </si>
@@ -533,6 +533,24 @@
   </si>
   <si>
     <t xml:space="preserve">seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Hop Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-26 08:38:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-27 05:31:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-27</t>
   </si>
 </sst>
 </file>
@@ -4629,6 +4647,84 @@
         <v>165</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>3</v>
+      </c>
+      <c r="B145" t="s">
+        <v>173</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>46047.4198329487</v>
+      </c>
+      <c r="E145" t="s">
+        <v>163</v>
+      </c>
+      <c r="F145" t="n">
+        <v>50</v>
+      </c>
+      <c r="G145" t="s">
+        <v>170</v>
+      </c>
+      <c r="H145" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2</v>
+      </c>
+      <c r="B146" t="s">
+        <v>174</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>46047.4450652627</v>
+      </c>
+      <c r="E146" t="s">
+        <v>163</v>
+      </c>
+      <c r="F146" t="n">
+        <v>30</v>
+      </c>
+      <c r="G146" t="s">
+        <v>172</v>
+      </c>
+      <c r="H146" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" t="s">
+        <v>174</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>46047.4451068267</v>
+      </c>
+      <c r="E147" t="s">
+        <v>166</v>
+      </c>
+      <c r="F147" t="n">
+        <v>30</v>
+      </c>
+      <c r="G147" t="s">
+        <v>172</v>
+      </c>
+      <c r="H147" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5632,6 +5728,52 @@
         <v>2</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>Phase</t>
   </si>
@@ -551,6 +551,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-01-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Balance (Eyes Open)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-28 19:21:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-28</t>
   </si>
 </sst>
 </file>
@@ -4725,6 +4737,266 @@
         <v>165</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2</v>
+      </c>
+      <c r="B148" t="s">
+        <v>179</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>46049.2447859849</v>
+      </c>
+      <c r="E148" t="s">
+        <v>163</v>
+      </c>
+      <c r="F148" t="n">
+        <v>37</v>
+      </c>
+      <c r="G148" t="s">
+        <v>172</v>
+      </c>
+      <c r="H148" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>179</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>46049.2452408769</v>
+      </c>
+      <c r="E149" t="s">
+        <v>166</v>
+      </c>
+      <c r="F149" t="n">
+        <v>45</v>
+      </c>
+      <c r="G149" t="s">
+        <v>172</v>
+      </c>
+      <c r="H149" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>171</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>46049.2453695697</v>
+      </c>
+      <c r="E150" t="s">
+        <v>163</v>
+      </c>
+      <c r="F150" t="n">
+        <v>6</v>
+      </c>
+      <c r="G150" t="s">
+        <v>172</v>
+      </c>
+      <c r="H150" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2</v>
+      </c>
+      <c r="B151" t="s">
+        <v>171</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>46049.2454065638</v>
+      </c>
+      <c r="E151" t="s">
+        <v>166</v>
+      </c>
+      <c r="F151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G151" t="s">
+        <v>172</v>
+      </c>
+      <c r="H151" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2</v>
+      </c>
+      <c r="B152" t="s">
+        <v>180</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>46049.2458257244</v>
+      </c>
+      <c r="E152" t="s">
+        <v>163</v>
+      </c>
+      <c r="F152" t="n">
+        <v>42</v>
+      </c>
+      <c r="G152" t="s">
+        <v>170</v>
+      </c>
+      <c r="H152" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>180</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>46049.2458756964</v>
+      </c>
+      <c r="E153" t="s">
+        <v>163</v>
+      </c>
+      <c r="F153" t="n">
+        <v>43</v>
+      </c>
+      <c r="G153" t="s">
+        <v>170</v>
+      </c>
+      <c r="H153" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>180</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>46049.2459168743</v>
+      </c>
+      <c r="E154" t="s">
+        <v>163</v>
+      </c>
+      <c r="F154" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="G154" t="s">
+        <v>170</v>
+      </c>
+      <c r="H154" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2</v>
+      </c>
+      <c r="B155" t="s">
+        <v>180</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>46049.2460143919</v>
+      </c>
+      <c r="E155" t="s">
+        <v>166</v>
+      </c>
+      <c r="F155" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G155" t="s">
+        <v>170</v>
+      </c>
+      <c r="H155" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>180</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>46049.2460697722</v>
+      </c>
+      <c r="E156" t="s">
+        <v>166</v>
+      </c>
+      <c r="F156" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G156" t="s">
+        <v>170</v>
+      </c>
+      <c r="H156" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2</v>
+      </c>
+      <c r="B157" t="s">
+        <v>180</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>46049.2461241977</v>
+      </c>
+      <c r="E157" t="s">
+        <v>166</v>
+      </c>
+      <c r="F157" t="n">
+        <v>64</v>
+      </c>
+      <c r="G157" t="s">
+        <v>170</v>
+      </c>
+      <c r="H157" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5774,6 +6046,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t>Phase</t>
   </si>
@@ -563,6 +563,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-01-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-29 10:23:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-29</t>
   </si>
 </sst>
 </file>
@@ -6069,6 +6075,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t>Phase</t>
   </si>
@@ -563,6 +563,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-01-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-29 11:14:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-29</t>
   </si>
 </sst>
 </file>
@@ -6069,6 +6075,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -1,20 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_9C9E34505BA97CF0BA284CBCF432B33B6D082C3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6728692-3663-3441-AFA6-F6FAC16EBE12}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase_data" sheetId="1" r:id="rId1"/>
+    <sheet name="daily" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="196">
   <si>
     <t>Phase</t>
   </si>
@@ -496,90 +503,122 @@
     <t>2026-01-21</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-01-23 10:42:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reps</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Calf Raises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Rise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ankle Dorsiflexion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Balance (Eyes Closed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Hop Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-26 08:38:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-27 05:31:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Balance (Eyes Open)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Anterior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-28 19:21:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-29 11:14:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-01-29</t>
+    <t>2026-01-23 10:42:32</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>Single Leg Bridge</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>reps</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Single Leg Calf Raises</t>
+  </si>
+  <si>
+    <t>Single Leg Rise</t>
+  </si>
+  <si>
+    <t>Ankle Dorsiflexion</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>Single Leg Balance (Eyes Closed)</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>Single Leg Hop Test</t>
+  </si>
+  <si>
+    <t>Side Bridge</t>
+  </si>
+  <si>
+    <t>2026-01-26 08:38:29</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>2026-01-27 05:31:12</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>Single Leg Balance (Eyes Open)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t>2026-01-28 19:21:43</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-01-29 11:14:08</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-30 08:44:51</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-02-01 08:52:23</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>Passive Knee Extension</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>Passive Knee Flexion</t>
+  </si>
+  <si>
+    <t>Swelling</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -613,11 +652,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -913,15 +951,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H175"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="39.33203125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -947,23 +985,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>45947</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>45947.704595950803</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
@@ -973,23 +1011,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>45947</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>45947.704659476702</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
@@ -999,23 +1037,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1">
         <v>45947</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>45947.704952933702</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>100</v>
       </c>
       <c r="G4" t="s">
@@ -1025,23 +1063,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>45947</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>45947.705045544899</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>130</v>
       </c>
       <c r="G5" t="s">
@@ -1051,23 +1089,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>45947</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>45947.705211323802</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" t="s">
@@ -1077,23 +1115,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1">
         <v>45947</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>45947.705280315502</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
@@ -1103,23 +1141,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>0</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="1">
         <v>45948</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>45948.664888072301</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
@@ -1129,23 +1167,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="1">
         <v>45948</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>45948.664965998003</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
@@ -1155,23 +1193,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>0</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="1">
         <v>45948</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>45948.665130714297</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>105</v>
       </c>
       <c r="G10" t="s">
@@ -1181,23 +1219,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>0</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="1">
         <v>45948</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>45948.665214019697</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>128</v>
       </c>
       <c r="G11" t="s">
@@ -1207,23 +1245,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>0</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="1">
         <v>45948</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>45948.665349680203</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0</v>
       </c>
       <c r="G12" t="s">
@@ -1233,23 +1271,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>0</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="1">
         <v>45948</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2">
         <v>45948.665392863797</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
@@ -1259,23 +1297,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>0</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="1">
         <v>45948</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>45948.666299291603</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>45</v>
       </c>
       <c r="G14" t="s">
@@ -1285,23 +1323,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="1">
         <v>45948</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="2">
         <v>45948.666350146101</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>60</v>
       </c>
       <c r="G15" t="s">
@@ -1311,23 +1349,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>0</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="1">
         <v>45950</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2">
         <v>45950.435864299601</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" t="s">
@@ -1337,23 +1375,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>0</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="1">
         <v>45950</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2">
         <v>45950.435907915002</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0</v>
       </c>
       <c r="G17" t="s">
@@ -1363,23 +1401,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>0</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="1">
         <v>45950</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2">
         <v>45950.436296253101</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
@@ -1389,23 +1427,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>0</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="1">
         <v>45950</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="2">
         <v>45950.436443767503</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>118</v>
       </c>
       <c r="G19" t="s">
@@ -1415,23 +1453,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>0</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="1">
         <v>45950</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2">
         <v>45950.436589819903</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>47</v>
       </c>
       <c r="G20" t="s">
@@ -1441,23 +1479,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>0</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="1">
         <v>45950</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="2">
         <v>45950.436639752603</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>59</v>
       </c>
       <c r="G21" t="s">
@@ -1467,23 +1505,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="1">
         <v>45958</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="2">
         <v>45958.6841577331</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
@@ -1493,23 +1531,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>0</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="1">
         <v>45958</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2">
         <v>45958.684209632003</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" t="s">
@@ -1519,23 +1557,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>0</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="1">
         <v>45958</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="2">
         <v>45958.684322089699</v>
       </c>
       <c r="E24" t="s">
         <v>44</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>121</v>
       </c>
       <c r="G24" t="s">
@@ -1545,23 +1583,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="1">
         <v>45958</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="2">
         <v>45958.684389989503</v>
       </c>
       <c r="E25" t="s">
         <v>47</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>130</v>
       </c>
       <c r="G25" t="s">
@@ -1571,23 +1609,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>0</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="1">
         <v>45958</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="2">
         <v>45958.684524802797</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
@@ -1597,23 +1635,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>0</v>
       </c>
       <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="1">
         <v>45958</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="2">
         <v>45958.684905007998</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>59</v>
       </c>
       <c r="G27" t="s">
@@ -1623,23 +1661,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>0</v>
       </c>
       <c r="B28" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="1">
         <v>45958</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="2">
         <v>45958.684968170899</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>48</v>
       </c>
       <c r="G28" t="s">
@@ -1649,23 +1687,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>0</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="1">
         <v>45958</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="2">
         <v>45958.685067698403</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>95</v>
       </c>
       <c r="G29" t="s">
@@ -1675,23 +1713,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>0</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="1">
         <v>45958</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="2">
         <v>45958.685166592397</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>64</v>
       </c>
       <c r="G30" t="s">
@@ -1701,23 +1739,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>0</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="1">
         <v>45958</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="2">
         <v>45958.685324976199</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>93</v>
       </c>
       <c r="G31" t="s">
@@ -1727,23 +1765,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>0</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="1">
         <v>45958</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="2">
         <v>45958.685387673802</v>
       </c>
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>62</v>
       </c>
       <c r="G32" t="s">
@@ -1753,23 +1791,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>0</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="1">
         <v>45959</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="2">
         <v>45959.385571423503</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" t="s">
@@ -1779,23 +1817,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>0</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="1">
         <v>45959</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="2">
         <v>45959.385909921002</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
@@ -1805,23 +1843,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="1">
         <v>45960</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="2">
         <v>45960.491801712298</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>0</v>
       </c>
       <c r="G35" t="s">
@@ -1831,23 +1869,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>0</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="1">
         <v>45960</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="2">
         <v>45960.491960884297</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>125</v>
       </c>
       <c r="G36" t="s">
@@ -1857,23 +1895,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>0</v>
       </c>
       <c r="B37" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="1">
         <v>45960</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="2">
         <v>45960.492014117801</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>128</v>
       </c>
       <c r="G37" t="s">
@@ -1883,23 +1921,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="1">
         <v>45960</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="2">
         <v>45960.492522578497</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>72</v>
       </c>
       <c r="G38" t="s">
@@ -1909,23 +1947,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39">
         <v>0</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="1">
         <v>45960</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="2">
         <v>45960.4925716453</v>
       </c>
       <c r="E39" t="s">
         <v>47</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>92</v>
       </c>
       <c r="G39" t="s">
@@ -1935,23 +1973,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>0</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="1">
         <v>45960</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="2">
         <v>45960.492643531601</v>
       </c>
       <c r="E40" t="s">
         <v>44</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>74</v>
       </c>
       <c r="G40" t="s">
@@ -1961,23 +1999,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>0</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="1">
         <v>45960</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="2">
         <v>45960.492700254901</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>90</v>
       </c>
       <c r="G41" t="s">
@@ -1987,23 +2025,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>0</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="1">
         <v>45965</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="2">
         <v>45965.485657138801</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
@@ -2013,23 +2051,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43">
         <v>0</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="1">
         <v>45965</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="2">
         <v>45965.485844846997</v>
       </c>
       <c r="E43" t="s">
         <v>44</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>80</v>
       </c>
       <c r="G43" t="s">
@@ -2039,23 +2077,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44">
         <v>0</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="1">
         <v>45965</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="2">
         <v>45965.485890989898</v>
       </c>
       <c r="E44" t="s">
         <v>44</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>82</v>
       </c>
       <c r="G44" t="s">
@@ -2065,23 +2103,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>0</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="1">
         <v>45965</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="2">
         <v>45965.485968485897</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>87</v>
       </c>
       <c r="G45" t="s">
@@ -2091,23 +2129,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>0</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="1">
         <v>45965</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="2">
         <v>45965.486001955702</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>89</v>
       </c>
       <c r="G46" t="s">
@@ -2117,23 +2155,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>0</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="1">
         <v>45965</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="2">
         <v>45965.486250549002</v>
       </c>
       <c r="E47" t="s">
         <v>44</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>50</v>
       </c>
       <c r="G47" t="s">
@@ -2143,23 +2181,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>0</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="1">
         <v>45965</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="2">
         <v>45965.486292492598</v>
       </c>
       <c r="E48" t="s">
         <v>44</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>52</v>
       </c>
       <c r="G48" t="s">
@@ -2169,23 +2207,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49">
         <v>0</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="1">
         <v>45965</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="2">
         <v>45965.486377312402</v>
       </c>
       <c r="E49" t="s">
         <v>47</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>54</v>
       </c>
       <c r="G49" t="s">
@@ -2195,23 +2233,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50">
         <v>0</v>
       </c>
       <c r="B50" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="1">
         <v>45965</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="2">
         <v>45965.486404639203</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>56</v>
       </c>
       <c r="G50" t="s">
@@ -2221,23 +2259,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51">
         <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="1">
         <v>45974</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="2">
         <v>45974.411367086701</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>3</v>
       </c>
       <c r="G51" t="s">
@@ -2247,23 +2285,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="1">
         <v>45974</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="2">
         <v>45974.411416700903</v>
       </c>
       <c r="E52" t="s">
         <v>47</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
@@ -2273,23 +2311,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="1">
         <v>45975</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="2">
         <v>45975.537941231603</v>
       </c>
       <c r="E53" t="s">
         <v>44</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>2</v>
       </c>
       <c r="G53" t="s">
@@ -2299,23 +2337,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>1</v>
       </c>
       <c r="B54" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="1">
         <v>45975</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="2">
         <v>45975.538157998897</v>
       </c>
       <c r="E54" t="s">
         <v>47</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
@@ -2325,23 +2363,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="1">
         <v>45975</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="2">
         <v>45975.544261836498</v>
       </c>
       <c r="E55" t="s">
         <v>44</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>5</v>
       </c>
       <c r="G55" t="s">
@@ -2351,23 +2389,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56">
         <v>1</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="1">
         <v>45975</v>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="2">
         <v>45975.544303050097</v>
       </c>
       <c r="E56" t="s">
         <v>47</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
@@ -2377,23 +2415,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>1</v>
       </c>
       <c r="B57" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="1">
         <v>45975</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="2">
         <v>45975.544539589202</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>110</v>
       </c>
       <c r="G57" t="s">
@@ -2403,23 +2441,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58">
         <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="1">
         <v>45975</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="2">
         <v>45975.544575668398</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>125</v>
       </c>
       <c r="G58" t="s">
@@ -2429,23 +2467,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59">
         <v>1</v>
       </c>
       <c r="B59" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="1">
         <v>45989</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="2">
         <v>45989.657419278097</v>
       </c>
       <c r="E59" t="s">
         <v>44</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
@@ -2455,23 +2493,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60">
         <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="1">
         <v>45989</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="2">
         <v>45989.657464727003</v>
       </c>
       <c r="E60" t="s">
         <v>47</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>0</v>
       </c>
       <c r="G60" t="s">
@@ -2481,23 +2519,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61">
         <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="1">
         <v>45989</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="2">
         <v>45989.657658854201</v>
       </c>
       <c r="E61" t="s">
         <v>44</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
@@ -2507,23 +2545,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="1">
         <v>45989</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="2">
         <v>45989.657725292898</v>
       </c>
       <c r="E62" t="s">
         <v>47</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
@@ -2533,23 +2571,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>1</v>
       </c>
       <c r="B63" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="1">
         <v>45989</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="2">
         <v>45989.657879157297</v>
       </c>
       <c r="E63" t="s">
         <v>44</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>117</v>
       </c>
       <c r="G63" t="s">
@@ -2559,23 +2597,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64">
         <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="1">
         <v>45989</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="2">
         <v>45989.657918513098</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>126</v>
       </c>
       <c r="G64" t="s">
@@ -2585,23 +2623,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65">
         <v>1</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="1">
         <v>45989</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="2">
         <v>45989.658742763997</v>
       </c>
       <c r="E65" t="s">
         <v>44</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>2</v>
       </c>
       <c r="G65" t="s">
@@ -2611,23 +2649,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66">
         <v>1</v>
       </c>
       <c r="B66" t="s">
         <v>114</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="1">
         <v>45996</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="2">
         <v>46030.597367625</v>
       </c>
       <c r="E66" t="s">
         <v>115</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
@@ -2637,23 +2675,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67">
         <v>1</v>
       </c>
       <c r="B67" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="1">
         <v>45996</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="2">
         <v>46030.597429351699</v>
       </c>
       <c r="E67" t="s">
         <v>118</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
@@ -2663,23 +2701,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68">
         <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>119</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="1">
         <v>45996</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="2">
         <v>46030.597768818101</v>
       </c>
       <c r="E68" t="s">
         <v>115</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>120</v>
       </c>
       <c r="G68" t="s">
@@ -2689,23 +2727,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69">
         <v>1</v>
       </c>
       <c r="B69" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="1">
         <v>45996</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="2">
         <v>46030.597819244598</v>
       </c>
       <c r="E69" t="s">
         <v>118</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>125</v>
       </c>
       <c r="G69" t="s">
@@ -2715,23 +2753,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70">
         <v>1</v>
       </c>
       <c r="B70" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="1">
         <v>45996</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="2">
         <v>46030.5981109887</v>
       </c>
       <c r="E70" t="s">
         <v>115</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>2</v>
       </c>
       <c r="G70" t="s">
@@ -2741,23 +2779,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71">
         <v>1</v>
       </c>
       <c r="B71" t="s">
         <v>121</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="1">
         <v>45996</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="2">
         <v>46030.598165269199</v>
       </c>
       <c r="E71" t="s">
         <v>118</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" t="s">
@@ -2767,23 +2805,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72">
         <v>1</v>
       </c>
       <c r="B72" t="s">
         <v>122</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="1">
         <v>45996</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="2">
         <v>46030.5985355347</v>
       </c>
       <c r="E72" t="s">
         <v>115</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
@@ -2793,23 +2831,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73">
         <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="1">
         <v>46003</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="2">
         <v>46030.598729730598</v>
       </c>
       <c r="E73" t="s">
         <v>115</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
@@ -2819,23 +2857,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74">
         <v>1</v>
       </c>
       <c r="B74" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="1">
         <v>46003</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="2">
         <v>46030.598804364497</v>
       </c>
       <c r="E74" t="s">
         <v>118</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>0</v>
       </c>
       <c r="G74" t="s">
@@ -2845,23 +2883,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75">
         <v>1</v>
       </c>
       <c r="B75" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="1">
         <v>46003</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="2">
         <v>46030.598952235603</v>
       </c>
       <c r="E75" t="s">
         <v>115</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>122</v>
       </c>
       <c r="G75" t="s">
@@ -2871,23 +2909,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76">
         <v>1</v>
       </c>
       <c r="B76" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="C76" s="1">
         <v>46003</v>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="2">
         <v>46030.5989977875</v>
       </c>
       <c r="E76" t="s">
         <v>118</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>127</v>
       </c>
       <c r="G76" t="s">
@@ -2897,23 +2935,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77">
         <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>121</v>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C77" s="1">
         <v>46003</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="2">
         <v>46030.5991297031</v>
       </c>
       <c r="E77" t="s">
         <v>115</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
@@ -2923,23 +2961,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78">
         <v>1</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
       </c>
-      <c r="C78" s="1" t="n">
+      <c r="C78" s="1">
         <v>46003</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="2">
         <v>46030.599185763604</v>
       </c>
       <c r="E78" t="s">
         <v>118</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>0</v>
       </c>
       <c r="G78" t="s">
@@ -2949,23 +2987,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79">
         <v>1</v>
       </c>
       <c r="B79" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="1" t="n">
+      <c r="C79" s="1">
         <v>46003</v>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="2">
         <v>46030.599461440201</v>
       </c>
       <c r="E79" t="s">
         <v>118</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
@@ -2975,23 +3013,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80">
         <v>1</v>
       </c>
       <c r="B80" t="s">
         <v>122</v>
       </c>
-      <c r="C80" s="1" t="n">
+      <c r="C80" s="1">
         <v>46003</v>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="2">
         <v>46030.6009521206</v>
       </c>
       <c r="E80" t="s">
         <v>115</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
@@ -3001,23 +3039,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81">
         <v>1</v>
       </c>
       <c r="B81" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="1" t="n">
+      <c r="C81" s="1">
         <v>46010</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="2">
         <v>46030.601362099602</v>
       </c>
       <c r="E81" t="s">
         <v>115</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
@@ -3027,23 +3065,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82">
         <v>1</v>
       </c>
       <c r="B82" t="s">
         <v>114</v>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="C82" s="1">
         <v>46010</v>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="2">
         <v>46030.601397267797</v>
       </c>
       <c r="E82" t="s">
         <v>118</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>0</v>
       </c>
       <c r="G82" t="s">
@@ -3053,23 +3091,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83">
         <v>1</v>
       </c>
       <c r="B83" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="1" t="n">
+      <c r="C83" s="1">
         <v>46010</v>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="2">
         <v>46030.601664699498</v>
       </c>
       <c r="E83" t="s">
         <v>115</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>124</v>
       </c>
       <c r="G83" t="s">
@@ -3079,23 +3117,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84">
         <v>1</v>
       </c>
       <c r="B84" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="1" t="n">
+      <c r="C84" s="1">
         <v>46010</v>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="2">
         <v>46030.601707849899</v>
       </c>
       <c r="E84" t="s">
         <v>118</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>125</v>
       </c>
       <c r="G84" t="s">
@@ -3105,23 +3143,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85">
         <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>121</v>
       </c>
-      <c r="C85" s="1" t="n">
+      <c r="C85" s="1">
         <v>46010</v>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="2">
         <v>46030.601880503098</v>
       </c>
       <c r="E85" t="s">
         <v>115</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" t="s">
@@ -3131,23 +3169,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86">
         <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>121</v>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="C86" s="1">
         <v>46010</v>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="2">
         <v>46030.601922228001</v>
       </c>
       <c r="E86" t="s">
         <v>118</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
@@ -3157,23 +3195,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87">
         <v>1</v>
       </c>
       <c r="B87" t="s">
         <v>122</v>
       </c>
-      <c r="C87" s="1" t="n">
+      <c r="C87" s="1">
         <v>46010</v>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="2">
         <v>46030.602015028402</v>
       </c>
       <c r="E87" t="s">
         <v>115</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
@@ -3183,23 +3221,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88">
         <v>1</v>
       </c>
       <c r="B88" t="s">
         <v>114</v>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="C88" s="1">
         <v>46022</v>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="2">
         <v>46030.602325239699</v>
       </c>
       <c r="E88" t="s">
         <v>115</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>0</v>
       </c>
       <c r="G88" t="s">
@@ -3209,23 +3247,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89">
         <v>1</v>
       </c>
       <c r="B89" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="1" t="n">
+      <c r="C89" s="1">
         <v>46022</v>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="2">
         <v>46030.602364462902</v>
       </c>
       <c r="E89" t="s">
         <v>118</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>0</v>
       </c>
       <c r="G89" t="s">
@@ -3235,23 +3273,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90">
         <v>1</v>
       </c>
       <c r="B90" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="1" t="n">
+      <c r="C90" s="1">
         <v>46022</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="2">
         <v>46030.602432747299</v>
       </c>
       <c r="E90" t="s">
         <v>115</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>125</v>
       </c>
       <c r="G90" t="s">
@@ -3261,23 +3299,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91">
         <v>1</v>
       </c>
       <c r="B91" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="1" t="n">
+      <c r="C91" s="1">
         <v>46022</v>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="2">
         <v>46030.602474245497</v>
       </c>
       <c r="E91" t="s">
         <v>118</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>125</v>
       </c>
       <c r="G91" t="s">
@@ -3287,23 +3325,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92">
         <v>1</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
       </c>
-      <c r="C92" s="1" t="n">
+      <c r="C92" s="1">
         <v>46022</v>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" s="2">
         <v>46030.602583176304</v>
       </c>
       <c r="E92" t="s">
         <v>115</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>0</v>
       </c>
       <c r="G92" t="s">
@@ -3313,23 +3351,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93">
         <v>1</v>
       </c>
       <c r="B93" t="s">
         <v>121</v>
       </c>
-      <c r="C93" s="1" t="n">
+      <c r="C93" s="1">
         <v>46022</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="2">
         <v>46030.602620265403</v>
       </c>
       <c r="E93" t="s">
         <v>118</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>0</v>
       </c>
       <c r="G93" t="s">
@@ -3339,23 +3377,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94">
         <v>1</v>
       </c>
       <c r="B94" t="s">
         <v>122</v>
       </c>
-      <c r="C94" s="1" t="n">
+      <c r="C94" s="1">
         <v>46022</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="2">
         <v>46030.602707964201</v>
       </c>
       <c r="E94" t="s">
         <v>115</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>0</v>
       </c>
       <c r="G94" t="s">
@@ -3365,23 +3403,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95">
         <v>2</v>
       </c>
       <c r="B95" t="s">
         <v>126</v>
       </c>
-      <c r="C95" s="1" t="n">
+      <c r="C95" s="1">
         <v>46034</v>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="2">
         <v>46034.442400281303</v>
       </c>
       <c r="E95" t="s">
         <v>127</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" t="s">
@@ -3391,23 +3429,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96">
         <v>2</v>
       </c>
       <c r="B96" t="s">
         <v>126</v>
       </c>
-      <c r="C96" s="1" t="n">
+      <c r="C96" s="1">
         <v>46034</v>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D96" s="2">
         <v>46034.442454999</v>
       </c>
       <c r="E96" t="s">
         <v>130</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>0</v>
       </c>
       <c r="G96" t="s">
@@ -3417,23 +3455,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97">
         <v>2</v>
       </c>
       <c r="B97" t="s">
         <v>131</v>
       </c>
-      <c r="C97" s="1" t="n">
+      <c r="C97" s="1">
         <v>46034</v>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" s="2">
         <v>46034.442543972596</v>
       </c>
       <c r="E97" t="s">
         <v>127</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>126</v>
       </c>
       <c r="G97" t="s">
@@ -3443,23 +3481,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98">
         <v>2</v>
       </c>
       <c r="B98" t="s">
         <v>131</v>
       </c>
-      <c r="C98" s="1" t="n">
+      <c r="C98" s="1">
         <v>46034</v>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="2">
         <v>46034.442594817498</v>
       </c>
       <c r="E98" t="s">
         <v>130</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>126</v>
       </c>
       <c r="G98" t="s">
@@ -3469,23 +3507,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99">
         <v>2</v>
       </c>
       <c r="B99" t="s">
         <v>132</v>
       </c>
-      <c r="C99" s="1" t="n">
+      <c r="C99" s="1">
         <v>46034</v>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" s="2">
         <v>46034.4427237583</v>
       </c>
       <c r="E99" t="s">
         <v>127</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>0</v>
       </c>
       <c r="G99" t="s">
@@ -3495,23 +3533,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100">
         <v>2</v>
       </c>
       <c r="B100" t="s">
         <v>134</v>
       </c>
-      <c r="C100" s="1" t="n">
+      <c r="C100" s="1">
         <v>46034</v>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" s="2">
         <v>46034.442922526003</v>
       </c>
       <c r="E100" t="s">
         <v>127</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>7</v>
       </c>
       <c r="G100" t="s">
@@ -3521,23 +3559,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101">
         <v>2</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
       </c>
-      <c r="C101" s="1" t="n">
+      <c r="C101" s="1">
         <v>46034</v>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" s="2">
         <v>46034.442973844598</v>
       </c>
       <c r="E101" t="s">
         <v>130</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>15</v>
       </c>
       <c r="G101" t="s">
@@ -3547,23 +3585,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102">
         <v>2</v>
       </c>
       <c r="B102" t="s">
         <v>136</v>
       </c>
-      <c r="C102" s="1" t="n">
+      <c r="C102" s="1">
         <v>46034</v>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="2">
         <v>46034.443637573902</v>
       </c>
       <c r="E102" t="s">
         <v>127</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>5</v>
       </c>
       <c r="G102" t="s">
@@ -3573,23 +3611,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103">
         <v>2</v>
       </c>
       <c r="B103" t="s">
         <v>136</v>
       </c>
-      <c r="C103" s="1" t="n">
+      <c r="C103" s="1">
         <v>46034</v>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="2">
         <v>46034.443697991803</v>
       </c>
       <c r="E103" t="s">
         <v>130</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>13</v>
       </c>
       <c r="G103" t="s">
@@ -3599,23 +3637,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104">
         <v>2</v>
       </c>
       <c r="B104" t="s">
         <v>137</v>
       </c>
-      <c r="C104" s="1" t="n">
+      <c r="C104" s="1">
         <v>46034</v>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D104" s="2">
         <v>46034.539288706503</v>
       </c>
       <c r="E104" t="s">
         <v>138</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>40</v>
       </c>
       <c r="G104" t="s">
@@ -3625,23 +3663,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105">
         <v>2</v>
       </c>
       <c r="B105" t="s">
         <v>140</v>
       </c>
-      <c r="C105" s="1" t="n">
+      <c r="C105" s="1">
         <v>46034</v>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" s="2">
         <v>46034.5661824204</v>
       </c>
       <c r="E105" t="s">
         <v>127</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>6</v>
       </c>
       <c r="G105" t="s">
@@ -3651,23 +3689,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106">
         <v>2</v>
       </c>
       <c r="B106" t="s">
         <v>140</v>
       </c>
-      <c r="C106" s="1" t="n">
+      <c r="C106" s="1">
         <v>46034</v>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D106" s="2">
         <v>46034.566247390401</v>
       </c>
       <c r="E106" t="s">
         <v>130</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>15</v>
       </c>
       <c r="G106" t="s">
@@ -3677,23 +3715,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107">
         <v>2</v>
       </c>
       <c r="B107" t="s">
         <v>134</v>
       </c>
-      <c r="C107" s="1" t="n">
+      <c r="C107" s="1">
         <v>46038</v>
       </c>
-      <c r="D107" s="2" t="n">
+      <c r="D107" s="2">
         <v>46038.6692860279</v>
       </c>
       <c r="E107" t="s">
         <v>127</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>9</v>
       </c>
       <c r="G107" t="s">
@@ -3703,23 +3741,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108">
         <v>2</v>
       </c>
       <c r="B108" t="s">
         <v>134</v>
       </c>
-      <c r="C108" s="1" t="n">
+      <c r="C108" s="1">
         <v>46038</v>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" s="2">
         <v>46038.669370621101</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>17</v>
       </c>
       <c r="G108" t="s">
@@ -3729,23 +3767,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109">
         <v>2</v>
       </c>
       <c r="B109" t="s">
         <v>136</v>
       </c>
-      <c r="C109" s="1" t="n">
+      <c r="C109" s="1">
         <v>46038</v>
       </c>
-      <c r="D109" s="2" t="n">
+      <c r="D109" s="2">
         <v>46038.669554267297</v>
       </c>
       <c r="E109" t="s">
         <v>127</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>7</v>
       </c>
       <c r="G109" t="s">
@@ -3755,23 +3793,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110">
         <v>2</v>
       </c>
       <c r="B110" t="s">
         <v>136</v>
       </c>
-      <c r="C110" s="1" t="n">
+      <c r="C110" s="1">
         <v>46038</v>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D110" s="2">
         <v>46038.669627650503</v>
       </c>
       <c r="E110" t="s">
         <v>130</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>14</v>
       </c>
       <c r="G110" t="s">
@@ -3781,23 +3819,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111">
         <v>2</v>
       </c>
       <c r="B111" t="s">
         <v>140</v>
       </c>
-      <c r="C111" s="1" t="n">
+      <c r="C111" s="1">
         <v>46038</v>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D111" s="2">
         <v>46038.6698742878</v>
       </c>
       <c r="E111" t="s">
         <v>127</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>8</v>
       </c>
       <c r="G111" t="s">
@@ -3807,23 +3845,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112">
         <v>2</v>
       </c>
       <c r="B112" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="1" t="n">
+      <c r="C112" s="1">
         <v>46038</v>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D112" s="2">
         <v>46038.669928152704</v>
       </c>
       <c r="E112" t="s">
         <v>130</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>15</v>
       </c>
       <c r="G112" t="s">
@@ -3833,23 +3871,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113">
         <v>2</v>
       </c>
       <c r="B113" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="1" t="n">
+      <c r="C113" s="1">
         <v>46038</v>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D113" s="2">
         <v>46038.6707992843</v>
       </c>
       <c r="E113" t="s">
         <v>127</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>30</v>
       </c>
       <c r="G113" t="s">
@@ -3859,23 +3897,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114">
         <v>2</v>
       </c>
       <c r="B114" t="s">
         <v>148</v>
       </c>
-      <c r="C114" s="1" t="n">
+      <c r="C114" s="1">
         <v>46038</v>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" s="2">
         <v>46038.670836973499</v>
       </c>
       <c r="E114" t="s">
         <v>130</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>30</v>
       </c>
       <c r="G114" t="s">
@@ -3885,23 +3923,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A115">
         <v>2</v>
       </c>
       <c r="B115" t="s">
         <v>154</v>
       </c>
-      <c r="C115" s="1" t="n">
+      <c r="C115" s="1">
         <v>46042</v>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D115" s="2">
         <v>46042.360163172401</v>
       </c>
       <c r="E115" t="s">
         <v>127</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>30</v>
       </c>
       <c r="G115" t="s">
@@ -3911,23 +3949,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116">
         <v>2</v>
       </c>
       <c r="B116" t="s">
         <v>154</v>
       </c>
-      <c r="C116" s="1" t="n">
+      <c r="C116" s="1">
         <v>46042</v>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" s="2">
         <v>46042.360217777801</v>
       </c>
       <c r="E116" t="s">
         <v>130</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>45</v>
       </c>
       <c r="G116" t="s">
@@ -3937,23 +3975,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117">
         <v>2</v>
       </c>
       <c r="B117" t="s">
         <v>155</v>
       </c>
-      <c r="C117" s="1" t="n">
+      <c r="C117" s="1">
         <v>46042</v>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D117" s="2">
         <v>46042.361174106802</v>
       </c>
       <c r="E117" t="s">
         <v>127</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>40</v>
       </c>
       <c r="G117" t="s">
@@ -3963,23 +4001,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118">
         <v>2</v>
       </c>
       <c r="B118" t="s">
         <v>155</v>
       </c>
-      <c r="C118" s="1" t="n">
+      <c r="C118" s="1">
         <v>46042</v>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D118" s="2">
         <v>46042.361259715202</v>
       </c>
       <c r="E118" t="s">
         <v>127</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>38</v>
       </c>
       <c r="G118" t="s">
@@ -3989,23 +4027,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A119">
         <v>2</v>
       </c>
       <c r="B119" t="s">
         <v>155</v>
       </c>
-      <c r="C119" s="1" t="n">
+      <c r="C119" s="1">
         <v>46042</v>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D119" s="2">
         <v>46042.361303134297</v>
       </c>
       <c r="E119" t="s">
         <v>127</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>38</v>
       </c>
       <c r="G119" t="s">
@@ -4015,23 +4053,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="n">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A120">
         <v>2</v>
       </c>
       <c r="B120" t="s">
         <v>155</v>
       </c>
-      <c r="C120" s="1" t="n">
+      <c r="C120" s="1">
         <v>46042</v>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D120" s="2">
         <v>46042.361404144598</v>
       </c>
       <c r="E120" t="s">
         <v>130</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>60</v>
       </c>
       <c r="G120" t="s">
@@ -4041,23 +4079,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A121">
         <v>2</v>
       </c>
       <c r="B121" t="s">
         <v>155</v>
       </c>
-      <c r="C121" s="1" t="n">
+      <c r="C121" s="1">
         <v>46042</v>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D121" s="2">
         <v>46042.361443357302</v>
       </c>
       <c r="E121" t="s">
         <v>130</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>61</v>
       </c>
       <c r="G121" t="s">
@@ -4067,23 +4105,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A122">
         <v>2</v>
       </c>
       <c r="B122" t="s">
         <v>155</v>
       </c>
-      <c r="C122" s="1" t="n">
+      <c r="C122" s="1">
         <v>46042</v>
       </c>
-      <c r="D122" s="2" t="n">
+      <c r="D122" s="2">
         <v>46042.361489097799</v>
       </c>
       <c r="E122" t="s">
         <v>130</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>64</v>
       </c>
       <c r="G122" t="s">
@@ -4093,23 +4131,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123">
         <v>2</v>
       </c>
       <c r="B123" t="s">
         <v>156</v>
       </c>
-      <c r="C123" s="1" t="n">
+      <c r="C123" s="1">
         <v>46042</v>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D123" s="2">
         <v>46042.361928238002</v>
       </c>
       <c r="E123" t="s">
         <v>127</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>80</v>
       </c>
       <c r="G123" t="s">
@@ -4119,23 +4157,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A124">
         <v>2</v>
       </c>
       <c r="B124" t="s">
         <v>156</v>
       </c>
-      <c r="C124" s="1" t="n">
+      <c r="C124" s="1">
         <v>46042</v>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D124" s="2">
         <v>46042.362212514498</v>
       </c>
       <c r="E124" t="s">
         <v>127</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>78.5</v>
       </c>
       <c r="G124" t="s">
@@ -4145,23 +4183,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125">
         <v>2</v>
       </c>
       <c r="B125" t="s">
         <v>156</v>
       </c>
-      <c r="C125" s="1" t="n">
+      <c r="C125" s="1">
         <v>46042</v>
       </c>
-      <c r="D125" s="2" t="n">
+      <c r="D125" s="2">
         <v>46042.362270635203</v>
       </c>
       <c r="E125" t="s">
         <v>127</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>81.5</v>
       </c>
       <c r="G125" t="s">
@@ -4171,23 +4209,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126">
         <v>2</v>
       </c>
       <c r="B126" t="s">
         <v>156</v>
       </c>
-      <c r="C126" s="1" t="n">
+      <c r="C126" s="1">
         <v>46042</v>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D126" s="2">
         <v>46042.362343741297</v>
       </c>
       <c r="E126" t="s">
         <v>130</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>99.5</v>
       </c>
       <c r="G126" t="s">
@@ -4197,23 +4235,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127">
         <v>2</v>
       </c>
       <c r="B127" t="s">
         <v>156</v>
       </c>
-      <c r="C127" s="1" t="n">
+      <c r="C127" s="1">
         <v>46042</v>
       </c>
-      <c r="D127" s="2" t="n">
+      <c r="D127" s="2">
         <v>46042.362396041899</v>
       </c>
       <c r="E127" t="s">
         <v>130</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>100.5</v>
       </c>
       <c r="G127" t="s">
@@ -4223,23 +4261,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="n">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128">
         <v>2</v>
       </c>
       <c r="B128" t="s">
         <v>156</v>
       </c>
-      <c r="C128" s="1" t="n">
+      <c r="C128" s="1">
         <v>46042</v>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D128" s="2">
         <v>46042.362431900103</v>
       </c>
       <c r="E128" t="s">
         <v>130</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128">
         <v>101</v>
       </c>
       <c r="G128" t="s">
@@ -4249,23 +4287,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="n">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129">
         <v>2</v>
       </c>
       <c r="B129" t="s">
         <v>157</v>
       </c>
-      <c r="C129" s="1" t="n">
+      <c r="C129" s="1">
         <v>46042</v>
       </c>
-      <c r="D129" s="2" t="n">
+      <c r="D129" s="2">
         <v>46042.362576904197</v>
       </c>
       <c r="E129" t="s">
         <v>127</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129">
         <v>65</v>
       </c>
       <c r="G129" t="s">
@@ -4275,23 +4313,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="n">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A130">
         <v>2</v>
       </c>
       <c r="B130" t="s">
         <v>157</v>
       </c>
-      <c r="C130" s="1" t="n">
+      <c r="C130" s="1">
         <v>46042</v>
       </c>
-      <c r="D130" s="2" t="n">
+      <c r="D130" s="2">
         <v>46042.3626157908</v>
       </c>
       <c r="E130" t="s">
         <v>127</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130">
         <v>66.5</v>
       </c>
       <c r="G130" t="s">
@@ -4301,23 +4339,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A131">
         <v>2</v>
       </c>
       <c r="B131" t="s">
         <v>157</v>
       </c>
-      <c r="C131" s="1" t="n">
+      <c r="C131" s="1">
         <v>46042</v>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D131" s="2">
         <v>46042.362653184799</v>
       </c>
       <c r="E131" t="s">
         <v>127</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131">
         <v>68.5</v>
       </c>
       <c r="G131" t="s">
@@ -4327,23 +4365,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132">
         <v>2</v>
       </c>
       <c r="B132" t="s">
         <v>157</v>
       </c>
-      <c r="C132" s="1" t="n">
+      <c r="C132" s="1">
         <v>46042</v>
       </c>
-      <c r="D132" s="2" t="n">
+      <c r="D132" s="2">
         <v>46042.362854254898</v>
       </c>
       <c r="E132" t="s">
         <v>130</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132">
         <v>89.5</v>
       </c>
       <c r="G132" t="s">
@@ -4353,23 +4391,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="n">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A133">
         <v>2</v>
       </c>
       <c r="B133" t="s">
         <v>157</v>
       </c>
-      <c r="C133" s="1" t="n">
+      <c r="C133" s="1">
         <v>46042</v>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D133" s="2">
         <v>46042.362889967699</v>
       </c>
       <c r="E133" t="s">
         <v>130</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133">
         <v>92</v>
       </c>
       <c r="G133" t="s">
@@ -4379,23 +4417,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="n">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A134">
         <v>2</v>
       </c>
       <c r="B134" t="s">
         <v>157</v>
       </c>
-      <c r="C134" s="1" t="n">
+      <c r="C134" s="1">
         <v>46042</v>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D134" s="2">
         <v>46042.362965286797</v>
       </c>
       <c r="E134" t="s">
         <v>130</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134">
         <v>91.5</v>
       </c>
       <c r="G134" t="s">
@@ -4405,23 +4443,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A135">
         <v>2</v>
       </c>
       <c r="B135" t="s">
         <v>162</v>
       </c>
-      <c r="C135" s="1" t="n">
+      <c r="C135" s="1">
         <v>46045</v>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="D135" s="2">
         <v>46045.4466951266</v>
       </c>
       <c r="E135" t="s">
         <v>163</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135">
         <v>12</v>
       </c>
       <c r="G135" t="s">
@@ -4431,23 +4469,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="n">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A136">
         <v>2</v>
       </c>
       <c r="B136" t="s">
         <v>162</v>
       </c>
-      <c r="C136" s="1" t="n">
+      <c r="C136" s="1">
         <v>46045</v>
       </c>
-      <c r="D136" s="3" t="n">
-        <v>46045.4467432926</v>
+      <c r="D136" s="2">
+        <v>46045.446743292603</v>
       </c>
       <c r="E136" t="s">
         <v>166</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136">
         <v>19</v>
       </c>
       <c r="G136" t="s">
@@ -4457,23 +4495,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="n">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A137">
         <v>2</v>
       </c>
       <c r="B137" t="s">
         <v>167</v>
       </c>
-      <c r="C137" s="1" t="n">
+      <c r="C137" s="1">
         <v>46045</v>
       </c>
-      <c r="D137" s="3" t="n">
+      <c r="D137" s="2">
         <v>46045.4469611491</v>
       </c>
       <c r="E137" t="s">
         <v>163</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137">
         <v>10</v>
       </c>
       <c r="G137" t="s">
@@ -4483,23 +4521,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="n">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A138">
         <v>2</v>
       </c>
       <c r="B138" t="s">
         <v>167</v>
       </c>
-      <c r="C138" s="1" t="n">
+      <c r="C138" s="1">
         <v>46045</v>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="D138" s="2">
         <v>46045.4469929935</v>
       </c>
       <c r="E138" t="s">
         <v>166</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138">
         <v>15</v>
       </c>
       <c r="G138" t="s">
@@ -4509,23 +4547,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="n">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A139">
         <v>2</v>
       </c>
       <c r="B139" t="s">
         <v>168</v>
       </c>
-      <c r="C139" s="1" t="n">
+      <c r="C139" s="1">
         <v>46045</v>
       </c>
-      <c r="D139" s="3" t="n">
-        <v>46045.4472388466</v>
+      <c r="D139" s="2">
+        <v>46045.447238846602</v>
       </c>
       <c r="E139" t="s">
         <v>163</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139">
         <v>2</v>
       </c>
       <c r="G139" t="s">
@@ -4535,23 +4573,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A140">
         <v>2</v>
       </c>
       <c r="B140" t="s">
         <v>168</v>
       </c>
-      <c r="C140" s="1" t="n">
+      <c r="C140" s="1">
         <v>46045</v>
       </c>
-      <c r="D140" s="3" t="n">
-        <v>46045.4472716892</v>
+      <c r="D140" s="2">
+        <v>46045.447271689198</v>
       </c>
       <c r="E140" t="s">
         <v>166</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140">
         <v>8</v>
       </c>
       <c r="G140" t="s">
@@ -4561,23 +4599,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="n">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A141">
         <v>2</v>
       </c>
       <c r="B141" t="s">
         <v>169</v>
       </c>
-      <c r="C141" s="1" t="n">
+      <c r="C141" s="1">
         <v>46045</v>
       </c>
-      <c r="D141" s="3" t="n">
-        <v>46045.4475711992</v>
+      <c r="D141" s="2">
+        <v>46045.447571199198</v>
       </c>
       <c r="E141" t="s">
         <v>163</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141">
         <v>10</v>
       </c>
       <c r="G141" t="s">
@@ -4587,23 +4625,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A142">
         <v>2</v>
       </c>
       <c r="B142" t="s">
         <v>169</v>
       </c>
-      <c r="C142" s="1" t="n">
+      <c r="C142" s="1">
         <v>46045</v>
       </c>
-      <c r="D142" s="3" t="n">
+      <c r="D142" s="2">
         <v>46045.4476158369</v>
       </c>
       <c r="E142" t="s">
         <v>166</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142">
         <v>15</v>
       </c>
       <c r="G142" t="s">
@@ -4613,23 +4651,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A143">
         <v>2</v>
       </c>
       <c r="B143" t="s">
         <v>171</v>
       </c>
-      <c r="C143" s="1" t="n">
+      <c r="C143" s="1">
         <v>46045</v>
       </c>
-      <c r="D143" s="3" t="n">
-        <v>46045.4481392084</v>
+      <c r="D143" s="2">
+        <v>46045.448139208398</v>
       </c>
       <c r="E143" t="s">
         <v>163</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143">
         <v>3</v>
       </c>
       <c r="G143" t="s">
@@ -4639,23 +4677,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A144">
         <v>2</v>
       </c>
       <c r="B144" t="s">
         <v>171</v>
       </c>
-      <c r="C144" s="1" t="n">
+      <c r="C144" s="1">
         <v>46045</v>
       </c>
-      <c r="D144" s="3" t="n">
-        <v>46045.4481779641</v>
+      <c r="D144" s="2">
+        <v>46045.448177964099</v>
       </c>
       <c r="E144" t="s">
         <v>166</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144">
         <v>10</v>
       </c>
       <c r="G144" t="s">
@@ -4665,23 +4703,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A145">
         <v>3</v>
       </c>
       <c r="B145" t="s">
         <v>173</v>
       </c>
-      <c r="C145" s="1" t="n">
+      <c r="C145" s="1">
         <v>46047</v>
       </c>
-      <c r="D145" s="3" t="n">
-        <v>46047.4198329487</v>
+      <c r="D145" s="2">
+        <v>46047.419832948697</v>
       </c>
       <c r="E145" t="s">
         <v>163</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145">
         <v>50</v>
       </c>
       <c r="G145" t="s">
@@ -4691,23 +4729,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A146">
         <v>2</v>
       </c>
       <c r="B146" t="s">
         <v>174</v>
       </c>
-      <c r="C146" s="1" t="n">
+      <c r="C146" s="1">
         <v>46047</v>
       </c>
-      <c r="D146" s="3" t="n">
-        <v>46047.4450652627</v>
+      <c r="D146" s="2">
+        <v>46047.445065262698</v>
       </c>
       <c r="E146" t="s">
         <v>163</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146">
         <v>30</v>
       </c>
       <c r="G146" t="s">
@@ -4717,23 +4755,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A147">
         <v>2</v>
       </c>
       <c r="B147" t="s">
         <v>174</v>
       </c>
-      <c r="C147" s="1" t="n">
+      <c r="C147" s="1">
         <v>46047</v>
       </c>
-      <c r="D147" s="3" t="n">
-        <v>46047.4451068267</v>
+      <c r="D147" s="2">
+        <v>46047.445106826701</v>
       </c>
       <c r="E147" t="s">
         <v>166</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147">
         <v>30</v>
       </c>
       <c r="G147" t="s">
@@ -4743,23 +4781,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A148">
         <v>2</v>
       </c>
       <c r="B148" t="s">
         <v>179</v>
       </c>
-      <c r="C148" s="1" t="n">
+      <c r="C148" s="1">
         <v>46049</v>
       </c>
-      <c r="D148" s="3" t="n">
-        <v>46049.2447859849</v>
+      <c r="D148" s="2">
+        <v>46049.244785984898</v>
       </c>
       <c r="E148" t="s">
         <v>163</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148">
         <v>37</v>
       </c>
       <c r="G148" t="s">
@@ -4769,23 +4807,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A149">
         <v>2</v>
       </c>
       <c r="B149" t="s">
         <v>179</v>
       </c>
-      <c r="C149" s="1" t="n">
+      <c r="C149" s="1">
         <v>46049</v>
       </c>
-      <c r="D149" s="3" t="n">
-        <v>46049.2452408769</v>
+      <c r="D149" s="2">
+        <v>46049.245240876902</v>
       </c>
       <c r="E149" t="s">
         <v>166</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149">
         <v>45</v>
       </c>
       <c r="G149" t="s">
@@ -4795,23 +4833,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A150">
         <v>2</v>
       </c>
       <c r="B150" t="s">
         <v>171</v>
       </c>
-      <c r="C150" s="1" t="n">
+      <c r="C150" s="1">
         <v>46049</v>
       </c>
-      <c r="D150" s="3" t="n">
-        <v>46049.2453695697</v>
+      <c r="D150" s="2">
+        <v>46049.245369569697</v>
       </c>
       <c r="E150" t="s">
         <v>163</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150">
         <v>6</v>
       </c>
       <c r="G150" t="s">
@@ -4821,23 +4859,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A151">
         <v>2</v>
       </c>
       <c r="B151" t="s">
         <v>171</v>
       </c>
-      <c r="C151" s="1" t="n">
+      <c r="C151" s="1">
         <v>46049</v>
       </c>
-      <c r="D151" s="3" t="n">
-        <v>46049.2454065638</v>
+      <c r="D151" s="2">
+        <v>46049.245406563801</v>
       </c>
       <c r="E151" t="s">
         <v>166</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151">
         <v>9</v>
       </c>
       <c r="G151" t="s">
@@ -4847,23 +4885,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="n">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A152">
         <v>2</v>
       </c>
       <c r="B152" t="s">
         <v>180</v>
       </c>
-      <c r="C152" s="1" t="n">
+      <c r="C152" s="1">
         <v>46049</v>
       </c>
-      <c r="D152" s="3" t="n">
+      <c r="D152" s="2">
         <v>46049.2458257244</v>
       </c>
       <c r="E152" t="s">
         <v>163</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152">
         <v>42</v>
       </c>
       <c r="G152" t="s">
@@ -4873,23 +4911,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="n">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A153">
         <v>2</v>
       </c>
       <c r="B153" t="s">
         <v>180</v>
       </c>
-      <c r="C153" s="1" t="n">
+      <c r="C153" s="1">
         <v>46049</v>
       </c>
-      <c r="D153" s="3" t="n">
-        <v>46049.2458756964</v>
+      <c r="D153" s="2">
+        <v>46049.245875696397</v>
       </c>
       <c r="E153" t="s">
         <v>163</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153">
         <v>43</v>
       </c>
       <c r="G153" t="s">
@@ -4899,23 +4937,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="n">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A154">
         <v>2</v>
       </c>
       <c r="B154" t="s">
         <v>180</v>
       </c>
-      <c r="C154" s="1" t="n">
+      <c r="C154" s="1">
         <v>46049</v>
       </c>
-      <c r="D154" s="3" t="n">
-        <v>46049.2459168743</v>
+      <c r="D154" s="2">
+        <v>46049.245916874301</v>
       </c>
       <c r="E154" t="s">
         <v>163</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154">
         <v>43.5</v>
       </c>
       <c r="G154" t="s">
@@ -4925,23 +4963,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="n">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A155">
         <v>2</v>
       </c>
       <c r="B155" t="s">
         <v>180</v>
       </c>
-      <c r="C155" s="1" t="n">
+      <c r="C155" s="1">
         <v>46049</v>
       </c>
-      <c r="D155" s="3" t="n">
-        <v>46049.2460143919</v>
+      <c r="D155" s="2">
+        <v>46049.246014391902</v>
       </c>
       <c r="E155" t="s">
         <v>166</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155">
         <v>62.5</v>
       </c>
       <c r="G155" t="s">
@@ -4951,23 +4989,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="n">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A156">
         <v>2</v>
       </c>
       <c r="B156" t="s">
         <v>180</v>
       </c>
-      <c r="C156" s="1" t="n">
+      <c r="C156" s="1">
         <v>46049</v>
       </c>
-      <c r="D156" s="3" t="n">
-        <v>46049.2460697722</v>
+      <c r="D156" s="2">
+        <v>46049.246069772198</v>
       </c>
       <c r="E156" t="s">
         <v>166</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156">
         <v>63.5</v>
       </c>
       <c r="G156" t="s">
@@ -4977,29 +5015,497 @@
         <v>165</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="n">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A157">
         <v>2</v>
       </c>
       <c r="B157" t="s">
         <v>180</v>
       </c>
-      <c r="C157" s="1" t="n">
+      <c r="C157" s="1">
         <v>46049</v>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="D157" s="2">
         <v>46049.2461241977</v>
       </c>
       <c r="E157" t="s">
         <v>166</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157">
         <v>64</v>
       </c>
       <c r="G157" t="s">
         <v>170</v>
       </c>
       <c r="H157" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>2</v>
+      </c>
+      <c r="B158" t="s">
+        <v>189</v>
+      </c>
+      <c r="C158" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D158" s="2">
+        <v>46054.373075639203</v>
+      </c>
+      <c r="E158" t="s">
+        <v>163</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158" t="s">
+        <v>190</v>
+      </c>
+      <c r="H158" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>2</v>
+      </c>
+      <c r="B159" t="s">
+        <v>189</v>
+      </c>
+      <c r="C159" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D159" s="2">
+        <v>46054.3731330847</v>
+      </c>
+      <c r="E159" t="s">
+        <v>166</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159" t="s">
+        <v>190</v>
+      </c>
+      <c r="H159" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>191</v>
+      </c>
+      <c r="C160" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D160" s="2">
+        <v>46054.373350648799</v>
+      </c>
+      <c r="E160" t="s">
+        <v>163</v>
+      </c>
+      <c r="F160">
+        <v>127</v>
+      </c>
+      <c r="G160" t="s">
+        <v>190</v>
+      </c>
+      <c r="H160" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>191</v>
+      </c>
+      <c r="C161" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D161" s="2">
+        <v>46054.373401007098</v>
+      </c>
+      <c r="E161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F161">
+        <v>127</v>
+      </c>
+      <c r="G161" t="s">
+        <v>190</v>
+      </c>
+      <c r="H161" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>2</v>
+      </c>
+      <c r="B162" t="s">
+        <v>192</v>
+      </c>
+      <c r="C162" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D162" s="2">
+        <v>46054.374090033103</v>
+      </c>
+      <c r="E162" t="s">
+        <v>163</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162" t="s">
+        <v>193</v>
+      </c>
+      <c r="H162" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>2</v>
+      </c>
+      <c r="B163" t="s">
+        <v>162</v>
+      </c>
+      <c r="C163" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D163" s="2">
+        <v>46054.374287611798</v>
+      </c>
+      <c r="E163" t="s">
+        <v>163</v>
+      </c>
+      <c r="F163">
+        <v>14</v>
+      </c>
+      <c r="G163" t="s">
+        <v>164</v>
+      </c>
+      <c r="H163" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>162</v>
+      </c>
+      <c r="C164" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D164" s="2">
+        <v>46054.374329414699</v>
+      </c>
+      <c r="E164" t="s">
+        <v>166</v>
+      </c>
+      <c r="F164">
+        <v>20</v>
+      </c>
+      <c r="G164" t="s">
+        <v>164</v>
+      </c>
+      <c r="H164" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>167</v>
+      </c>
+      <c r="C165" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D165" s="2">
+        <v>46054.375393863796</v>
+      </c>
+      <c r="E165" t="s">
+        <v>163</v>
+      </c>
+      <c r="F165">
+        <v>12</v>
+      </c>
+      <c r="G165" t="s">
+        <v>164</v>
+      </c>
+      <c r="H165" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>2</v>
+      </c>
+      <c r="B166" t="s">
+        <v>167</v>
+      </c>
+      <c r="C166" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D166" s="2">
+        <v>46054.375432872897</v>
+      </c>
+      <c r="E166" t="s">
+        <v>166</v>
+      </c>
+      <c r="F166">
+        <v>17</v>
+      </c>
+      <c r="G166" t="s">
+        <v>164</v>
+      </c>
+      <c r="H166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>2</v>
+      </c>
+      <c r="B167" t="s">
+        <v>168</v>
+      </c>
+      <c r="C167" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D167" s="2">
+        <v>46054.375730488297</v>
+      </c>
+      <c r="E167" t="s">
+        <v>163</v>
+      </c>
+      <c r="F167">
+        <v>4</v>
+      </c>
+      <c r="G167" t="s">
+        <v>164</v>
+      </c>
+      <c r="H167" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>2</v>
+      </c>
+      <c r="B168" t="s">
+        <v>168</v>
+      </c>
+      <c r="C168" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D168" s="2">
+        <v>46054.375768050602</v>
+      </c>
+      <c r="E168" t="s">
+        <v>166</v>
+      </c>
+      <c r="F168">
+        <v>9</v>
+      </c>
+      <c r="G168" t="s">
+        <v>164</v>
+      </c>
+      <c r="H168" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>2</v>
+      </c>
+      <c r="B169" t="s">
+        <v>179</v>
+      </c>
+      <c r="C169" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D169" s="2">
+        <v>46054.375964423198</v>
+      </c>
+      <c r="E169" t="s">
+        <v>163</v>
+      </c>
+      <c r="F169">
+        <v>45</v>
+      </c>
+      <c r="G169" t="s">
+        <v>172</v>
+      </c>
+      <c r="H169" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>2</v>
+      </c>
+      <c r="B170" t="s">
+        <v>179</v>
+      </c>
+      <c r="C170" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D170" s="2">
+        <v>46054.375998781703</v>
+      </c>
+      <c r="E170" t="s">
+        <v>166</v>
+      </c>
+      <c r="F170">
+        <v>45</v>
+      </c>
+      <c r="G170" t="s">
+        <v>172</v>
+      </c>
+      <c r="H170" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>2</v>
+      </c>
+      <c r="B171" t="s">
+        <v>171</v>
+      </c>
+      <c r="C171" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D171" s="2">
+        <v>46054.377199965696</v>
+      </c>
+      <c r="E171" t="s">
+        <v>163</v>
+      </c>
+      <c r="F171">
+        <v>9</v>
+      </c>
+      <c r="G171" t="s">
+        <v>172</v>
+      </c>
+      <c r="H171" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>2</v>
+      </c>
+      <c r="B172" t="s">
+        <v>171</v>
+      </c>
+      <c r="C172" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D172" s="2">
+        <v>46054.3772267725</v>
+      </c>
+      <c r="E172" t="s">
+        <v>166</v>
+      </c>
+      <c r="F172">
+        <v>9</v>
+      </c>
+      <c r="G172" t="s">
+        <v>172</v>
+      </c>
+      <c r="H172" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>2</v>
+      </c>
+      <c r="B173" t="s">
+        <v>194</v>
+      </c>
+      <c r="C173" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D173" s="2">
+        <v>46054.377639929997</v>
+      </c>
+      <c r="E173" t="s">
+        <v>138</v>
+      </c>
+      <c r="F173">
+        <v>60</v>
+      </c>
+      <c r="G173" t="s">
+        <v>195</v>
+      </c>
+      <c r="H173" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s">
+        <v>169</v>
+      </c>
+      <c r="C174" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D174" s="2">
+        <v>46054.378020765304</v>
+      </c>
+      <c r="E174" t="s">
+        <v>163</v>
+      </c>
+      <c r="F174">
+        <v>11</v>
+      </c>
+      <c r="G174" t="s">
+        <v>170</v>
+      </c>
+      <c r="H174" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>2</v>
+      </c>
+      <c r="B175" t="s">
+        <v>169</v>
+      </c>
+      <c r="C175" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D175" s="2">
+        <v>46054.378060841897</v>
+      </c>
+      <c r="E175" t="s">
+        <v>166</v>
+      </c>
+      <c r="F175">
+        <v>15</v>
+      </c>
+      <c r="G175" t="s">
+        <v>170</v>
+      </c>
+      <c r="H175" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5010,14 +5516,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -5040,1062 +5546,1108 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>6.5</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>56</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>58</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>6.5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>60</v>
       </c>
       <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>8.5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>62</v>
       </c>
       <c r="B11" t="s">
         <v>63</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>8</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>64</v>
       </c>
       <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>8</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>72</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>7</v>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>7</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>8.5</v>
       </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
         <v>3</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>80</v>
       </c>
       <c r="B19" t="s">
         <v>81</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>9</v>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
         <v>3</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20" t="s">
         <v>83</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>7.5</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>3</v>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
         <v>4</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>8.5</v>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>87</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>7.5</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>6.5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
         <v>3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>91</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>7.5</v>
       </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>7</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>95</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>9</v>
       </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>8</v>
       </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>8</v>
       </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>103</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>8.5</v>
       </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>7.5</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="G31" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>7.5</v>
       </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
         <v>3</v>
       </c>
-      <c r="G32" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>7</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>3</v>
       </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>111</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>7</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>4</v>
       </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>113</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>7</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>3</v>
       </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
         <v>3</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>3</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>124</v>
       </c>
       <c r="B36" t="s">
         <v>125</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>8</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>3</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>3</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>143</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>6.5</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>144</v>
       </c>
       <c r="B38" t="s">
         <v>145</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>7.5</v>
       </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
         <v>4</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>3</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>146</v>
       </c>
       <c r="B39" t="s">
         <v>147</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>6</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>4</v>
       </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>150</v>
       </c>
       <c r="B40" t="s">
         <v>151</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>7.5</v>
       </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>4</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>3</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>153</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>5</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>4</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>3</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>4</v>
       </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>159</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>7</v>
       </c>
-      <c r="D42" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
         <v>3</v>
       </c>
-      <c r="F42" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42">
         <v>4</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>160</v>
       </c>
       <c r="B43" t="s">
         <v>161</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>7</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>4</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>3</v>
       </c>
-      <c r="G43" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="G43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>175</v>
       </c>
       <c r="B44" t="s">
         <v>176</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>6.5</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>4</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>3</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>5</v>
       </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>177</v>
       </c>
       <c r="B45" t="s">
         <v>178</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>8.5</v>
       </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
         <v>3</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>5</v>
       </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="G45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>181</v>
       </c>
       <c r="B46" t="s">
         <v>182</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>8</v>
       </c>
-      <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="n">
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
         <v>4</v>
       </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="G46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>183</v>
       </c>
       <c r="B47" t="s">
         <v>184</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>8</v>
       </c>
-      <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="n">
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47">
         <v>4</v>
       </c>
-      <c r="G47" t="n">
-        <v>1</v>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48">
+        <v>8.5</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49">
+        <v>7.5</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_9C9E34505BA97CF0BA284CBCF432B33B6D082C3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6728692-3663-3441-AFA6-F6FAC16EBE12}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase_data" sheetId="1" r:id="rId1"/>
-    <sheet name="daily" sheetId="2" r:id="rId2"/>
+    <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="197">
   <si>
     <t>Phase</t>
   </si>
@@ -518,7 +511,7 @@
     <t>reps</t>
   </si>
   <si>
-    <t/>
+    <t>NA</t>
   </si>
   <si>
     <t>Right</t>
@@ -609,6 +602,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-02 10:30:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-02</t>
   </si>
 </sst>
 </file>
@@ -618,7 +617,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -654,8 +653,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -951,15 +950,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H175"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="39.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -985,23 +984,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="2" t="n">
         <v>45947.704595950803</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="s">
@@ -1011,23 +1010,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>45947.704659476702</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="s">
@@ -1037,23 +1036,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="2" t="n">
         <v>45947.704952933702</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="s">
@@ -1063,23 +1062,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" t="n">
         <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="2" t="n">
         <v>45947.705045544899</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>130</v>
       </c>
       <c r="G5" t="s">
@@ -1089,23 +1088,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" t="n">
         <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>45947.705211323802</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="s">
@@ -1115,23 +1114,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" t="n">
         <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="2" t="n">
         <v>45947.705280315502</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" t="s">
@@ -1141,23 +1140,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>0</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="2" t="n">
         <v>45948.664888072301</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="s">
@@ -1167,23 +1166,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="2" t="n">
         <v>45948.664965998003</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="s">
@@ -1193,23 +1192,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" t="n">
         <v>0</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="2" t="n">
         <v>45948.665130714297</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>105</v>
       </c>
       <c r="G10" t="s">
@@ -1219,23 +1218,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" t="n">
         <v>0</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="n">
         <v>45948.665214019697</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>128</v>
       </c>
       <c r="G11" t="s">
@@ -1245,23 +1244,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" t="n">
         <v>0</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="n">
         <v>45948.665349680203</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="s">
@@ -1271,23 +1270,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" t="n">
         <v>0</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="2" t="n">
         <v>45948.665392863797</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="s">
@@ -1297,23 +1296,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="14">
+      <c r="A14" t="n">
         <v>0</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="2" t="n">
         <v>45948.666299291603</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>45</v>
       </c>
       <c r="G14" t="s">
@@ -1323,23 +1322,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" t="n">
         <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="2" t="n">
         <v>45948.666350146101</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="s">
@@ -1349,23 +1348,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="16">
+      <c r="A16" t="n">
         <v>0</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="2" t="n">
         <v>45950.435864299601</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="s">
@@ -1375,23 +1374,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="17">
+      <c r="A17" t="n">
         <v>0</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="2" t="n">
         <v>45950.435907915002</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="s">
@@ -1401,23 +1400,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="18">
+      <c r="A18" t="n">
         <v>0</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="2" t="n">
         <v>45950.436296253101</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="s">
@@ -1427,23 +1426,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="19">
+      <c r="A19" t="n">
         <v>0</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="2" t="n">
         <v>45950.436443767503</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>118</v>
       </c>
       <c r="G19" t="s">
@@ -1453,23 +1452,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="20">
+      <c r="A20" t="n">
         <v>0</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="2" t="n">
         <v>45950.436589819903</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>47</v>
       </c>
       <c r="G20" t="s">
@@ -1479,23 +1478,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21">
+    <row r="21">
+      <c r="A21" t="n">
         <v>0</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="2" t="n">
         <v>45950.436639752603</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>59</v>
       </c>
       <c r="G21" t="s">
@@ -1505,23 +1504,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22">
+    <row r="22">
+      <c r="A22" t="n">
         <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="2" t="n">
         <v>45958.6841577331</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="s">
@@ -1531,23 +1530,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23">
+    <row r="23">
+      <c r="A23" t="n">
         <v>0</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="2" t="n">
         <v>45958.684209632003</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="s">
@@ -1557,23 +1556,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24">
+    <row r="24">
+      <c r="A24" t="n">
         <v>0</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="2" t="n">
         <v>45958.684322089699</v>
       </c>
       <c r="E24" t="s">
         <v>44</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>121</v>
       </c>
       <c r="G24" t="s">
@@ -1583,23 +1582,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25">
+    <row r="25">
+      <c r="A25" t="n">
         <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="2" t="n">
         <v>45958.684389989503</v>
       </c>
       <c r="E25" t="s">
         <v>47</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>130</v>
       </c>
       <c r="G25" t="s">
@@ -1609,23 +1608,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26">
+    <row r="26">
+      <c r="A26" t="n">
         <v>0</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="2" t="n">
         <v>45958.684524802797</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="s">
@@ -1635,23 +1634,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27">
+    <row r="27">
+      <c r="A27" t="n">
         <v>0</v>
       </c>
       <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="2" t="n">
         <v>45958.684905007998</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>59</v>
       </c>
       <c r="G27" t="s">
@@ -1661,23 +1660,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="28">
+      <c r="A28" t="n">
         <v>0</v>
       </c>
       <c r="B28" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="2" t="n">
         <v>45958.684968170899</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>48</v>
       </c>
       <c r="G28" t="s">
@@ -1687,23 +1686,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="29">
+      <c r="A29" t="n">
         <v>0</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="2" t="n">
         <v>45958.685067698403</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>95</v>
       </c>
       <c r="G29" t="s">
@@ -1713,23 +1712,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="30">
+      <c r="A30" t="n">
         <v>0</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="2" t="n">
         <v>45958.685166592397</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>64</v>
       </c>
       <c r="G30" t="s">
@@ -1739,23 +1738,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31">
+    <row r="31">
+      <c r="A31" t="n">
         <v>0</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="2" t="n">
         <v>45958.685324976199</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>93</v>
       </c>
       <c r="G31" t="s">
@@ -1765,23 +1764,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32">
+      <c r="A32" t="n">
         <v>0</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="1" t="n">
         <v>45958</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="2" t="n">
         <v>45958.685387673802</v>
       </c>
       <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>62</v>
       </c>
       <c r="G32" t="s">
@@ -1791,23 +1790,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33">
+    <row r="33">
+      <c r="A33" t="n">
         <v>0</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="2" t="n">
         <v>45959.385571423503</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="s">
@@ -1817,23 +1816,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="34">
+      <c r="A34" t="n">
         <v>0</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="2" t="n">
         <v>45959.385909921002</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="s">
@@ -1843,23 +1842,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="35">
+      <c r="A35" t="n">
         <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="2" t="n">
         <v>45960.491801712298</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="s">
@@ -1869,23 +1868,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="36">
+      <c r="A36" t="n">
         <v>0</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="2" t="n">
         <v>45960.491960884297</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>125</v>
       </c>
       <c r="G36" t="s">
@@ -1895,23 +1894,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="37">
+      <c r="A37" t="n">
         <v>0</v>
       </c>
       <c r="B37" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="2" t="n">
         <v>45960.492014117801</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>128</v>
       </c>
       <c r="G37" t="s">
@@ -1921,23 +1920,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="38">
+      <c r="A38" t="n">
         <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="2" t="n">
         <v>45960.492522578497</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>72</v>
       </c>
       <c r="G38" t="s">
@@ -1947,23 +1946,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39">
+    <row r="39">
+      <c r="A39" t="n">
         <v>0</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="2" t="n">
         <v>45960.4925716453</v>
       </c>
       <c r="E39" t="s">
         <v>47</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>92</v>
       </c>
       <c r="G39" t="s">
@@ -1973,23 +1972,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40">
+    <row r="40">
+      <c r="A40" t="n">
         <v>0</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="2" t="n">
         <v>45960.492643531601</v>
       </c>
       <c r="E40" t="s">
         <v>44</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>74</v>
       </c>
       <c r="G40" t="s">
@@ -1999,23 +1998,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41">
+    <row r="41">
+      <c r="A41" t="n">
         <v>0</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="2" t="n">
         <v>45960.492700254901</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>90</v>
       </c>
       <c r="G41" t="s">
@@ -2025,23 +2024,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42">
+    <row r="42">
+      <c r="A42" t="n">
         <v>0</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="2" t="n">
         <v>45965.485657138801</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="s">
@@ -2051,23 +2050,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43">
+    <row r="43">
+      <c r="A43" t="n">
         <v>0</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="2" t="n">
         <v>45965.485844846997</v>
       </c>
       <c r="E43" t="s">
         <v>44</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>80</v>
       </c>
       <c r="G43" t="s">
@@ -2077,23 +2076,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44">
+    <row r="44">
+      <c r="A44" t="n">
         <v>0</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="2" t="n">
         <v>45965.485890989898</v>
       </c>
       <c r="E44" t="s">
         <v>44</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>82</v>
       </c>
       <c r="G44" t="s">
@@ -2103,23 +2102,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45">
+    <row r="45">
+      <c r="A45" t="n">
         <v>0</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="2" t="n">
         <v>45965.485968485897</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="n">
         <v>87</v>
       </c>
       <c r="G45" t="s">
@@ -2129,23 +2128,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46">
+    <row r="46">
+      <c r="A46" t="n">
         <v>0</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="2" t="n">
         <v>45965.486001955702</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="n">
         <v>89</v>
       </c>
       <c r="G46" t="s">
@@ -2155,23 +2154,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47">
+    <row r="47">
+      <c r="A47" t="n">
         <v>0</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="2" t="n">
         <v>45965.486250549002</v>
       </c>
       <c r="E47" t="s">
         <v>44</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="n">
         <v>50</v>
       </c>
       <c r="G47" t="s">
@@ -2181,23 +2180,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48">
+    <row r="48">
+      <c r="A48" t="n">
         <v>0</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="2" t="n">
         <v>45965.486292492598</v>
       </c>
       <c r="E48" t="s">
         <v>44</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="n">
         <v>52</v>
       </c>
       <c r="G48" t="s">
@@ -2207,23 +2206,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49">
+    <row r="49">
+      <c r="A49" t="n">
         <v>0</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="2" t="n">
         <v>45965.486377312402</v>
       </c>
       <c r="E49" t="s">
         <v>47</v>
       </c>
-      <c r="F49">
+      <c r="F49" t="n">
         <v>54</v>
       </c>
       <c r="G49" t="s">
@@ -2233,23 +2232,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50">
+    <row r="50">
+      <c r="A50" t="n">
         <v>0</v>
       </c>
       <c r="B50" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="2" t="n">
         <v>45965.486404639203</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
       </c>
-      <c r="F50">
+      <c r="F50" t="n">
         <v>56</v>
       </c>
       <c r="G50" t="s">
@@ -2259,23 +2258,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51">
+    <row r="51">
+      <c r="A51" t="n">
         <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="1" t="n">
         <v>45974</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="2" t="n">
         <v>45974.411367086701</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="n">
         <v>3</v>
       </c>
       <c r="G51" t="s">
@@ -2285,23 +2284,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52">
+    <row r="52">
+      <c r="A52" t="n">
         <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="1" t="n">
         <v>45974</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="2" t="n">
         <v>45974.411416700903</v>
       </c>
       <c r="E52" t="s">
         <v>47</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="s">
@@ -2311,23 +2310,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53">
+    <row r="53">
+      <c r="A53" t="n">
         <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="2" t="n">
         <v>45975.537941231603</v>
       </c>
       <c r="E53" t="s">
         <v>44</v>
       </c>
-      <c r="F53">
+      <c r="F53" t="n">
         <v>2</v>
       </c>
       <c r="G53" t="s">
@@ -2337,23 +2336,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54">
+    <row r="54">
+      <c r="A54" t="n">
         <v>1</v>
       </c>
       <c r="B54" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="2" t="n">
         <v>45975.538157998897</v>
       </c>
       <c r="E54" t="s">
         <v>47</v>
       </c>
-      <c r="F54">
+      <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="s">
@@ -2363,23 +2362,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55">
+    <row r="55">
+      <c r="A55" t="n">
         <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="2" t="n">
         <v>45975.544261836498</v>
       </c>
       <c r="E55" t="s">
         <v>44</v>
       </c>
-      <c r="F55">
+      <c r="F55" t="n">
         <v>5</v>
       </c>
       <c r="G55" t="s">
@@ -2389,23 +2388,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56">
+    <row r="56">
+      <c r="A56" t="n">
         <v>1</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="2" t="n">
         <v>45975.544303050097</v>
       </c>
       <c r="E56" t="s">
         <v>47</v>
       </c>
-      <c r="F56">
+      <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="s">
@@ -2415,23 +2414,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57">
+    <row r="57">
+      <c r="A57" t="n">
         <v>1</v>
       </c>
       <c r="B57" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="2" t="n">
         <v>45975.544539589202</v>
       </c>
       <c r="E57" t="s">
         <v>44</v>
       </c>
-      <c r="F57">
+      <c r="F57" t="n">
         <v>110</v>
       </c>
       <c r="G57" t="s">
@@ -2441,23 +2440,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58">
+    <row r="58">
+      <c r="A58" t="n">
         <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="2" t="n">
         <v>45975.544575668398</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="n">
         <v>125</v>
       </c>
       <c r="G58" t="s">
@@ -2467,23 +2466,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59">
+    <row r="59">
+      <c r="A59" t="n">
         <v>1</v>
       </c>
       <c r="B59" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="2" t="n">
         <v>45989.657419278097</v>
       </c>
       <c r="E59" t="s">
         <v>44</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="s">
@@ -2493,23 +2492,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60">
+    <row r="60">
+      <c r="A60" t="n">
         <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="2" t="n">
         <v>45989.657464727003</v>
       </c>
       <c r="E60" t="s">
         <v>47</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="s">
@@ -2519,23 +2518,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61">
+    <row r="61">
+      <c r="A61" t="n">
         <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="2" t="n">
         <v>45989.657658854201</v>
       </c>
       <c r="E61" t="s">
         <v>44</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="n">
         <v>2</v>
       </c>
       <c r="G61" t="s">
@@ -2545,23 +2544,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62">
+    <row r="62">
+      <c r="A62" t="n">
         <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="2" t="n">
         <v>45989.657725292898</v>
       </c>
       <c r="E62" t="s">
         <v>47</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="s">
@@ -2571,23 +2570,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63">
+    <row r="63">
+      <c r="A63" t="n">
         <v>1</v>
       </c>
       <c r="B63" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="2" t="n">
         <v>45989.657879157297</v>
       </c>
       <c r="E63" t="s">
         <v>44</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="n">
         <v>117</v>
       </c>
       <c r="G63" t="s">
@@ -2597,23 +2596,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64">
+    <row r="64">
+      <c r="A64" t="n">
         <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="2" t="n">
         <v>45989.657918513098</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="n">
         <v>126</v>
       </c>
       <c r="G64" t="s">
@@ -2623,23 +2622,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65">
+    <row r="65">
+      <c r="A65" t="n">
         <v>1</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="2" t="n">
         <v>45989.658742763997</v>
       </c>
       <c r="E65" t="s">
         <v>44</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="n">
         <v>2</v>
       </c>
       <c r="G65" t="s">
@@ -2649,23 +2648,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66">
+    <row r="66">
+      <c r="A66" t="n">
         <v>1</v>
       </c>
       <c r="B66" t="s">
         <v>114</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="2" t="n">
         <v>46030.597367625</v>
       </c>
       <c r="E66" t="s">
         <v>115</v>
       </c>
-      <c r="F66">
+      <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="s">
@@ -2675,23 +2674,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67">
+    <row r="67">
+      <c r="A67" t="n">
         <v>1</v>
       </c>
       <c r="B67" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="2" t="n">
         <v>46030.597429351699</v>
       </c>
       <c r="E67" t="s">
         <v>118</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="s">
@@ -2701,23 +2700,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68">
+    <row r="68">
+      <c r="A68" t="n">
         <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>119</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="2" t="n">
         <v>46030.597768818101</v>
       </c>
       <c r="E68" t="s">
         <v>115</v>
       </c>
-      <c r="F68">
+      <c r="F68" t="n">
         <v>120</v>
       </c>
       <c r="G68" t="s">
@@ -2727,23 +2726,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69">
+    <row r="69">
+      <c r="A69" t="n">
         <v>1</v>
       </c>
       <c r="B69" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="2" t="n">
         <v>46030.597819244598</v>
       </c>
       <c r="E69" t="s">
         <v>118</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="n">
         <v>125</v>
       </c>
       <c r="G69" t="s">
@@ -2753,23 +2752,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70">
+    <row r="70">
+      <c r="A70" t="n">
         <v>1</v>
       </c>
       <c r="B70" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="2" t="n">
         <v>46030.5981109887</v>
       </c>
       <c r="E70" t="s">
         <v>115</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="n">
         <v>2</v>
       </c>
       <c r="G70" t="s">
@@ -2779,23 +2778,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71">
+    <row r="71">
+      <c r="A71" t="n">
         <v>1</v>
       </c>
       <c r="B71" t="s">
         <v>121</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="2" t="n">
         <v>46030.598165269199</v>
       </c>
       <c r="E71" t="s">
         <v>118</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="s">
@@ -2805,23 +2804,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72">
+    <row r="72">
+      <c r="A72" t="n">
         <v>1</v>
       </c>
       <c r="B72" t="s">
         <v>122</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="2" t="n">
         <v>46030.5985355347</v>
       </c>
       <c r="E72" t="s">
         <v>115</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="s">
@@ -2831,23 +2830,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73">
+    <row r="73">
+      <c r="A73" t="n">
         <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="2" t="n">
         <v>46030.598729730598</v>
       </c>
       <c r="E73" t="s">
         <v>115</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="s">
@@ -2857,23 +2856,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74">
+    <row r="74">
+      <c r="A74" t="n">
         <v>1</v>
       </c>
       <c r="B74" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="2" t="n">
         <v>46030.598804364497</v>
       </c>
       <c r="E74" t="s">
         <v>118</v>
       </c>
-      <c r="F74">
+      <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="s">
@@ -2883,23 +2882,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75">
+    <row r="75">
+      <c r="A75" t="n">
         <v>1</v>
       </c>
       <c r="B75" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="2" t="n">
         <v>46030.598952235603</v>
       </c>
       <c r="E75" t="s">
         <v>115</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="n">
         <v>122</v>
       </c>
       <c r="G75" t="s">
@@ -2909,23 +2908,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76">
+    <row r="76">
+      <c r="A76" t="n">
         <v>1</v>
       </c>
       <c r="B76" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="2" t="n">
         <v>46030.5989977875</v>
       </c>
       <c r="E76" t="s">
         <v>118</v>
       </c>
-      <c r="F76">
+      <c r="F76" t="n">
         <v>127</v>
       </c>
       <c r="G76" t="s">
@@ -2935,23 +2934,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77">
+    <row r="77">
+      <c r="A77" t="n">
         <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>121</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="2" t="n">
         <v>46030.5991297031</v>
       </c>
       <c r="E77" t="s">
         <v>115</v>
       </c>
-      <c r="F77">
+      <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="s">
@@ -2961,23 +2960,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78">
+    <row r="78">
+      <c r="A78" t="n">
         <v>1</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="2" t="n">
         <v>46030.599185763604</v>
       </c>
       <c r="E78" t="s">
         <v>118</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="s">
@@ -2987,23 +2986,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79">
+    <row r="79">
+      <c r="A79" t="n">
         <v>1</v>
       </c>
       <c r="B79" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="2" t="n">
         <v>46030.599461440201</v>
       </c>
       <c r="E79" t="s">
         <v>118</v>
       </c>
-      <c r="F79">
+      <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="s">
@@ -3013,23 +3012,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80">
+    <row r="80">
+      <c r="A80" t="n">
         <v>1</v>
       </c>
       <c r="B80" t="s">
         <v>122</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="2" t="n">
         <v>46030.6009521206</v>
       </c>
       <c r="E80" t="s">
         <v>115</v>
       </c>
-      <c r="F80">
+      <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="s">
@@ -3039,23 +3038,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81">
+    <row r="81">
+      <c r="A81" t="n">
         <v>1</v>
       </c>
       <c r="B81" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="2" t="n">
         <v>46030.601362099602</v>
       </c>
       <c r="E81" t="s">
         <v>115</v>
       </c>
-      <c r="F81">
+      <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="s">
@@ -3065,23 +3064,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82">
+    <row r="82">
+      <c r="A82" t="n">
         <v>1</v>
       </c>
       <c r="B82" t="s">
         <v>114</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="2" t="n">
         <v>46030.601397267797</v>
       </c>
       <c r="E82" t="s">
         <v>118</v>
       </c>
-      <c r="F82">
+      <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="s">
@@ -3091,23 +3090,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83">
+    <row r="83">
+      <c r="A83" t="n">
         <v>1</v>
       </c>
       <c r="B83" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="2" t="n">
         <v>46030.601664699498</v>
       </c>
       <c r="E83" t="s">
         <v>115</v>
       </c>
-      <c r="F83">
+      <c r="F83" t="n">
         <v>124</v>
       </c>
       <c r="G83" t="s">
@@ -3117,23 +3116,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84">
+    <row r="84">
+      <c r="A84" t="n">
         <v>1</v>
       </c>
       <c r="B84" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="2" t="n">
         <v>46030.601707849899</v>
       </c>
       <c r="E84" t="s">
         <v>118</v>
       </c>
-      <c r="F84">
+      <c r="F84" t="n">
         <v>125</v>
       </c>
       <c r="G84" t="s">
@@ -3143,23 +3142,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85">
+    <row r="85">
+      <c r="A85" t="n">
         <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>121</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="2" t="n">
         <v>46030.601880503098</v>
       </c>
       <c r="E85" t="s">
         <v>115</v>
       </c>
-      <c r="F85">
+      <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="s">
@@ -3169,23 +3168,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86">
+    <row r="86">
+      <c r="A86" t="n">
         <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>121</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="2" t="n">
         <v>46030.601922228001</v>
       </c>
       <c r="E86" t="s">
         <v>118</v>
       </c>
-      <c r="F86">
+      <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="s">
@@ -3195,23 +3194,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87">
+    <row r="87">
+      <c r="A87" t="n">
         <v>1</v>
       </c>
       <c r="B87" t="s">
         <v>122</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="2" t="n">
         <v>46030.602015028402</v>
       </c>
       <c r="E87" t="s">
         <v>115</v>
       </c>
-      <c r="F87">
+      <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="s">
@@ -3221,23 +3220,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88">
+    <row r="88">
+      <c r="A88" t="n">
         <v>1</v>
       </c>
       <c r="B88" t="s">
         <v>114</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="2" t="n">
         <v>46030.602325239699</v>
       </c>
       <c r="E88" t="s">
         <v>115</v>
       </c>
-      <c r="F88">
+      <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="s">
@@ -3247,23 +3246,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89">
+    <row r="89">
+      <c r="A89" t="n">
         <v>1</v>
       </c>
       <c r="B89" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="2" t="n">
         <v>46030.602364462902</v>
       </c>
       <c r="E89" t="s">
         <v>118</v>
       </c>
-      <c r="F89">
+      <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="s">
@@ -3273,23 +3272,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90">
+    <row r="90">
+      <c r="A90" t="n">
         <v>1</v>
       </c>
       <c r="B90" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="2" t="n">
         <v>46030.602432747299</v>
       </c>
       <c r="E90" t="s">
         <v>115</v>
       </c>
-      <c r="F90">
+      <c r="F90" t="n">
         <v>125</v>
       </c>
       <c r="G90" t="s">
@@ -3299,23 +3298,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91">
+    <row r="91">
+      <c r="A91" t="n">
         <v>1</v>
       </c>
       <c r="B91" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C91" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="2" t="n">
         <v>46030.602474245497</v>
       </c>
       <c r="E91" t="s">
         <v>118</v>
       </c>
-      <c r="F91">
+      <c r="F91" t="n">
         <v>125</v>
       </c>
       <c r="G91" t="s">
@@ -3325,23 +3324,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92">
+    <row r="92">
+      <c r="A92" t="n">
         <v>1</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="2" t="n">
         <v>46030.602583176304</v>
       </c>
       <c r="E92" t="s">
         <v>115</v>
       </c>
-      <c r="F92">
+      <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="s">
@@ -3351,23 +3350,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93">
+    <row r="93">
+      <c r="A93" t="n">
         <v>1</v>
       </c>
       <c r="B93" t="s">
         <v>121</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="2" t="n">
         <v>46030.602620265403</v>
       </c>
       <c r="E93" t="s">
         <v>118</v>
       </c>
-      <c r="F93">
+      <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="s">
@@ -3377,23 +3376,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94">
+    <row r="94">
+      <c r="A94" t="n">
         <v>1</v>
       </c>
       <c r="B94" t="s">
         <v>122</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="2" t="n">
         <v>46030.602707964201</v>
       </c>
       <c r="E94" t="s">
         <v>115</v>
       </c>
-      <c r="F94">
+      <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="s">
@@ -3403,23 +3402,23 @@
         <v>117</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95">
+    <row r="95">
+      <c r="A95" t="n">
         <v>2</v>
       </c>
       <c r="B95" t="s">
         <v>126</v>
       </c>
-      <c r="C95" s="1">
+      <c r="C95" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="2" t="n">
         <v>46034.442400281303</v>
       </c>
       <c r="E95" t="s">
         <v>127</v>
       </c>
-      <c r="F95">
+      <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="s">
@@ -3429,23 +3428,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96">
+    <row r="96">
+      <c r="A96" t="n">
         <v>2</v>
       </c>
       <c r="B96" t="s">
         <v>126</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="2" t="n">
         <v>46034.442454999</v>
       </c>
       <c r="E96" t="s">
         <v>130</v>
       </c>
-      <c r="F96">
+      <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="s">
@@ -3455,23 +3454,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97">
+    <row r="97">
+      <c r="A97" t="n">
         <v>2</v>
       </c>
       <c r="B97" t="s">
         <v>131</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="2" t="n">
         <v>46034.442543972596</v>
       </c>
       <c r="E97" t="s">
         <v>127</v>
       </c>
-      <c r="F97">
+      <c r="F97" t="n">
         <v>126</v>
       </c>
       <c r="G97" t="s">
@@ -3481,23 +3480,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98">
+    <row r="98">
+      <c r="A98" t="n">
         <v>2</v>
       </c>
       <c r="B98" t="s">
         <v>131</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="2" t="n">
         <v>46034.442594817498</v>
       </c>
       <c r="E98" t="s">
         <v>130</v>
       </c>
-      <c r="F98">
+      <c r="F98" t="n">
         <v>126</v>
       </c>
       <c r="G98" t="s">
@@ -3507,23 +3506,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99">
+    <row r="99">
+      <c r="A99" t="n">
         <v>2</v>
       </c>
       <c r="B99" t="s">
         <v>132</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="2" t="n">
         <v>46034.4427237583</v>
       </c>
       <c r="E99" t="s">
         <v>127</v>
       </c>
-      <c r="F99">
+      <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="s">
@@ -3533,23 +3532,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100">
+    <row r="100">
+      <c r="A100" t="n">
         <v>2</v>
       </c>
       <c r="B100" t="s">
         <v>134</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="2" t="n">
         <v>46034.442922526003</v>
       </c>
       <c r="E100" t="s">
         <v>127</v>
       </c>
-      <c r="F100">
+      <c r="F100" t="n">
         <v>7</v>
       </c>
       <c r="G100" t="s">
@@ -3559,23 +3558,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101">
+    <row r="101">
+      <c r="A101" t="n">
         <v>2</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C101" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="2" t="n">
         <v>46034.442973844598</v>
       </c>
       <c r="E101" t="s">
         <v>130</v>
       </c>
-      <c r="F101">
+      <c r="F101" t="n">
         <v>15</v>
       </c>
       <c r="G101" t="s">
@@ -3585,23 +3584,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" t="n">
         <v>2</v>
       </c>
       <c r="B102" t="s">
         <v>136</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="2" t="n">
         <v>46034.443637573902</v>
       </c>
       <c r="E102" t="s">
         <v>127</v>
       </c>
-      <c r="F102">
+      <c r="F102" t="n">
         <v>5</v>
       </c>
       <c r="G102" t="s">
@@ -3611,23 +3610,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103">
+    <row r="103">
+      <c r="A103" t="n">
         <v>2</v>
       </c>
       <c r="B103" t="s">
         <v>136</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C103" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="2" t="n">
         <v>46034.443697991803</v>
       </c>
       <c r="E103" t="s">
         <v>130</v>
       </c>
-      <c r="F103">
+      <c r="F103" t="n">
         <v>13</v>
       </c>
       <c r="G103" t="s">
@@ -3637,23 +3636,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104">
+    <row r="104">
+      <c r="A104" t="n">
         <v>2</v>
       </c>
       <c r="B104" t="s">
         <v>137</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="2" t="n">
         <v>46034.539288706503</v>
       </c>
       <c r="E104" t="s">
         <v>138</v>
       </c>
-      <c r="F104">
+      <c r="F104" t="n">
         <v>40</v>
       </c>
       <c r="G104" t="s">
@@ -3663,23 +3662,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105">
+    <row r="105">
+      <c r="A105" t="n">
         <v>2</v>
       </c>
       <c r="B105" t="s">
         <v>140</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C105" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="2" t="n">
         <v>46034.5661824204</v>
       </c>
       <c r="E105" t="s">
         <v>127</v>
       </c>
-      <c r="F105">
+      <c r="F105" t="n">
         <v>6</v>
       </c>
       <c r="G105" t="s">
@@ -3689,23 +3688,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106">
+    <row r="106">
+      <c r="A106" t="n">
         <v>2</v>
       </c>
       <c r="B106" t="s">
         <v>140</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="2" t="n">
         <v>46034.566247390401</v>
       </c>
       <c r="E106" t="s">
         <v>130</v>
       </c>
-      <c r="F106">
+      <c r="F106" t="n">
         <v>15</v>
       </c>
       <c r="G106" t="s">
@@ -3715,23 +3714,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107">
+    <row r="107">
+      <c r="A107" t="n">
         <v>2</v>
       </c>
       <c r="B107" t="s">
         <v>134</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="2" t="n">
         <v>46038.6692860279</v>
       </c>
       <c r="E107" t="s">
         <v>127</v>
       </c>
-      <c r="F107">
+      <c r="F107" t="n">
         <v>9</v>
       </c>
       <c r="G107" t="s">
@@ -3741,23 +3740,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108">
+    <row r="108">
+      <c r="A108" t="n">
         <v>2</v>
       </c>
       <c r="B108" t="s">
         <v>134</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C108" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="2" t="n">
         <v>46038.669370621101</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
       </c>
-      <c r="F108">
+      <c r="F108" t="n">
         <v>17</v>
       </c>
       <c r="G108" t="s">
@@ -3767,23 +3766,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109">
+    <row r="109">
+      <c r="A109" t="n">
         <v>2</v>
       </c>
       <c r="B109" t="s">
         <v>136</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C109" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="2" t="n">
         <v>46038.669554267297</v>
       </c>
       <c r="E109" t="s">
         <v>127</v>
       </c>
-      <c r="F109">
+      <c r="F109" t="n">
         <v>7</v>
       </c>
       <c r="G109" t="s">
@@ -3793,23 +3792,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110">
+    <row r="110">
+      <c r="A110" t="n">
         <v>2</v>
       </c>
       <c r="B110" t="s">
         <v>136</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="2" t="n">
         <v>46038.669627650503</v>
       </c>
       <c r="E110" t="s">
         <v>130</v>
       </c>
-      <c r="F110">
+      <c r="F110" t="n">
         <v>14</v>
       </c>
       <c r="G110" t="s">
@@ -3819,23 +3818,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111">
+    <row r="111">
+      <c r="A111" t="n">
         <v>2</v>
       </c>
       <c r="B111" t="s">
         <v>140</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="2" t="n">
         <v>46038.6698742878</v>
       </c>
       <c r="E111" t="s">
         <v>127</v>
       </c>
-      <c r="F111">
+      <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="s">
@@ -3845,23 +3844,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112">
+    <row r="112">
+      <c r="A112" t="n">
         <v>2</v>
       </c>
       <c r="B112" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="2" t="n">
         <v>46038.669928152704</v>
       </c>
       <c r="E112" t="s">
         <v>130</v>
       </c>
-      <c r="F112">
+      <c r="F112" t="n">
         <v>15</v>
       </c>
       <c r="G112" t="s">
@@ -3871,23 +3870,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113">
+    <row r="113">
+      <c r="A113" t="n">
         <v>2</v>
       </c>
       <c r="B113" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C113" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="2" t="n">
         <v>46038.6707992843</v>
       </c>
       <c r="E113" t="s">
         <v>127</v>
       </c>
-      <c r="F113">
+      <c r="F113" t="n">
         <v>30</v>
       </c>
       <c r="G113" t="s">
@@ -3897,23 +3896,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114">
+    <row r="114">
+      <c r="A114" t="n">
         <v>2</v>
       </c>
       <c r="B114" t="s">
         <v>148</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="2" t="n">
         <v>46038.670836973499</v>
       </c>
       <c r="E114" t="s">
         <v>130</v>
       </c>
-      <c r="F114">
+      <c r="F114" t="n">
         <v>30</v>
       </c>
       <c r="G114" t="s">
@@ -3923,23 +3922,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115">
+    <row r="115">
+      <c r="A115" t="n">
         <v>2</v>
       </c>
       <c r="B115" t="s">
         <v>154</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="2" t="n">
         <v>46042.360163172401</v>
       </c>
       <c r="E115" t="s">
         <v>127</v>
       </c>
-      <c r="F115">
+      <c r="F115" t="n">
         <v>30</v>
       </c>
       <c r="G115" t="s">
@@ -3949,23 +3948,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116">
+    <row r="116">
+      <c r="A116" t="n">
         <v>2</v>
       </c>
       <c r="B116" t="s">
         <v>154</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="2" t="n">
         <v>46042.360217777801</v>
       </c>
       <c r="E116" t="s">
         <v>130</v>
       </c>
-      <c r="F116">
+      <c r="F116" t="n">
         <v>45</v>
       </c>
       <c r="G116" t="s">
@@ -3975,23 +3974,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117">
+    <row r="117">
+      <c r="A117" t="n">
         <v>2</v>
       </c>
       <c r="B117" t="s">
         <v>155</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="2" t="n">
         <v>46042.361174106802</v>
       </c>
       <c r="E117" t="s">
         <v>127</v>
       </c>
-      <c r="F117">
+      <c r="F117" t="n">
         <v>40</v>
       </c>
       <c r="G117" t="s">
@@ -4001,23 +4000,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118">
+    <row r="118">
+      <c r="A118" t="n">
         <v>2</v>
       </c>
       <c r="B118" t="s">
         <v>155</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="2" t="n">
         <v>46042.361259715202</v>
       </c>
       <c r="E118" t="s">
         <v>127</v>
       </c>
-      <c r="F118">
+      <c r="F118" t="n">
         <v>38</v>
       </c>
       <c r="G118" t="s">
@@ -4027,23 +4026,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119">
+    <row r="119">
+      <c r="A119" t="n">
         <v>2</v>
       </c>
       <c r="B119" t="s">
         <v>155</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="2" t="n">
         <v>46042.361303134297</v>
       </c>
       <c r="E119" t="s">
         <v>127</v>
       </c>
-      <c r="F119">
+      <c r="F119" t="n">
         <v>38</v>
       </c>
       <c r="G119" t="s">
@@ -4053,23 +4052,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120">
+    <row r="120">
+      <c r="A120" t="n">
         <v>2</v>
       </c>
       <c r="B120" t="s">
         <v>155</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C120" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="2" t="n">
         <v>46042.361404144598</v>
       </c>
       <c r="E120" t="s">
         <v>130</v>
       </c>
-      <c r="F120">
+      <c r="F120" t="n">
         <v>60</v>
       </c>
       <c r="G120" t="s">
@@ -4079,23 +4078,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121">
+    <row r="121">
+      <c r="A121" t="n">
         <v>2</v>
       </c>
       <c r="B121" t="s">
         <v>155</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C121" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="2" t="n">
         <v>46042.361443357302</v>
       </c>
       <c r="E121" t="s">
         <v>130</v>
       </c>
-      <c r="F121">
+      <c r="F121" t="n">
         <v>61</v>
       </c>
       <c r="G121" t="s">
@@ -4105,23 +4104,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122">
+    <row r="122">
+      <c r="A122" t="n">
         <v>2</v>
       </c>
       <c r="B122" t="s">
         <v>155</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C122" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="2" t="n">
         <v>46042.361489097799</v>
       </c>
       <c r="E122" t="s">
         <v>130</v>
       </c>
-      <c r="F122">
+      <c r="F122" t="n">
         <v>64</v>
       </c>
       <c r="G122" t="s">
@@ -4131,23 +4130,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123">
+    <row r="123">
+      <c r="A123" t="n">
         <v>2</v>
       </c>
       <c r="B123" t="s">
         <v>156</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C123" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="2" t="n">
         <v>46042.361928238002</v>
       </c>
       <c r="E123" t="s">
         <v>127</v>
       </c>
-      <c r="F123">
+      <c r="F123" t="n">
         <v>80</v>
       </c>
       <c r="G123" t="s">
@@ -4157,23 +4156,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124">
+    <row r="124">
+      <c r="A124" t="n">
         <v>2</v>
       </c>
       <c r="B124" t="s">
         <v>156</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C124" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="2" t="n">
         <v>46042.362212514498</v>
       </c>
       <c r="E124" t="s">
         <v>127</v>
       </c>
-      <c r="F124">
+      <c r="F124" t="n">
         <v>78.5</v>
       </c>
       <c r="G124" t="s">
@@ -4183,23 +4182,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125">
+    <row r="125">
+      <c r="A125" t="n">
         <v>2</v>
       </c>
       <c r="B125" t="s">
         <v>156</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C125" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="2" t="n">
         <v>46042.362270635203</v>
       </c>
       <c r="E125" t="s">
         <v>127</v>
       </c>
-      <c r="F125">
+      <c r="F125" t="n">
         <v>81.5</v>
       </c>
       <c r="G125" t="s">
@@ -4209,23 +4208,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126">
+    <row r="126">
+      <c r="A126" t="n">
         <v>2</v>
       </c>
       <c r="B126" t="s">
         <v>156</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="2" t="n">
         <v>46042.362343741297</v>
       </c>
       <c r="E126" t="s">
         <v>130</v>
       </c>
-      <c r="F126">
+      <c r="F126" t="n">
         <v>99.5</v>
       </c>
       <c r="G126" t="s">
@@ -4235,23 +4234,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127">
+    <row r="127">
+      <c r="A127" t="n">
         <v>2</v>
       </c>
       <c r="B127" t="s">
         <v>156</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="2" t="n">
         <v>46042.362396041899</v>
       </c>
       <c r="E127" t="s">
         <v>130</v>
       </c>
-      <c r="F127">
+      <c r="F127" t="n">
         <v>100.5</v>
       </c>
       <c r="G127" t="s">
@@ -4261,23 +4260,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128">
+    <row r="128">
+      <c r="A128" t="n">
         <v>2</v>
       </c>
       <c r="B128" t="s">
         <v>156</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="2" t="n">
         <v>46042.362431900103</v>
       </c>
       <c r="E128" t="s">
         <v>130</v>
       </c>
-      <c r="F128">
+      <c r="F128" t="n">
         <v>101</v>
       </c>
       <c r="G128" t="s">
@@ -4287,23 +4286,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129">
+    <row r="129">
+      <c r="A129" t="n">
         <v>2</v>
       </c>
       <c r="B129" t="s">
         <v>157</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="2" t="n">
         <v>46042.362576904197</v>
       </c>
       <c r="E129" t="s">
         <v>127</v>
       </c>
-      <c r="F129">
+      <c r="F129" t="n">
         <v>65</v>
       </c>
       <c r="G129" t="s">
@@ -4313,23 +4312,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130">
+    <row r="130">
+      <c r="A130" t="n">
         <v>2</v>
       </c>
       <c r="B130" t="s">
         <v>157</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="2" t="n">
         <v>46042.3626157908</v>
       </c>
       <c r="E130" t="s">
         <v>127</v>
       </c>
-      <c r="F130">
+      <c r="F130" t="n">
         <v>66.5</v>
       </c>
       <c r="G130" t="s">
@@ -4339,23 +4338,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131">
+    <row r="131">
+      <c r="A131" t="n">
         <v>2</v>
       </c>
       <c r="B131" t="s">
         <v>157</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="2" t="n">
         <v>46042.362653184799</v>
       </c>
       <c r="E131" t="s">
         <v>127</v>
       </c>
-      <c r="F131">
+      <c r="F131" t="n">
         <v>68.5</v>
       </c>
       <c r="G131" t="s">
@@ -4365,23 +4364,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132">
+    <row r="132">
+      <c r="A132" t="n">
         <v>2</v>
       </c>
       <c r="B132" t="s">
         <v>157</v>
       </c>
-      <c r="C132" s="1">
+      <c r="C132" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="2" t="n">
         <v>46042.362854254898</v>
       </c>
       <c r="E132" t="s">
         <v>130</v>
       </c>
-      <c r="F132">
+      <c r="F132" t="n">
         <v>89.5</v>
       </c>
       <c r="G132" t="s">
@@ -4391,23 +4390,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133">
+    <row r="133">
+      <c r="A133" t="n">
         <v>2</v>
       </c>
       <c r="B133" t="s">
         <v>157</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C133" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="2" t="n">
         <v>46042.362889967699</v>
       </c>
       <c r="E133" t="s">
         <v>130</v>
       </c>
-      <c r="F133">
+      <c r="F133" t="n">
         <v>92</v>
       </c>
       <c r="G133" t="s">
@@ -4417,23 +4416,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134">
+    <row r="134">
+      <c r="A134" t="n">
         <v>2</v>
       </c>
       <c r="B134" t="s">
         <v>157</v>
       </c>
-      <c r="C134" s="1">
+      <c r="C134" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="2" t="n">
         <v>46042.362965286797</v>
       </c>
       <c r="E134" t="s">
         <v>130</v>
       </c>
-      <c r="F134">
+      <c r="F134" t="n">
         <v>91.5</v>
       </c>
       <c r="G134" t="s">
@@ -4443,23 +4442,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135">
+    <row r="135">
+      <c r="A135" t="n">
         <v>2</v>
       </c>
       <c r="B135" t="s">
         <v>162</v>
       </c>
-      <c r="C135" s="1">
+      <c r="C135" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="2" t="n">
         <v>46045.4466951266</v>
       </c>
       <c r="E135" t="s">
         <v>163</v>
       </c>
-      <c r="F135">
+      <c r="F135" t="n">
         <v>12</v>
       </c>
       <c r="G135" t="s">
@@ -4469,23 +4468,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136">
+    <row r="136">
+      <c r="A136" t="n">
         <v>2</v>
       </c>
       <c r="B136" t="s">
         <v>162</v>
       </c>
-      <c r="C136" s="1">
+      <c r="C136" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="2" t="n">
         <v>46045.446743292603</v>
       </c>
       <c r="E136" t="s">
         <v>166</v>
       </c>
-      <c r="F136">
+      <c r="F136" t="n">
         <v>19</v>
       </c>
       <c r="G136" t="s">
@@ -4495,23 +4494,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A137">
+    <row r="137">
+      <c r="A137" t="n">
         <v>2</v>
       </c>
       <c r="B137" t="s">
         <v>167</v>
       </c>
-      <c r="C137" s="1">
+      <c r="C137" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="2" t="n">
         <v>46045.4469611491</v>
       </c>
       <c r="E137" t="s">
         <v>163</v>
       </c>
-      <c r="F137">
+      <c r="F137" t="n">
         <v>10</v>
       </c>
       <c r="G137" t="s">
@@ -4521,23 +4520,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138">
+    <row r="138">
+      <c r="A138" t="n">
         <v>2</v>
       </c>
       <c r="B138" t="s">
         <v>167</v>
       </c>
-      <c r="C138" s="1">
+      <c r="C138" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="2" t="n">
         <v>46045.4469929935</v>
       </c>
       <c r="E138" t="s">
         <v>166</v>
       </c>
-      <c r="F138">
+      <c r="F138" t="n">
         <v>15</v>
       </c>
       <c r="G138" t="s">
@@ -4547,23 +4546,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A139">
+    <row r="139">
+      <c r="A139" t="n">
         <v>2</v>
       </c>
       <c r="B139" t="s">
         <v>168</v>
       </c>
-      <c r="C139" s="1">
+      <c r="C139" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="2" t="n">
         <v>46045.447238846602</v>
       </c>
       <c r="E139" t="s">
         <v>163</v>
       </c>
-      <c r="F139">
+      <c r="F139" t="n">
         <v>2</v>
       </c>
       <c r="G139" t="s">
@@ -4573,23 +4572,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A140">
+    <row r="140">
+      <c r="A140" t="n">
         <v>2</v>
       </c>
       <c r="B140" t="s">
         <v>168</v>
       </c>
-      <c r="C140" s="1">
+      <c r="C140" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="2" t="n">
         <v>46045.447271689198</v>
       </c>
       <c r="E140" t="s">
         <v>166</v>
       </c>
-      <c r="F140">
+      <c r="F140" t="n">
         <v>8</v>
       </c>
       <c r="G140" t="s">
@@ -4599,23 +4598,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141">
+    <row r="141">
+      <c r="A141" t="n">
         <v>2</v>
       </c>
       <c r="B141" t="s">
         <v>169</v>
       </c>
-      <c r="C141" s="1">
+      <c r="C141" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="2" t="n">
         <v>46045.447571199198</v>
       </c>
       <c r="E141" t="s">
         <v>163</v>
       </c>
-      <c r="F141">
+      <c r="F141" t="n">
         <v>10</v>
       </c>
       <c r="G141" t="s">
@@ -4625,23 +4624,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142">
+    <row r="142">
+      <c r="A142" t="n">
         <v>2</v>
       </c>
       <c r="B142" t="s">
         <v>169</v>
       </c>
-      <c r="C142" s="1">
+      <c r="C142" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="2" t="n">
         <v>46045.4476158369</v>
       </c>
       <c r="E142" t="s">
         <v>166</v>
       </c>
-      <c r="F142">
+      <c r="F142" t="n">
         <v>15</v>
       </c>
       <c r="G142" t="s">
@@ -4651,23 +4650,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143">
+    <row r="143">
+      <c r="A143" t="n">
         <v>2</v>
       </c>
       <c r="B143" t="s">
         <v>171</v>
       </c>
-      <c r="C143" s="1">
+      <c r="C143" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="2" t="n">
         <v>46045.448139208398</v>
       </c>
       <c r="E143" t="s">
         <v>163</v>
       </c>
-      <c r="F143">
+      <c r="F143" t="n">
         <v>3</v>
       </c>
       <c r="G143" t="s">
@@ -4677,23 +4676,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144">
+    <row r="144">
+      <c r="A144" t="n">
         <v>2</v>
       </c>
       <c r="B144" t="s">
         <v>171</v>
       </c>
-      <c r="C144" s="1">
+      <c r="C144" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="2" t="n">
         <v>46045.448177964099</v>
       </c>
       <c r="E144" t="s">
         <v>166</v>
       </c>
-      <c r="F144">
+      <c r="F144" t="n">
         <v>10</v>
       </c>
       <c r="G144" t="s">
@@ -4703,23 +4702,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A145">
+    <row r="145">
+      <c r="A145" t="n">
         <v>3</v>
       </c>
       <c r="B145" t="s">
         <v>173</v>
       </c>
-      <c r="C145" s="1">
+      <c r="C145" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="2" t="n">
         <v>46047.419832948697</v>
       </c>
       <c r="E145" t="s">
         <v>163</v>
       </c>
-      <c r="F145">
+      <c r="F145" t="n">
         <v>50</v>
       </c>
       <c r="G145" t="s">
@@ -4729,23 +4728,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A146">
+    <row r="146">
+      <c r="A146" t="n">
         <v>2</v>
       </c>
       <c r="B146" t="s">
         <v>174</v>
       </c>
-      <c r="C146" s="1">
+      <c r="C146" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="2" t="n">
         <v>46047.445065262698</v>
       </c>
       <c r="E146" t="s">
         <v>163</v>
       </c>
-      <c r="F146">
+      <c r="F146" t="n">
         <v>30</v>
       </c>
       <c r="G146" t="s">
@@ -4755,23 +4754,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147">
+    <row r="147">
+      <c r="A147" t="n">
         <v>2</v>
       </c>
       <c r="B147" t="s">
         <v>174</v>
       </c>
-      <c r="C147" s="1">
+      <c r="C147" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="2" t="n">
         <v>46047.445106826701</v>
       </c>
       <c r="E147" t="s">
         <v>166</v>
       </c>
-      <c r="F147">
+      <c r="F147" t="n">
         <v>30</v>
       </c>
       <c r="G147" t="s">
@@ -4781,23 +4780,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A148">
+    <row r="148">
+      <c r="A148" t="n">
         <v>2</v>
       </c>
       <c r="B148" t="s">
         <v>179</v>
       </c>
-      <c r="C148" s="1">
+      <c r="C148" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="2" t="n">
         <v>46049.244785984898</v>
       </c>
       <c r="E148" t="s">
         <v>163</v>
       </c>
-      <c r="F148">
+      <c r="F148" t="n">
         <v>37</v>
       </c>
       <c r="G148" t="s">
@@ -4807,23 +4806,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A149">
+    <row r="149">
+      <c r="A149" t="n">
         <v>2</v>
       </c>
       <c r="B149" t="s">
         <v>179</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C149" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="2" t="n">
         <v>46049.245240876902</v>
       </c>
       <c r="E149" t="s">
         <v>166</v>
       </c>
-      <c r="F149">
+      <c r="F149" t="n">
         <v>45</v>
       </c>
       <c r="G149" t="s">
@@ -4833,23 +4832,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A150">
+    <row r="150">
+      <c r="A150" t="n">
         <v>2</v>
       </c>
       <c r="B150" t="s">
         <v>171</v>
       </c>
-      <c r="C150" s="1">
+      <c r="C150" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="2" t="n">
         <v>46049.245369569697</v>
       </c>
       <c r="E150" t="s">
         <v>163</v>
       </c>
-      <c r="F150">
+      <c r="F150" t="n">
         <v>6</v>
       </c>
       <c r="G150" t="s">
@@ -4859,23 +4858,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A151">
+    <row r="151">
+      <c r="A151" t="n">
         <v>2</v>
       </c>
       <c r="B151" t="s">
         <v>171</v>
       </c>
-      <c r="C151" s="1">
+      <c r="C151" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="2" t="n">
         <v>46049.245406563801</v>
       </c>
       <c r="E151" t="s">
         <v>166</v>
       </c>
-      <c r="F151">
+      <c r="F151" t="n">
         <v>9</v>
       </c>
       <c r="G151" t="s">
@@ -4885,23 +4884,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A152">
+    <row r="152">
+      <c r="A152" t="n">
         <v>2</v>
       </c>
       <c r="B152" t="s">
         <v>180</v>
       </c>
-      <c r="C152" s="1">
+      <c r="C152" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="2" t="n">
         <v>46049.2458257244</v>
       </c>
       <c r="E152" t="s">
         <v>163</v>
       </c>
-      <c r="F152">
+      <c r="F152" t="n">
         <v>42</v>
       </c>
       <c r="G152" t="s">
@@ -4911,23 +4910,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A153">
+    <row r="153">
+      <c r="A153" t="n">
         <v>2</v>
       </c>
       <c r="B153" t="s">
         <v>180</v>
       </c>
-      <c r="C153" s="1">
+      <c r="C153" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="2" t="n">
         <v>46049.245875696397</v>
       </c>
       <c r="E153" t="s">
         <v>163</v>
       </c>
-      <c r="F153">
+      <c r="F153" t="n">
         <v>43</v>
       </c>
       <c r="G153" t="s">
@@ -4937,23 +4936,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A154">
+    <row r="154">
+      <c r="A154" t="n">
         <v>2</v>
       </c>
       <c r="B154" t="s">
         <v>180</v>
       </c>
-      <c r="C154" s="1">
+      <c r="C154" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="2" t="n">
         <v>46049.245916874301</v>
       </c>
       <c r="E154" t="s">
         <v>163</v>
       </c>
-      <c r="F154">
+      <c r="F154" t="n">
         <v>43.5</v>
       </c>
       <c r="G154" t="s">
@@ -4963,23 +4962,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A155">
+    <row r="155">
+      <c r="A155" t="n">
         <v>2</v>
       </c>
       <c r="B155" t="s">
         <v>180</v>
       </c>
-      <c r="C155" s="1">
+      <c r="C155" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="2" t="n">
         <v>46049.246014391902</v>
       </c>
       <c r="E155" t="s">
         <v>166</v>
       </c>
-      <c r="F155">
+      <c r="F155" t="n">
         <v>62.5</v>
       </c>
       <c r="G155" t="s">
@@ -4989,23 +4988,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A156">
+    <row r="156">
+      <c r="A156" t="n">
         <v>2</v>
       </c>
       <c r="B156" t="s">
         <v>180</v>
       </c>
-      <c r="C156" s="1">
+      <c r="C156" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="2" t="n">
         <v>46049.246069772198</v>
       </c>
       <c r="E156" t="s">
         <v>166</v>
       </c>
-      <c r="F156">
+      <c r="F156" t="n">
         <v>63.5</v>
       </c>
       <c r="G156" t="s">
@@ -5015,23 +5014,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A157">
+    <row r="157">
+      <c r="A157" t="n">
         <v>2</v>
       </c>
       <c r="B157" t="s">
         <v>180</v>
       </c>
-      <c r="C157" s="1">
+      <c r="C157" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="2" t="n">
         <v>46049.2461241977</v>
       </c>
       <c r="E157" t="s">
         <v>166</v>
       </c>
-      <c r="F157">
+      <c r="F157" t="n">
         <v>64</v>
       </c>
       <c r="G157" t="s">
@@ -5041,23 +5040,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158">
+    <row r="158">
+      <c r="A158" t="n">
         <v>2</v>
       </c>
       <c r="B158" t="s">
         <v>189</v>
       </c>
-      <c r="C158" s="1">
+      <c r="C158" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="2" t="n">
         <v>46054.373075639203</v>
       </c>
       <c r="E158" t="s">
         <v>163</v>
       </c>
-      <c r="F158">
+      <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="s">
@@ -5067,23 +5066,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159">
+    <row r="159">
+      <c r="A159" t="n">
         <v>2</v>
       </c>
       <c r="B159" t="s">
         <v>189</v>
       </c>
-      <c r="C159" s="1">
+      <c r="C159" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="2" t="n">
         <v>46054.3731330847</v>
       </c>
       <c r="E159" t="s">
         <v>166</v>
       </c>
-      <c r="F159">
+      <c r="F159" t="n">
         <v>0</v>
       </c>
       <c r="G159" t="s">
@@ -5093,23 +5092,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A160">
+    <row r="160">
+      <c r="A160" t="n">
         <v>2</v>
       </c>
       <c r="B160" t="s">
         <v>191</v>
       </c>
-      <c r="C160" s="1">
+      <c r="C160" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="2" t="n">
         <v>46054.373350648799</v>
       </c>
       <c r="E160" t="s">
         <v>163</v>
       </c>
-      <c r="F160">
+      <c r="F160" t="n">
         <v>127</v>
       </c>
       <c r="G160" t="s">
@@ -5119,23 +5118,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161">
+    <row r="161">
+      <c r="A161" t="n">
         <v>2</v>
       </c>
       <c r="B161" t="s">
         <v>191</v>
       </c>
-      <c r="C161" s="1">
+      <c r="C161" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="2" t="n">
         <v>46054.373401007098</v>
       </c>
       <c r="E161" t="s">
         <v>166</v>
       </c>
-      <c r="F161">
+      <c r="F161" t="n">
         <v>127</v>
       </c>
       <c r="G161" t="s">
@@ -5145,23 +5144,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A162">
+    <row r="162">
+      <c r="A162" t="n">
         <v>2</v>
       </c>
       <c r="B162" t="s">
         <v>192</v>
       </c>
-      <c r="C162" s="1">
+      <c r="C162" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="2" t="n">
         <v>46054.374090033103</v>
       </c>
       <c r="E162" t="s">
         <v>163</v>
       </c>
-      <c r="F162">
+      <c r="F162" t="n">
         <v>0</v>
       </c>
       <c r="G162" t="s">
@@ -5171,23 +5170,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163">
+    <row r="163">
+      <c r="A163" t="n">
         <v>2</v>
       </c>
       <c r="B163" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="1">
+      <c r="C163" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="2" t="n">
         <v>46054.374287611798</v>
       </c>
       <c r="E163" t="s">
         <v>163</v>
       </c>
-      <c r="F163">
+      <c r="F163" t="n">
         <v>14</v>
       </c>
       <c r="G163" t="s">
@@ -5197,23 +5196,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A164">
+    <row r="164">
+      <c r="A164" t="n">
         <v>2</v>
       </c>
       <c r="B164" t="s">
         <v>162</v>
       </c>
-      <c r="C164" s="1">
+      <c r="C164" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="2" t="n">
         <v>46054.374329414699</v>
       </c>
       <c r="E164" t="s">
         <v>166</v>
       </c>
-      <c r="F164">
+      <c r="F164" t="n">
         <v>20</v>
       </c>
       <c r="G164" t="s">
@@ -5223,23 +5222,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A165">
+    <row r="165">
+      <c r="A165" t="n">
         <v>2</v>
       </c>
       <c r="B165" t="s">
         <v>167</v>
       </c>
-      <c r="C165" s="1">
+      <c r="C165" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D165" s="2">
+      <c r="D165" s="2" t="n">
         <v>46054.375393863796</v>
       </c>
       <c r="E165" t="s">
         <v>163</v>
       </c>
-      <c r="F165">
+      <c r="F165" t="n">
         <v>12</v>
       </c>
       <c r="G165" t="s">
@@ -5249,23 +5248,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A166">
+    <row r="166">
+      <c r="A166" t="n">
         <v>2</v>
       </c>
       <c r="B166" t="s">
         <v>167</v>
       </c>
-      <c r="C166" s="1">
+      <c r="C166" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="2" t="n">
         <v>46054.375432872897</v>
       </c>
       <c r="E166" t="s">
         <v>166</v>
       </c>
-      <c r="F166">
+      <c r="F166" t="n">
         <v>17</v>
       </c>
       <c r="G166" t="s">
@@ -5275,23 +5274,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A167">
+    <row r="167">
+      <c r="A167" t="n">
         <v>2</v>
       </c>
       <c r="B167" t="s">
         <v>168</v>
       </c>
-      <c r="C167" s="1">
+      <c r="C167" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="2" t="n">
         <v>46054.375730488297</v>
       </c>
       <c r="E167" t="s">
         <v>163</v>
       </c>
-      <c r="F167">
+      <c r="F167" t="n">
         <v>4</v>
       </c>
       <c r="G167" t="s">
@@ -5301,23 +5300,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A168">
+    <row r="168">
+      <c r="A168" t="n">
         <v>2</v>
       </c>
       <c r="B168" t="s">
         <v>168</v>
       </c>
-      <c r="C168" s="1">
+      <c r="C168" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="2" t="n">
         <v>46054.375768050602</v>
       </c>
       <c r="E168" t="s">
         <v>166</v>
       </c>
-      <c r="F168">
+      <c r="F168" t="n">
         <v>9</v>
       </c>
       <c r="G168" t="s">
@@ -5327,23 +5326,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A169">
+    <row r="169">
+      <c r="A169" t="n">
         <v>2</v>
       </c>
       <c r="B169" t="s">
         <v>179</v>
       </c>
-      <c r="C169" s="1">
+      <c r="C169" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="2" t="n">
         <v>46054.375964423198</v>
       </c>
       <c r="E169" t="s">
         <v>163</v>
       </c>
-      <c r="F169">
+      <c r="F169" t="n">
         <v>45</v>
       </c>
       <c r="G169" t="s">
@@ -5353,23 +5352,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A170">
+    <row r="170">
+      <c r="A170" t="n">
         <v>2</v>
       </c>
       <c r="B170" t="s">
         <v>179</v>
       </c>
-      <c r="C170" s="1">
+      <c r="C170" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="2" t="n">
         <v>46054.375998781703</v>
       </c>
       <c r="E170" t="s">
         <v>166</v>
       </c>
-      <c r="F170">
+      <c r="F170" t="n">
         <v>45</v>
       </c>
       <c r="G170" t="s">
@@ -5379,23 +5378,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A171">
+    <row r="171">
+      <c r="A171" t="n">
         <v>2</v>
       </c>
       <c r="B171" t="s">
         <v>171</v>
       </c>
-      <c r="C171" s="1">
+      <c r="C171" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="2" t="n">
         <v>46054.377199965696</v>
       </c>
       <c r="E171" t="s">
         <v>163</v>
       </c>
-      <c r="F171">
+      <c r="F171" t="n">
         <v>9</v>
       </c>
       <c r="G171" t="s">
@@ -5405,23 +5404,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A172">
+    <row r="172">
+      <c r="A172" t="n">
         <v>2</v>
       </c>
       <c r="B172" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="1">
+      <c r="C172" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D172" s="2">
+      <c r="D172" s="2" t="n">
         <v>46054.3772267725</v>
       </c>
       <c r="E172" t="s">
         <v>166</v>
       </c>
-      <c r="F172">
+      <c r="F172" t="n">
         <v>9</v>
       </c>
       <c r="G172" t="s">
@@ -5431,23 +5430,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A173">
+    <row r="173">
+      <c r="A173" t="n">
         <v>2</v>
       </c>
       <c r="B173" t="s">
         <v>194</v>
       </c>
-      <c r="C173" s="1">
+      <c r="C173" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="2" t="n">
         <v>46054.377639929997</v>
       </c>
       <c r="E173" t="s">
         <v>138</v>
       </c>
-      <c r="F173">
+      <c r="F173" t="n">
         <v>60</v>
       </c>
       <c r="G173" t="s">
@@ -5457,23 +5456,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A174">
+    <row r="174">
+      <c r="A174" t="n">
         <v>2</v>
       </c>
       <c r="B174" t="s">
         <v>169</v>
       </c>
-      <c r="C174" s="1">
+      <c r="C174" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="2" t="n">
         <v>46054.378020765304</v>
       </c>
       <c r="E174" t="s">
         <v>163</v>
       </c>
-      <c r="F174">
+      <c r="F174" t="n">
         <v>11</v>
       </c>
       <c r="G174" t="s">
@@ -5483,23 +5482,23 @@
         <v>165</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A175">
+    <row r="175">
+      <c r="A175" t="n">
         <v>2</v>
       </c>
       <c r="B175" t="s">
         <v>169</v>
       </c>
-      <c r="C175" s="1">
+      <c r="C175" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="2" t="n">
         <v>46054.378060841897</v>
       </c>
       <c r="E175" t="s">
         <v>166</v>
       </c>
-      <c r="F175">
+      <c r="F175" t="n">
         <v>15</v>
       </c>
       <c r="G175" t="s">
@@ -5516,14 +5515,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -5546,1107 +5545,1130 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>6.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>9</v>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>7.5</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>6.5</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>56</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>58</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>6.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>60</v>
       </c>
       <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>8.5</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>62</v>
       </c>
       <c r="B11" t="s">
         <v>63</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>64</v>
       </c>
       <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>7</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>72</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>8</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>7</v>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>7</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>8.5</v>
       </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>80</v>
       </c>
       <c r="B19" t="s">
         <v>81</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>9</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20" t="s">
         <v>83</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>7.5</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" t="s">
         <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>8.5</v>
       </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>87</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>7.5</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>6.5</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>3</v>
       </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23">
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24" t="s">
         <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>91</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>7.5</v>
       </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>7</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>4</v>
       </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>95</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>9</v>
       </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>9</v>
       </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
         <v>3</v>
       </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>8</v>
       </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
         <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>8</v>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>103</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>8.5</v>
       </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>2</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
         <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>7.5</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>3</v>
       </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="F31">
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>7.5</v>
       </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="F32">
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
         <v>3</v>
       </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>7</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>111</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>7</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>4</v>
       </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
         <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>113</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>7</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="F35">
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36" t="s">
         <v>124</v>
       </c>
       <c r="B36" t="s">
         <v>125</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>8</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>4</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>3</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37" t="s">
         <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>143</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>6.5</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>3</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>3</v>
       </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
         <v>144</v>
       </c>
       <c r="B38" t="s">
         <v>145</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="n">
         <v>7.5</v>
       </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38">
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>3</v>
       </c>
-      <c r="G38">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39" t="s">
         <v>146</v>
       </c>
       <c r="B39" t="s">
         <v>147</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="n">
         <v>6</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>4</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
         <v>150</v>
       </c>
       <c r="B40" t="s">
         <v>151</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="n">
         <v>7.5</v>
       </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40">
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
         <v>3</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>4</v>
       </c>
-      <c r="G40">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41" t="s">
         <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>153</v>
       </c>
-      <c r="C41">
+      <c r="C41" t="n">
         <v>5</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>3</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>4</v>
       </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
         <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>159</v>
       </c>
-      <c r="C42">
+      <c r="C42" t="n">
         <v>7</v>
       </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42">
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
         <v>3</v>
       </c>
-      <c r="F42">
-        <v>2</v>
-      </c>
-      <c r="G42">
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43" t="s">
         <v>160</v>
       </c>
       <c r="B43" t="s">
         <v>161</v>
       </c>
-      <c r="C43">
+      <c r="C43" t="n">
         <v>7</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="n">
         <v>3</v>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>4</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>3</v>
       </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
         <v>175</v>
       </c>
       <c r="B44" t="s">
         <v>176</v>
       </c>
-      <c r="C44">
+      <c r="C44" t="n">
         <v>6.5</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="n">
         <v>4</v>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>3</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>5</v>
       </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
         <v>177</v>
       </c>
       <c r="B45" t="s">
         <v>178</v>
       </c>
-      <c r="C45">
+      <c r="C45" t="n">
         <v>8.5</v>
       </c>
-      <c r="D45">
-        <v>2</v>
-      </c>
-      <c r="E45">
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
         <v>3</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="n">
         <v>5</v>
       </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
         <v>181</v>
       </c>
       <c r="B46" t="s">
         <v>182</v>
       </c>
-      <c r="C46">
+      <c r="C46" t="n">
         <v>8</v>
       </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46">
-        <v>2</v>
-      </c>
-      <c r="F46">
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
         <v>4</v>
       </c>
-      <c r="G46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
         <v>183</v>
       </c>
       <c r="B47" t="s">
         <v>184</v>
       </c>
-      <c r="C47">
+      <c r="C47" t="n">
         <v>8</v>
       </c>
-      <c r="D47">
-        <v>2</v>
-      </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47">
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
         <v>4</v>
       </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
         <v>185</v>
       </c>
       <c r="B48" t="s">
         <v>186</v>
       </c>
-      <c r="C48">
+      <c r="C48" t="n">
         <v>8.5</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="n">
         <v>3</v>
       </c>
-      <c r="E48">
-        <v>2</v>
-      </c>
-      <c r="F48">
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
         <v>3</v>
       </c>
-      <c r="G48">
+      <c r="G48" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49" t="s">
         <v>187</v>
       </c>
       <c r="B49" t="s">
         <v>188</v>
       </c>
-      <c r="C49">
+      <c r="C49" t="n">
         <v>7.5</v>
       </c>
-      <c r="D49">
+      <c r="D49" t="n">
         <v>3</v>
       </c>
-      <c r="E49">
-        <v>2</v>
-      </c>
-      <c r="F49">
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="G49">
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="n">
         <v>2</v>
       </c>
     </row>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="199">
   <si>
     <t>Phase</t>
   </si>
@@ -608,6 +608,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-02-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-03 12:47:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-03</t>
   </si>
 </sst>
 </file>
@@ -6672,6 +6678,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" t="s">
+        <v>199</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="201">
   <si>
     <t>Phase</t>
   </si>
@@ -614,6 +614,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-02-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-25 16:47:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-25</t>
   </si>
 </sst>
 </file>
@@ -6701,6 +6707,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B52" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
   <si>
     <t>Phase</t>
   </si>
@@ -620,14 +620,90 @@
   </si>
   <si>
     <t xml:space="preserve">2026-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-26 10:06:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-27 15:03:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 09:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Knee Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">degrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Calf Raises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Rise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Postero-Medial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Postero-Lateral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-03 09:00:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-04 13:05:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -663,10 +739,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5520,6 +5597,760 @@
         <v>165</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2</v>
+      </c>
+      <c r="B176" t="s">
+        <v>208</v>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>46083.3919085403</v>
+      </c>
+      <c r="E176" t="s">
+        <v>209</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="s">
+        <v>210</v>
+      </c>
+      <c r="H176" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2</v>
+      </c>
+      <c r="B177" t="s">
+        <v>208</v>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>46083.3919498396</v>
+      </c>
+      <c r="E177" t="s">
+        <v>212</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="s">
+        <v>210</v>
+      </c>
+      <c r="H177" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2</v>
+      </c>
+      <c r="B178" t="s">
+        <v>213</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>46083.3921590049</v>
+      </c>
+      <c r="E178" t="s">
+        <v>209</v>
+      </c>
+      <c r="F178" t="n">
+        <v>18</v>
+      </c>
+      <c r="G178" t="s">
+        <v>214</v>
+      </c>
+      <c r="H178" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2</v>
+      </c>
+      <c r="B179" t="s">
+        <v>213</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>46083.3922015548</v>
+      </c>
+      <c r="E179" t="s">
+        <v>212</v>
+      </c>
+      <c r="F179" t="n">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>214</v>
+      </c>
+      <c r="H179" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2</v>
+      </c>
+      <c r="B180" t="s">
+        <v>215</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>46083.3923222592</v>
+      </c>
+      <c r="E180" t="s">
+        <v>209</v>
+      </c>
+      <c r="F180" t="n">
+        <v>17</v>
+      </c>
+      <c r="G180" t="s">
+        <v>214</v>
+      </c>
+      <c r="H180" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2</v>
+      </c>
+      <c r="B181" t="s">
+        <v>215</v>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>46083.3925034457</v>
+      </c>
+      <c r="E181" t="s">
+        <v>212</v>
+      </c>
+      <c r="F181" t="n">
+        <v>19</v>
+      </c>
+      <c r="G181" t="s">
+        <v>214</v>
+      </c>
+      <c r="H181" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2</v>
+      </c>
+      <c r="B182" t="s">
+        <v>216</v>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>46083.3927781041</v>
+      </c>
+      <c r="E182" t="s">
+        <v>209</v>
+      </c>
+      <c r="F182" t="n">
+        <v>8</v>
+      </c>
+      <c r="G182" t="s">
+        <v>214</v>
+      </c>
+      <c r="H182" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2</v>
+      </c>
+      <c r="B183" t="s">
+        <v>216</v>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>46083.3928599464</v>
+      </c>
+      <c r="E183" t="s">
+        <v>212</v>
+      </c>
+      <c r="F183" t="n">
+        <v>10</v>
+      </c>
+      <c r="G183" t="s">
+        <v>214</v>
+      </c>
+      <c r="H183" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2</v>
+      </c>
+      <c r="B184" t="s">
+        <v>217</v>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>46083.3956197562</v>
+      </c>
+      <c r="E184" t="s">
+        <v>209</v>
+      </c>
+      <c r="F184" t="n">
+        <v>80</v>
+      </c>
+      <c r="G184" t="s">
+        <v>218</v>
+      </c>
+      <c r="H184" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2</v>
+      </c>
+      <c r="B185" t="s">
+        <v>219</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>46083.3965193103</v>
+      </c>
+      <c r="E185" t="s">
+        <v>209</v>
+      </c>
+      <c r="F185" t="n">
+        <v>49</v>
+      </c>
+      <c r="G185" t="s">
+        <v>220</v>
+      </c>
+      <c r="H185" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2</v>
+      </c>
+      <c r="B186" t="s">
+        <v>219</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>46083.3965498016</v>
+      </c>
+      <c r="E186" t="s">
+        <v>209</v>
+      </c>
+      <c r="F186" t="n">
+        <v>50</v>
+      </c>
+      <c r="G186" t="s">
+        <v>220</v>
+      </c>
+      <c r="H186" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2</v>
+      </c>
+      <c r="B187" t="s">
+        <v>219</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>46083.3965833915</v>
+      </c>
+      <c r="E187" t="s">
+        <v>209</v>
+      </c>
+      <c r="F187" t="n">
+        <v>51</v>
+      </c>
+      <c r="G187" t="s">
+        <v>220</v>
+      </c>
+      <c r="H187" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B188" t="s">
+        <v>219</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>46083.3966559945</v>
+      </c>
+      <c r="E188" t="s">
+        <v>212</v>
+      </c>
+      <c r="F188" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G188" t="s">
+        <v>220</v>
+      </c>
+      <c r="H188" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2</v>
+      </c>
+      <c r="B189" t="s">
+        <v>219</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>46083.3967025095</v>
+      </c>
+      <c r="E189" t="s">
+        <v>212</v>
+      </c>
+      <c r="F189" t="n">
+        <v>65.1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>220</v>
+      </c>
+      <c r="H189" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2</v>
+      </c>
+      <c r="B190" t="s">
+        <v>219</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>46083.3967473219</v>
+      </c>
+      <c r="E190" t="s">
+        <v>212</v>
+      </c>
+      <c r="F190" t="n">
+        <v>64.9</v>
+      </c>
+      <c r="G190" t="s">
+        <v>220</v>
+      </c>
+      <c r="H190" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2</v>
+      </c>
+      <c r="B191" t="s">
+        <v>221</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>46083.3970990017</v>
+      </c>
+      <c r="E191" t="s">
+        <v>209</v>
+      </c>
+      <c r="F191" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="G191" t="s">
+        <v>220</v>
+      </c>
+      <c r="H191" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2</v>
+      </c>
+      <c r="B192" t="s">
+        <v>221</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>46083.3971387975</v>
+      </c>
+      <c r="E192" t="s">
+        <v>209</v>
+      </c>
+      <c r="F192" t="n">
+        <v>85.6</v>
+      </c>
+      <c r="G192" t="s">
+        <v>220</v>
+      </c>
+      <c r="H192" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2</v>
+      </c>
+      <c r="B193" t="s">
+        <v>221</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>46083.3971837428</v>
+      </c>
+      <c r="E193" t="s">
+        <v>209</v>
+      </c>
+      <c r="F193" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G193" t="s">
+        <v>220</v>
+      </c>
+      <c r="H193" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2</v>
+      </c>
+      <c r="B194" t="s">
+        <v>221</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>46083.3972640956</v>
+      </c>
+      <c r="E194" t="s">
+        <v>212</v>
+      </c>
+      <c r="F194" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="G194" t="s">
+        <v>220</v>
+      </c>
+      <c r="H194" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2</v>
+      </c>
+      <c r="B195" t="s">
+        <v>221</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>46083.3973017756</v>
+      </c>
+      <c r="E195" t="s">
+        <v>212</v>
+      </c>
+      <c r="F195" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="G195" t="s">
+        <v>220</v>
+      </c>
+      <c r="H195" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2</v>
+      </c>
+      <c r="B196" t="s">
+        <v>221</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>46083.3973467666</v>
+      </c>
+      <c r="E196" t="s">
+        <v>212</v>
+      </c>
+      <c r="F196" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="G196" t="s">
+        <v>220</v>
+      </c>
+      <c r="H196" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2</v>
+      </c>
+      <c r="B197" t="s">
+        <v>222</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>46083.397665173</v>
+      </c>
+      <c r="E197" t="s">
+        <v>209</v>
+      </c>
+      <c r="F197" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G197" t="s">
+        <v>220</v>
+      </c>
+      <c r="H197" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2</v>
+      </c>
+      <c r="B198" t="s">
+        <v>222</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>46083.3976947782</v>
+      </c>
+      <c r="E198" t="s">
+        <v>209</v>
+      </c>
+      <c r="F198" t="n">
+        <v>70</v>
+      </c>
+      <c r="G198" t="s">
+        <v>220</v>
+      </c>
+      <c r="H198" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2</v>
+      </c>
+      <c r="B199" t="s">
+        <v>222</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>46083.3977316747</v>
+      </c>
+      <c r="E199" t="s">
+        <v>209</v>
+      </c>
+      <c r="F199" t="n">
+        <v>70</v>
+      </c>
+      <c r="G199" t="s">
+        <v>220</v>
+      </c>
+      <c r="H199" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2</v>
+      </c>
+      <c r="B200" t="s">
+        <v>222</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>46083.3978990743</v>
+      </c>
+      <c r="E200" t="s">
+        <v>212</v>
+      </c>
+      <c r="F200" t="n">
+        <v>92</v>
+      </c>
+      <c r="G200" t="s">
+        <v>220</v>
+      </c>
+      <c r="H200" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2</v>
+      </c>
+      <c r="B201" t="s">
+        <v>222</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>46083.3979423335</v>
+      </c>
+      <c r="E201" t="s">
+        <v>212</v>
+      </c>
+      <c r="F201" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G201" t="s">
+        <v>220</v>
+      </c>
+      <c r="H201" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2</v>
+      </c>
+      <c r="B202" t="s">
+        <v>222</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>46083.3979767226</v>
+      </c>
+      <c r="E202" t="s">
+        <v>212</v>
+      </c>
+      <c r="F202" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G202" t="s">
+        <v>220</v>
+      </c>
+      <c r="H202" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2</v>
+      </c>
+      <c r="B203" t="s">
+        <v>216</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>46085.5461658332</v>
+      </c>
+      <c r="E203" t="s">
+        <v>209</v>
+      </c>
+      <c r="F203" t="n">
+        <v>10</v>
+      </c>
+      <c r="G203" t="s">
+        <v>214</v>
+      </c>
+      <c r="H203" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2</v>
+      </c>
+      <c r="B204" t="s">
+        <v>216</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>46085.5462013262</v>
+      </c>
+      <c r="E204" t="s">
+        <v>212</v>
+      </c>
+      <c r="F204" t="n">
+        <v>10</v>
+      </c>
+      <c r="G204" t="s">
+        <v>214</v>
+      </c>
+      <c r="H204" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6730,6 +7561,121 @@
         <v>2</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" t="s">
+        <v>205</v>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>225</v>
+      </c>
+      <c r="B57" t="s">
+        <v>226</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="228">
   <si>
     <t>Phase</t>
   </si>
@@ -695,6 +695,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-06 08:30:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-06</t>
   </si>
 </sst>
 </file>
@@ -7676,6 +7682,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="232">
   <si>
     <t>Phase</t>
   </si>
@@ -701,6 +701,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09 09:38:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-13 13:55:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-13</t>
   </si>
 </sst>
 </file>
@@ -7705,6 +7717,52 @@
         <v>3</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" t="s">
+        <v>230</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="252">
   <si>
     <t>Phase</t>
   </si>
@@ -535,9 +535,6 @@
     <t>seconds</t>
   </si>
   <si>
-    <t>Single Leg Hop Test</t>
-  </si>
-  <si>
     <t>Side Bridge</t>
   </si>
   <si>
@@ -604,49 +601,157 @@
     <t>kg</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-02 10:30:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-03 12:47:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-25 16:47:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-26 10:06:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-27 15:03:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02 09:23:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Knee Extension</t>
+    <t>2026-02-02 10:30:18</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-03 12:47:58</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-25 16:47:59</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:06:15</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:03:03</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:23:00</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>Passive Knee Extension</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Single Leg Bridge</t>
+  </si>
+  <si>
+    <t>reps</t>
+  </si>
+  <si>
+    <t>Single Leg Calf Raises</t>
+  </si>
+  <si>
+    <t>Single Leg Rise</t>
+  </si>
+  <si>
+    <t>TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>Y-Balance (Postero-Medial)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Postero-Lateral)</t>
+  </si>
+  <si>
+    <t>2026-03-03 09:00:53</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04 13:05:46</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-06 08:30:51</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:38:13</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-13 13:55:13</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14 10:43:27</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-16 12:32:22</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Single Leg Hop</t>
+  </si>
+  <si>
+    <t>Triple Hop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triple Cross Over Hop</t>
   </si>
   <si>
     <t xml:space="preserve">Left</t>
   </si>
   <si>
-    <t xml:space="preserve">degrees</t>
+    <t xml:space="preserve">cm</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -655,64 +760,19 @@
     <t xml:space="preserve">Right</t>
   </si>
   <si>
-    <t xml:space="preserve">Single Leg Bridge</t>
+    <t xml:space="preserve">Side Hop</t>
   </si>
   <si>
     <t xml:space="preserve">reps</t>
   </si>
   <si>
-    <t xml:space="preserve">Single Leg Calf Raises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Rise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrapBar Deadlift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Anterior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Postero-Medial)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Postero-Lateral)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-03 09:00:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-04 13:05:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-06 08:30:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-09 09:38:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-13 13:55:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-13</t>
+    <t xml:space="preserve">Vestibular Balance (Horizontal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vestibular Balance (Vertical)</t>
   </si>
 </sst>
 </file>
@@ -4811,7 +4871,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B145" t="s">
         <v>173</v>
@@ -4820,16 +4880,16 @@
         <v>46047</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>46047.419832948697</v>
+        <v>46047.445065262698</v>
       </c>
       <c r="E145" t="s">
         <v>163</v>
       </c>
       <c r="F145" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G145" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H145" t="s">
         <v>165</v>
@@ -4840,16 +4900,16 @@
         <v>2</v>
       </c>
       <c r="B146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C146" s="1" t="n">
         <v>46047</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>46047.445065262698</v>
+        <v>46047.445106826701</v>
       </c>
       <c r="E146" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F146" t="n">
         <v>30</v>
@@ -4866,19 +4926,19 @@
         <v>2</v>
       </c>
       <c r="B147" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>46047.445106826701</v>
+        <v>46049.244785984898</v>
       </c>
       <c r="E147" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F147" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G147" t="s">
         <v>172</v>
@@ -4892,19 +4952,19 @@
         <v>2</v>
       </c>
       <c r="B148" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C148" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>46049.244785984898</v>
+        <v>46049.245240876902</v>
       </c>
       <c r="E148" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F148" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G148" t="s">
         <v>172</v>
@@ -4918,19 +4978,19 @@
         <v>2</v>
       </c>
       <c r="B149" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C149" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>46049.245240876902</v>
+        <v>46049.245369569697</v>
       </c>
       <c r="E149" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F149" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="G149" t="s">
         <v>172</v>
@@ -4950,13 +5010,13 @@
         <v>46049</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>46049.245369569697</v>
+        <v>46049.245406563801</v>
       </c>
       <c r="E150" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F150" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G150" t="s">
         <v>172</v>
@@ -4970,22 +5030,22 @@
         <v>2</v>
       </c>
       <c r="B151" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C151" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>46049.245406563801</v>
+        <v>46049.2458257244</v>
       </c>
       <c r="E151" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F151" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G151" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H151" t="s">
         <v>165</v>
@@ -4996,19 +5056,19 @@
         <v>2</v>
       </c>
       <c r="B152" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C152" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>46049.2458257244</v>
+        <v>46049.245875696397</v>
       </c>
       <c r="E152" t="s">
         <v>163</v>
       </c>
       <c r="F152" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G152" t="s">
         <v>170</v>
@@ -5022,19 +5082,19 @@
         <v>2</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C153" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>46049.245875696397</v>
+        <v>46049.245916874301</v>
       </c>
       <c r="E153" t="s">
         <v>163</v>
       </c>
       <c r="F153" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G153" t="s">
         <v>170</v>
@@ -5048,19 +5108,19 @@
         <v>2</v>
       </c>
       <c r="B154" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C154" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>46049.245916874301</v>
+        <v>46049.246014391902</v>
       </c>
       <c r="E154" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F154" t="n">
-        <v>43.5</v>
+        <v>62.5</v>
       </c>
       <c r="G154" t="s">
         <v>170</v>
@@ -5074,19 +5134,19 @@
         <v>2</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C155" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>46049.246014391902</v>
+        <v>46049.246069772198</v>
       </c>
       <c r="E155" t="s">
         <v>166</v>
       </c>
       <c r="F155" t="n">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
       <c r="G155" t="s">
         <v>170</v>
@@ -5100,19 +5160,19 @@
         <v>2</v>
       </c>
       <c r="B156" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>46049.246069772198</v>
+        <v>46049.2461241977</v>
       </c>
       <c r="E156" t="s">
         <v>166</v>
       </c>
       <c r="F156" t="n">
-        <v>63.5</v>
+        <v>64</v>
       </c>
       <c r="G156" t="s">
         <v>170</v>
@@ -5126,22 +5186,22 @@
         <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>46049.2461241977</v>
+        <v>46054.373075639203</v>
       </c>
       <c r="E157" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F157" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G157" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="H157" t="s">
         <v>165</v>
@@ -5152,22 +5212,22 @@
         <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C158" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>46054.373075639203</v>
+        <v>46054.3731330847</v>
       </c>
       <c r="E158" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H158" t="s">
         <v>165</v>
@@ -5178,22 +5238,22 @@
         <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C159" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>46054.3731330847</v>
+        <v>46054.373350648799</v>
       </c>
       <c r="E159" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="G159" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H159" t="s">
         <v>165</v>
@@ -5204,22 +5264,22 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C160" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>46054.373350648799</v>
+        <v>46054.373401007098</v>
       </c>
       <c r="E160" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F160" t="n">
         <v>127</v>
       </c>
       <c r="G160" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H160" t="s">
         <v>165</v>
@@ -5236,16 +5296,16 @@
         <v>46054</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>46054.373401007098</v>
+        <v>46054.374090033103</v>
       </c>
       <c r="E161" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F161" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="G161" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H161" t="s">
         <v>165</v>
@@ -5256,22 +5316,22 @@
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="C162" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>46054.374090033103</v>
+        <v>46054.374287611798</v>
       </c>
       <c r="E162" t="s">
         <v>163</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="H162" t="s">
         <v>165</v>
@@ -5288,13 +5348,13 @@
         <v>46054</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>46054.374287611798</v>
+        <v>46054.374329414699</v>
       </c>
       <c r="E163" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F163" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G163" t="s">
         <v>164</v>
@@ -5308,19 +5368,19 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C164" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>46054.374329414699</v>
+        <v>46054.375393863796</v>
       </c>
       <c r="E164" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F164" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G164" t="s">
         <v>164</v>
@@ -5340,13 +5400,13 @@
         <v>46054</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>46054.375393863796</v>
+        <v>46054.375432872897</v>
       </c>
       <c r="E165" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F165" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G165" t="s">
         <v>164</v>
@@ -5360,19 +5420,19 @@
         <v>2</v>
       </c>
       <c r="B166" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C166" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>46054.375432872897</v>
+        <v>46054.375730488297</v>
       </c>
       <c r="E166" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F166" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G166" t="s">
         <v>164</v>
@@ -5392,13 +5452,13 @@
         <v>46054</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>46054.375730488297</v>
+        <v>46054.375768050602</v>
       </c>
       <c r="E167" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F167" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G167" t="s">
         <v>164</v>
@@ -5412,22 +5472,22 @@
         <v>2</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C168" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>46054.375768050602</v>
+        <v>46054.375964423198</v>
       </c>
       <c r="E168" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F168" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G168" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H168" t="s">
         <v>165</v>
@@ -5438,16 +5498,16 @@
         <v>2</v>
       </c>
       <c r="B169" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C169" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>46054.375964423198</v>
+        <v>46054.375998781703</v>
       </c>
       <c r="E169" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F169" t="n">
         <v>45</v>
@@ -5464,19 +5524,19 @@
         <v>2</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C170" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>46054.375998781703</v>
+        <v>46054.377199965696</v>
       </c>
       <c r="E170" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F170" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G170" t="s">
         <v>172</v>
@@ -5496,10 +5556,10 @@
         <v>46054</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>46054.377199965696</v>
+        <v>46054.3772267725</v>
       </c>
       <c r="E171" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F171" t="n">
         <v>9</v>
@@ -5516,22 +5576,22 @@
         <v>2</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C172" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>46054.3772267725</v>
+        <v>46054.377639929997</v>
       </c>
       <c r="E172" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="F172" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="G172" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="H172" t="s">
         <v>165</v>
@@ -5542,22 +5602,22 @@
         <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="C173" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>46054.377639929997</v>
+        <v>46054.378020765304</v>
       </c>
       <c r="E173" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="F173" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="G173" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="H173" t="s">
         <v>165</v>
@@ -5574,13 +5634,13 @@
         <v>46054</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>46054.378020765304</v>
+        <v>46054.378060841897</v>
       </c>
       <c r="E174" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F174" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G174" t="s">
         <v>170</v>
@@ -5594,25 +5654,25 @@
         <v>2</v>
       </c>
       <c r="B175" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46054</v>
+        <v>46083</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>46054.378060841897</v>
+        <v>46083.391908540303</v>
       </c>
       <c r="E175" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="F175" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="H175" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176">
@@ -5620,25 +5680,25 @@
         <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C176" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D176" s="3" t="n">
-        <v>46083.3919085403</v>
+      <c r="D176" s="2" t="n">
+        <v>46083.391949839599</v>
       </c>
       <c r="E176" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
       </c>
       <c r="G176" t="s">
+        <v>209</v>
+      </c>
+      <c r="H176" t="s">
         <v>210</v>
-      </c>
-      <c r="H176" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="177">
@@ -5646,25 +5706,25 @@
         <v>2</v>
       </c>
       <c r="B177" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C177" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D177" s="3" t="n">
-        <v>46083.3919498396</v>
+      <c r="D177" s="2" t="n">
+        <v>46083.392159004899</v>
       </c>
       <c r="E177" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G177" t="s">
+        <v>213</v>
+      </c>
+      <c r="H177" t="s">
         <v>210</v>
-      </c>
-      <c r="H177" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="178">
@@ -5672,25 +5732,25 @@
         <v>2</v>
       </c>
       <c r="B178" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C178" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D178" s="3" t="n">
-        <v>46083.3921590049</v>
+      <c r="D178" s="2" t="n">
+        <v>46083.392201554801</v>
       </c>
       <c r="E178" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F178" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G178" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H178" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="179">
@@ -5698,25 +5758,25 @@
         <v>2</v>
       </c>
       <c r="B179" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C179" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D179" s="3" t="n">
-        <v>46083.3922015548</v>
+      <c r="D179" s="2" t="n">
+        <v>46083.392322259198</v>
       </c>
       <c r="E179" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F179" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G179" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H179" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="180">
@@ -5724,25 +5784,25 @@
         <v>2</v>
       </c>
       <c r="B180" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C180" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D180" s="3" t="n">
-        <v>46083.3923222592</v>
+      <c r="D180" s="2" t="n">
+        <v>46083.392503445699</v>
       </c>
       <c r="E180" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F180" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G180" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H180" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="181">
@@ -5755,20 +5815,20 @@
       <c r="C181" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D181" s="3" t="n">
-        <v>46083.3925034457</v>
+      <c r="D181" s="2" t="n">
+        <v>46083.392778104098</v>
       </c>
       <c r="E181" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F181" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G181" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H181" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="182">
@@ -5776,25 +5836,25 @@
         <v>2</v>
       </c>
       <c r="B182" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C182" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D182" s="3" t="n">
-        <v>46083.3927781041</v>
+      <c r="D182" s="2" t="n">
+        <v>46083.392859946398</v>
       </c>
       <c r="E182" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F182" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G182" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H182" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="183">
@@ -5807,20 +5867,20 @@
       <c r="C183" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D183" s="3" t="n">
-        <v>46083.3928599464</v>
+      <c r="D183" s="2" t="n">
+        <v>46083.3956197562</v>
       </c>
       <c r="E183" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F183" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="G183" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H183" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="184">
@@ -5828,25 +5888,25 @@
         <v>2</v>
       </c>
       <c r="B184" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C184" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D184" s="3" t="n">
-        <v>46083.3956197562</v>
+      <c r="D184" s="2" t="n">
+        <v>46083.396519310299</v>
       </c>
       <c r="E184" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F184" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="G184" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H184" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="185">
@@ -5854,25 +5914,25 @@
         <v>2</v>
       </c>
       <c r="B185" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C185" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D185" s="3" t="n">
-        <v>46083.3965193103</v>
+      <c r="D185" s="2" t="n">
+        <v>46083.396549801597</v>
       </c>
       <c r="E185" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F185" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G185" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H185" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="186">
@@ -5880,25 +5940,25 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C186" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D186" s="3" t="n">
-        <v>46083.3965498016</v>
+      <c r="D186" s="2" t="n">
+        <v>46083.396583391499</v>
       </c>
       <c r="E186" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F186" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G186" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H186" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="187">
@@ -5906,25 +5966,25 @@
         <v>2</v>
       </c>
       <c r="B187" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C187" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D187" s="3" t="n">
-        <v>46083.3965833915</v>
+      <c r="D187" s="2" t="n">
+        <v>46083.396655994497</v>
       </c>
       <c r="E187" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F187" t="n">
-        <v>51</v>
+        <v>64.2</v>
       </c>
       <c r="G187" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H187" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="188">
@@ -5932,25 +5992,25 @@
         <v>2</v>
       </c>
       <c r="B188" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C188" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D188" s="3" t="n">
-        <v>46083.3966559945</v>
+      <c r="D188" s="2" t="n">
+        <v>46083.396702509497</v>
       </c>
       <c r="E188" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F188" t="n">
-        <v>64.2</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="G188" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H188" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="189">
@@ -5958,25 +6018,25 @@
         <v>2</v>
       </c>
       <c r="B189" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C189" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D189" s="3" t="n">
-        <v>46083.3967025095</v>
+      <c r="D189" s="2" t="n">
+        <v>46083.396747321902</v>
       </c>
       <c r="E189" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F189" t="n">
-        <v>65.1</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="G189" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H189" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="190">
@@ -5984,25 +6044,25 @@
         <v>2</v>
       </c>
       <c r="B190" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C190" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D190" s="3" t="n">
-        <v>46083.3967473219</v>
+      <c r="D190" s="2" t="n">
+        <v>46083.397099001697</v>
       </c>
       <c r="E190" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F190" t="n">
-        <v>64.9</v>
+        <v>84.7</v>
       </c>
       <c r="G190" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H190" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="191">
@@ -6010,25 +6070,25 @@
         <v>2</v>
       </c>
       <c r="B191" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C191" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D191" s="3" t="n">
-        <v>46083.3970990017</v>
+      <c r="D191" s="2" t="n">
+        <v>46083.397138797503</v>
       </c>
       <c r="E191" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F191" t="n">
-        <v>84.7</v>
+        <v>85.6</v>
       </c>
       <c r="G191" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H191" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="192">
@@ -6036,25 +6096,25 @@
         <v>2</v>
       </c>
       <c r="B192" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C192" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D192" s="3" t="n">
-        <v>46083.3971387975</v>
+      <c r="D192" s="2" t="n">
+        <v>46083.397183742803</v>
       </c>
       <c r="E192" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F192" t="n">
-        <v>85.6</v>
+        <v>85.8</v>
       </c>
       <c r="G192" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H192" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="193">
@@ -6062,25 +6122,25 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C193" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D193" s="3" t="n">
-        <v>46083.3971837428</v>
+      <c r="D193" s="2" t="n">
+        <v>46083.397264095598</v>
       </c>
       <c r="E193" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F193" t="n">
-        <v>85.8</v>
+        <v>102.2</v>
       </c>
       <c r="G193" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H193" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="194">
@@ -6088,25 +6148,25 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C194" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D194" s="3" t="n">
-        <v>46083.3972640956</v>
+      <c r="D194" s="2" t="n">
+        <v>46083.3973017756</v>
       </c>
       <c r="E194" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F194" t="n">
-        <v>102.2</v>
+        <v>102.4</v>
       </c>
       <c r="G194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H194" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="195">
@@ -6114,25 +6174,25 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C195" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D195" s="3" t="n">
-        <v>46083.3973017756</v>
+      <c r="D195" s="2" t="n">
+        <v>46083.3973467666</v>
       </c>
       <c r="E195" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F195" t="n">
-        <v>102.4</v>
+        <v>102.8</v>
       </c>
       <c r="G195" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H195" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="196">
@@ -6145,20 +6205,20 @@
       <c r="C196" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D196" s="3" t="n">
-        <v>46083.3973467666</v>
+      <c r="D196" s="2" t="n">
+        <v>46083.397665172997</v>
       </c>
       <c r="E196" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F196" t="n">
-        <v>102.8</v>
+        <v>69.5</v>
       </c>
       <c r="G196" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H196" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="197">
@@ -6166,25 +6226,25 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C197" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D197" s="3" t="n">
-        <v>46083.397665173</v>
+      <c r="D197" s="2" t="n">
+        <v>46083.397694778199</v>
       </c>
       <c r="E197" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F197" t="n">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="G197" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H197" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="198">
@@ -6192,25 +6252,25 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C198" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D198" s="3" t="n">
-        <v>46083.3976947782</v>
+      <c r="D198" s="2" t="n">
+        <v>46083.397731674697</v>
       </c>
       <c r="E198" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F198" t="n">
         <v>70</v>
       </c>
       <c r="G198" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H198" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="199">
@@ -6218,25 +6278,25 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C199" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D199" s="3" t="n">
-        <v>46083.3977316747</v>
+      <c r="D199" s="2" t="n">
+        <v>46083.397899074298</v>
       </c>
       <c r="E199" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F199" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G199" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H199" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="200">
@@ -6244,25 +6304,25 @@
         <v>2</v>
       </c>
       <c r="B200" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C200" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D200" s="3" t="n">
-        <v>46083.3978990743</v>
+      <c r="D200" s="2" t="n">
+        <v>46083.397942333497</v>
       </c>
       <c r="E200" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F200" t="n">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="G200" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H200" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="201">
@@ -6270,25 +6330,25 @@
         <v>2</v>
       </c>
       <c r="B201" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C201" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="D201" s="3" t="n">
-        <v>46083.3979423335</v>
+      <c r="D201" s="2" t="n">
+        <v>46083.397976722597</v>
       </c>
       <c r="E201" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F201" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="G201" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H201" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="202">
@@ -6296,25 +6356,25 @@
         <v>2</v>
       </c>
       <c r="B202" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="D202" s="3" t="n">
-        <v>46083.3979767226</v>
+        <v>46085</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>46085.546165833199</v>
       </c>
       <c r="E202" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F202" t="n">
-        <v>93.5</v>
+        <v>10</v>
       </c>
       <c r="G202" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H202" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="203">
@@ -6322,25 +6382,25 @@
         <v>2</v>
       </c>
       <c r="B203" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C203" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="D203" s="3" t="n">
-        <v>46085.5461658332</v>
+      <c r="D203" s="2" t="n">
+        <v>46085.5462013262</v>
       </c>
       <c r="E203" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F203" t="n">
         <v>10</v>
       </c>
       <c r="G203" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H203" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="204">
@@ -6348,25 +6408,1065 @@
         <v>2</v>
       </c>
       <c r="B204" t="s">
+        <v>212</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>46097.522855592899</v>
+      </c>
+      <c r="E204" t="s">
+        <v>208</v>
+      </c>
+      <c r="F204" t="n">
+        <v>20</v>
+      </c>
+      <c r="G204" t="s">
+        <v>213</v>
+      </c>
+      <c r="H204" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2</v>
+      </c>
+      <c r="B205" t="s">
+        <v>212</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>46097.522890234199</v>
+      </c>
+      <c r="E205" t="s">
+        <v>211</v>
+      </c>
+      <c r="F205" t="n">
+        <v>20</v>
+      </c>
+      <c r="G205" t="s">
+        <v>213</v>
+      </c>
+      <c r="H205" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2</v>
+      </c>
+      <c r="B206" t="s">
+        <v>214</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>46097.523113597097</v>
+      </c>
+      <c r="E206" t="s">
+        <v>208</v>
+      </c>
+      <c r="F206" t="n">
+        <v>20</v>
+      </c>
+      <c r="G206" t="s">
+        <v>213</v>
+      </c>
+      <c r="H206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2</v>
+      </c>
+      <c r="B207" t="s">
+        <v>214</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>46097.523147233798</v>
+      </c>
+      <c r="E207" t="s">
+        <v>211</v>
+      </c>
+      <c r="F207" t="n">
+        <v>20</v>
+      </c>
+      <c r="G207" t="s">
+        <v>213</v>
+      </c>
+      <c r="H207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2</v>
+      </c>
+      <c r="B208" t="s">
+        <v>218</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>46097.523852654398</v>
+      </c>
+      <c r="E208" t="s">
+        <v>208</v>
+      </c>
+      <c r="F208" t="n">
+        <v>59</v>
+      </c>
+      <c r="G208" t="s">
+        <v>219</v>
+      </c>
+      <c r="H208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2</v>
+      </c>
+      <c r="B209" t="s">
+        <v>218</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>46097.523910194999</v>
+      </c>
+      <c r="E209" t="s">
+        <v>208</v>
+      </c>
+      <c r="F209" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G209" t="s">
+        <v>219</v>
+      </c>
+      <c r="H209" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2</v>
+      </c>
+      <c r="B210" t="s">
+        <v>218</v>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>46097.523939590901</v>
+      </c>
+      <c r="E210" t="s">
+        <v>208</v>
+      </c>
+      <c r="F210" t="n">
+        <v>61</v>
+      </c>
+      <c r="G210" t="s">
+        <v>219</v>
+      </c>
+      <c r="H210" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2</v>
+      </c>
+      <c r="B211" t="s">
+        <v>218</v>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>46097.524105098302</v>
+      </c>
+      <c r="E211" t="s">
+        <v>211</v>
+      </c>
+      <c r="F211" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G211" t="s">
+        <v>219</v>
+      </c>
+      <c r="H211" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2</v>
+      </c>
+      <c r="B212" t="s">
+        <v>218</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>46097.524143677103</v>
+      </c>
+      <c r="E212" t="s">
+        <v>211</v>
+      </c>
+      <c r="F212" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G212" t="s">
+        <v>219</v>
+      </c>
+      <c r="H212" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2</v>
+      </c>
+      <c r="B213" t="s">
+        <v>218</v>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>46097.524185612499</v>
+      </c>
+      <c r="E213" t="s">
+        <v>211</v>
+      </c>
+      <c r="F213" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G213" t="s">
+        <v>219</v>
+      </c>
+      <c r="H213" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2</v>
+      </c>
+      <c r="B214" t="s">
+        <v>220</v>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>46097.524777407998</v>
+      </c>
+      <c r="E214" t="s">
+        <v>208</v>
+      </c>
+      <c r="F214" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G214" t="s">
+        <v>219</v>
+      </c>
+      <c r="H214" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2</v>
+      </c>
+      <c r="B215" t="s">
+        <v>220</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>46097.524840420898</v>
+      </c>
+      <c r="E215" t="s">
+        <v>208</v>
+      </c>
+      <c r="F215" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G215" t="s">
+        <v>219</v>
+      </c>
+      <c r="H215" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2</v>
+      </c>
+      <c r="B216" t="s">
+        <v>220</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>46097.524876933698</v>
+      </c>
+      <c r="E216" t="s">
+        <v>208</v>
+      </c>
+      <c r="F216" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G216" t="s">
+        <v>219</v>
+      </c>
+      <c r="H216" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2</v>
+      </c>
+      <c r="B217" t="s">
+        <v>220</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>46097.524949738799</v>
+      </c>
+      <c r="E217" t="s">
+        <v>211</v>
+      </c>
+      <c r="F217" t="n">
+        <v>101</v>
+      </c>
+      <c r="G217" t="s">
+        <v>219</v>
+      </c>
+      <c r="H217" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2</v>
+      </c>
+      <c r="B218" t="s">
+        <v>220</v>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>46097.524979291702</v>
+      </c>
+      <c r="E218" t="s">
+        <v>211</v>
+      </c>
+      <c r="F218" t="n">
+        <v>100</v>
+      </c>
+      <c r="G218" t="s">
+        <v>219</v>
+      </c>
+      <c r="H218" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2</v>
+      </c>
+      <c r="B219" t="s">
+        <v>220</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>46097.525022818401</v>
+      </c>
+      <c r="E219" t="s">
+        <v>211</v>
+      </c>
+      <c r="F219" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G219" t="s">
+        <v>219</v>
+      </c>
+      <c r="H219" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2</v>
+      </c>
+      <c r="B220" t="s">
+        <v>221</v>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>46097.525205614496</v>
+      </c>
+      <c r="E220" t="s">
+        <v>208</v>
+      </c>
+      <c r="F220" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G220" t="s">
+        <v>219</v>
+      </c>
+      <c r="H220" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2</v>
+      </c>
+      <c r="B221" t="s">
+        <v>221</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>46097.525241944597</v>
+      </c>
+      <c r="E221" t="s">
+        <v>208</v>
+      </c>
+      <c r="F221" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="G221" t="s">
+        <v>219</v>
+      </c>
+      <c r="H221" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2</v>
+      </c>
+      <c r="B222" t="s">
+        <v>221</v>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>46097.525271688501</v>
+      </c>
+      <c r="E222" t="s">
+        <v>208</v>
+      </c>
+      <c r="F222" t="n">
+        <v>80</v>
+      </c>
+      <c r="G222" t="s">
+        <v>219</v>
+      </c>
+      <c r="H222" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2</v>
+      </c>
+      <c r="B223" t="s">
+        <v>221</v>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>46097.5253470393</v>
+      </c>
+      <c r="E223" t="s">
+        <v>211</v>
+      </c>
+      <c r="F223" t="n">
+        <v>89</v>
+      </c>
+      <c r="G223" t="s">
+        <v>219</v>
+      </c>
+      <c r="H223" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2</v>
+      </c>
+      <c r="B224" t="s">
+        <v>221</v>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>46097.525391974101</v>
+      </c>
+      <c r="E224" t="s">
+        <v>211</v>
+      </c>
+      <c r="F224" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="G224" t="s">
+        <v>219</v>
+      </c>
+      <c r="H224" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2</v>
+      </c>
+      <c r="B225" t="s">
+        <v>221</v>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>46097.525422512699</v>
+      </c>
+      <c r="E225" t="s">
+        <v>211</v>
+      </c>
+      <c r="F225" t="n">
+        <v>90</v>
+      </c>
+      <c r="G225" t="s">
+        <v>219</v>
+      </c>
+      <c r="H225" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2</v>
+      </c>
+      <c r="B226" t="s">
         <v>216</v>
       </c>
-      <c r="C204" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>46085.5462013262</v>
-      </c>
-      <c r="E204" t="s">
-        <v>212</v>
-      </c>
-      <c r="F204" t="n">
-        <v>10</v>
-      </c>
-      <c r="G204" t="s">
-        <v>214</v>
-      </c>
-      <c r="H204" t="s">
-        <v>211</v>
+      <c r="C226" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>46097.526771824101</v>
+      </c>
+      <c r="E226" t="s">
+        <v>236</v>
+      </c>
+      <c r="F226" t="n">
+        <v>100</v>
+      </c>
+      <c r="G226" t="s">
+        <v>217</v>
+      </c>
+      <c r="H226" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>3</v>
+      </c>
+      <c r="B227" t="s">
+        <v>241</v>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>46097.5360398048</v>
+      </c>
+      <c r="E227" t="s">
+        <v>237</v>
+      </c>
+      <c r="F227" t="n">
+        <v>50</v>
+      </c>
+      <c r="G227" t="s">
+        <v>238</v>
+      </c>
+      <c r="H227" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>3</v>
+      </c>
+      <c r="B228" t="s">
+        <v>241</v>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>46097.536087360299</v>
+      </c>
+      <c r="E228" t="s">
+        <v>237</v>
+      </c>
+      <c r="F228" t="n">
+        <v>52</v>
+      </c>
+      <c r="G228" t="s">
+        <v>238</v>
+      </c>
+      <c r="H228" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>3</v>
+      </c>
+      <c r="B229" t="s">
+        <v>241</v>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>46097.536862096902</v>
+      </c>
+      <c r="E229" t="s">
+        <v>240</v>
+      </c>
+      <c r="F229" t="n">
+        <v>120</v>
+      </c>
+      <c r="G229" t="s">
+        <v>238</v>
+      </c>
+      <c r="H229" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>3</v>
+      </c>
+      <c r="B230" t="s">
+        <v>241</v>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>46097.536902898799</v>
+      </c>
+      <c r="E230" t="s">
+        <v>240</v>
+      </c>
+      <c r="F230" t="n">
+        <v>124</v>
+      </c>
+      <c r="G230" t="s">
+        <v>238</v>
+      </c>
+      <c r="H230" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>3</v>
+      </c>
+      <c r="B231" t="s">
+        <v>242</v>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>46097.586285992104</v>
+      </c>
+      <c r="E231" t="s">
+        <v>237</v>
+      </c>
+      <c r="F231" t="n">
+        <v>450</v>
+      </c>
+      <c r="G231" t="s">
+        <v>238</v>
+      </c>
+      <c r="H231" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>3</v>
+      </c>
+      <c r="B232" t="s">
+        <v>242</v>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>46097.586339884598</v>
+      </c>
+      <c r="E232" t="s">
+        <v>237</v>
+      </c>
+      <c r="F232" t="n">
+        <v>460</v>
+      </c>
+      <c r="G232" t="s">
+        <v>238</v>
+      </c>
+      <c r="H232" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>3</v>
+      </c>
+      <c r="B233" t="s">
+        <v>242</v>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>46097.5864288882</v>
+      </c>
+      <c r="E233" t="s">
+        <v>240</v>
+      </c>
+      <c r="F233" t="n">
+        <v>542</v>
+      </c>
+      <c r="G233" t="s">
+        <v>238</v>
+      </c>
+      <c r="H233" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>3</v>
+      </c>
+      <c r="B234" t="s">
+        <v>242</v>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>46097.586490094698</v>
+      </c>
+      <c r="E234" t="s">
+        <v>240</v>
+      </c>
+      <c r="F234" t="n">
+        <v>560</v>
+      </c>
+      <c r="G234" t="s">
+        <v>238</v>
+      </c>
+      <c r="H234" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3</v>
+      </c>
+      <c r="B235" t="s">
+        <v>243</v>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>46097.6012139835</v>
+      </c>
+      <c r="E235" t="s">
+        <v>244</v>
+      </c>
+      <c r="F235" t="n">
+        <v>400</v>
+      </c>
+      <c r="G235" t="s">
+        <v>245</v>
+      </c>
+      <c r="H235" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>3</v>
+      </c>
+      <c r="B236" t="s">
+        <v>243</v>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>46097.6012609843</v>
+      </c>
+      <c r="E236" t="s">
+        <v>244</v>
+      </c>
+      <c r="F236" t="n">
+        <v>410</v>
+      </c>
+      <c r="G236" t="s">
+        <v>245</v>
+      </c>
+      <c r="H236" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>3</v>
+      </c>
+      <c r="B237" t="s">
+        <v>243</v>
+      </c>
+      <c r="C237" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>46097.6013430131</v>
+      </c>
+      <c r="E237" t="s">
+        <v>247</v>
+      </c>
+      <c r="F237" t="n">
+        <v>483</v>
+      </c>
+      <c r="G237" t="s">
+        <v>245</v>
+      </c>
+      <c r="H237" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>3</v>
+      </c>
+      <c r="B238" t="s">
+        <v>243</v>
+      </c>
+      <c r="C238" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>46097.6014109983</v>
+      </c>
+      <c r="E238" t="s">
+        <v>247</v>
+      </c>
+      <c r="F238" t="n">
+        <v>487</v>
+      </c>
+      <c r="G238" t="s">
+        <v>245</v>
+      </c>
+      <c r="H238" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>3</v>
+      </c>
+      <c r="B239" t="s">
+        <v>248</v>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>46097.6154524684</v>
+      </c>
+      <c r="E239" t="s">
+        <v>244</v>
+      </c>
+      <c r="F239" t="n">
+        <v>31</v>
+      </c>
+      <c r="G239" t="s">
+        <v>249</v>
+      </c>
+      <c r="H239" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>3</v>
+      </c>
+      <c r="B240" t="s">
+        <v>248</v>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>46097.6155898686</v>
+      </c>
+      <c r="E240" t="s">
+        <v>247</v>
+      </c>
+      <c r="F240" t="n">
+        <v>45</v>
+      </c>
+      <c r="G240" t="s">
+        <v>249</v>
+      </c>
+      <c r="H240" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>3</v>
+      </c>
+      <c r="B241" t="s">
+        <v>250</v>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>46097.6404911276</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+      <c r="F241" t="n">
+        <v>6</v>
+      </c>
+      <c r="G241" t="s">
+        <v>251</v>
+      </c>
+      <c r="H241" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>3</v>
+      </c>
+      <c r="B242" t="s">
+        <v>250</v>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>46097.6405362685</v>
+      </c>
+      <c r="E242" t="s">
+        <v>247</v>
+      </c>
+      <c r="F242" t="n">
+        <v>15</v>
+      </c>
+      <c r="G242" t="s">
+        <v>251</v>
+      </c>
+      <c r="H242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>3</v>
+      </c>
+      <c r="B243" t="s">
+        <v>252</v>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>46097.6405887152</v>
+      </c>
+      <c r="E243" t="s">
+        <v>244</v>
+      </c>
+      <c r="F243" t="n">
+        <v>8</v>
+      </c>
+      <c r="G243" t="s">
+        <v>251</v>
+      </c>
+      <c r="H243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>3</v>
+      </c>
+      <c r="B244" t="s">
+        <v>252</v>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>46097.640626837</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+      <c r="F244" t="n">
+        <v>15</v>
+      </c>
+      <c r="G244" t="s">
+        <v>251</v>
+      </c>
+      <c r="H244" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -7374,10 +8474,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s">
         <v>175</v>
-      </c>
-      <c r="B44" t="s">
-        <v>176</v>
       </c>
       <c r="C44" t="n">
         <v>6.5</v>
@@ -7397,10 +8497,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" t="s">
         <v>177</v>
-      </c>
-      <c r="B45" t="s">
-        <v>178</v>
       </c>
       <c r="C45" t="n">
         <v>8.5</v>
@@ -7420,10 +8520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" t="s">
         <v>181</v>
-      </c>
-      <c r="B46" t="s">
-        <v>182</v>
       </c>
       <c r="C46" t="n">
         <v>8</v>
@@ -7443,10 +8543,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" t="s">
         <v>183</v>
-      </c>
-      <c r="B47" t="s">
-        <v>184</v>
       </c>
       <c r="C47" t="n">
         <v>8</v>
@@ -7466,10 +8566,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" t="s">
         <v>185</v>
-      </c>
-      <c r="B48" t="s">
-        <v>186</v>
       </c>
       <c r="C48" t="n">
         <v>8.5</v>
@@ -7489,10 +8589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" t="s">
         <v>187</v>
-      </c>
-      <c r="B49" t="s">
-        <v>188</v>
       </c>
       <c r="C49" t="n">
         <v>7.5</v>
@@ -7512,10 +8612,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" t="s">
         <v>196</v>
-      </c>
-      <c r="B50" t="s">
-        <v>197</v>
       </c>
       <c r="C50" t="n">
         <v>8</v>
@@ -7535,10 +8635,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>197</v>
+      </c>
+      <c r="B51" t="s">
         <v>198</v>
-      </c>
-      <c r="B51" t="s">
-        <v>199</v>
       </c>
       <c r="C51" t="n">
         <v>7</v>
@@ -7558,10 +8658,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" t="s">
         <v>200</v>
-      </c>
-      <c r="B52" t="s">
-        <v>201</v>
       </c>
       <c r="C52" t="n">
         <v>7.5</v>
@@ -7581,10 +8681,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" t="s">
         <v>202</v>
-      </c>
-      <c r="B53" t="s">
-        <v>203</v>
       </c>
       <c r="C53" t="n">
         <v>8</v>
@@ -7604,10 +8704,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" t="s">
         <v>204</v>
-      </c>
-      <c r="B54" t="s">
-        <v>205</v>
       </c>
       <c r="C54" t="n">
         <v>7</v>
@@ -7627,10 +8727,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" t="s">
         <v>206</v>
-      </c>
-      <c r="B55" t="s">
-        <v>207</v>
       </c>
       <c r="C55" t="n">
         <v>8.5</v>
@@ -7650,10 +8750,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" t="s">
         <v>223</v>
-      </c>
-      <c r="B56" t="s">
-        <v>224</v>
       </c>
       <c r="C56" t="n">
         <v>8.5</v>
@@ -7673,10 +8773,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>224</v>
+      </c>
+      <c r="B57" t="s">
         <v>225</v>
-      </c>
-      <c r="B57" t="s">
-        <v>226</v>
       </c>
       <c r="C57" t="n">
         <v>8</v>
@@ -7696,10 +8796,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>226</v>
+      </c>
+      <c r="B58" t="s">
         <v>227</v>
-      </c>
-      <c r="B58" t="s">
-        <v>228</v>
       </c>
       <c r="C58" t="n">
         <v>6.5</v>
@@ -7719,10 +8819,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>228</v>
+      </c>
+      <c r="B59" t="s">
         <v>229</v>
-      </c>
-      <c r="B59" t="s">
-        <v>230</v>
       </c>
       <c r="C59" t="n">
         <v>7</v>
@@ -7742,10 +8842,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" t="s">
         <v>231</v>
-      </c>
-      <c r="B60" t="s">
-        <v>232</v>
       </c>
       <c r="C60" t="n">
         <v>8</v>
@@ -7761,6 +8861,52 @@
       </c>
       <c r="G60" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>232</v>
+      </c>
+      <c r="B61" t="s">
+        <v>233</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>234</v>
+      </c>
+      <c r="B62" t="s">
+        <v>235</v>
+      </c>
+      <c r="C62" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="256">
   <si>
     <t>Phase</t>
   </si>
@@ -773,6 +773,18 @@
   </si>
   <si>
     <t xml:space="preserve">Vestibular Balance (Vertical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-17 15:01:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-18 08:38:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-18</t>
   </si>
 </sst>
 </file>
@@ -8909,6 +8921,52 @@
         <v>3</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>253</v>
+      </c>
+      <c r="B63" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>255</v>
+      </c>
+      <c r="B64" t="s">
+        <v>256</v>
+      </c>
+      <c r="C64" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="258">
   <si>
     <t>Phase</t>
   </si>
@@ -785,6 +785,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19 16:24:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19</t>
   </si>
 </sst>
 </file>
@@ -8967,6 +8973,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>257</v>
+      </c>
+      <c r="B65" t="s">
+        <v>258</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="265">
   <si>
     <t>Phase</t>
   </si>
@@ -791,6 +791,27 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-21 12:16:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Hop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triple Hop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg</t>
   </si>
 </sst>
 </file>
@@ -7487,6 +7508,500 @@
         <v>246</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>3</v>
+      </c>
+      <c r="B245" t="s">
+        <v>261</v>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>46102.5126323749</v>
+      </c>
+      <c r="E245" t="s">
+        <v>244</v>
+      </c>
+      <c r="F245" t="n">
+        <v>70</v>
+      </c>
+      <c r="G245" t="s">
+        <v>245</v>
+      </c>
+      <c r="H245" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>3</v>
+      </c>
+      <c r="B246" t="s">
+        <v>261</v>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>46102.5126703389</v>
+      </c>
+      <c r="E246" t="s">
+        <v>244</v>
+      </c>
+      <c r="F246" t="n">
+        <v>75</v>
+      </c>
+      <c r="G246" t="s">
+        <v>245</v>
+      </c>
+      <c r="H246" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>3</v>
+      </c>
+      <c r="B247" t="s">
+        <v>261</v>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>46102.5127515646</v>
+      </c>
+      <c r="E247" t="s">
+        <v>247</v>
+      </c>
+      <c r="F247" t="n">
+        <v>125</v>
+      </c>
+      <c r="G247" t="s">
+        <v>245</v>
+      </c>
+      <c r="H247" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>3</v>
+      </c>
+      <c r="B248" t="s">
+        <v>261</v>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>46102.5128015431</v>
+      </c>
+      <c r="E248" t="s">
+        <v>247</v>
+      </c>
+      <c r="F248" t="n">
+        <v>126</v>
+      </c>
+      <c r="G248" t="s">
+        <v>245</v>
+      </c>
+      <c r="H248" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>3</v>
+      </c>
+      <c r="B249" t="s">
+        <v>262</v>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>46102.5129456329</v>
+      </c>
+      <c r="E249" t="s">
+        <v>244</v>
+      </c>
+      <c r="F249" t="n">
+        <v>472</v>
+      </c>
+      <c r="G249" t="s">
+        <v>245</v>
+      </c>
+      <c r="H249" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>3</v>
+      </c>
+      <c r="B250" t="s">
+        <v>262</v>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>46102.5129859691</v>
+      </c>
+      <c r="E250" t="s">
+        <v>244</v>
+      </c>
+      <c r="F250" t="n">
+        <v>475</v>
+      </c>
+      <c r="G250" t="s">
+        <v>245</v>
+      </c>
+      <c r="H250" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>3</v>
+      </c>
+      <c r="B251" t="s">
+        <v>262</v>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>46102.5130910233</v>
+      </c>
+      <c r="E251" t="s">
+        <v>247</v>
+      </c>
+      <c r="F251" t="n">
+        <v>548</v>
+      </c>
+      <c r="G251" t="s">
+        <v>245</v>
+      </c>
+      <c r="H251" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>3</v>
+      </c>
+      <c r="B252" t="s">
+        <v>262</v>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>46102.5131404206</v>
+      </c>
+      <c r="E252" t="s">
+        <v>247</v>
+      </c>
+      <c r="F252" t="n">
+        <v>540</v>
+      </c>
+      <c r="G252" t="s">
+        <v>245</v>
+      </c>
+      <c r="H252" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>3</v>
+      </c>
+      <c r="B253" t="s">
+        <v>243</v>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>46102.5133358003</v>
+      </c>
+      <c r="E253" t="s">
+        <v>244</v>
+      </c>
+      <c r="F253" t="n">
+        <v>412</v>
+      </c>
+      <c r="G253" t="s">
+        <v>245</v>
+      </c>
+      <c r="H253" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>3</v>
+      </c>
+      <c r="B254" t="s">
+        <v>243</v>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>46102.5133780618</v>
+      </c>
+      <c r="E254" t="s">
+        <v>244</v>
+      </c>
+      <c r="F254" t="n">
+        <v>418</v>
+      </c>
+      <c r="G254" t="s">
+        <v>245</v>
+      </c>
+      <c r="H254" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>3</v>
+      </c>
+      <c r="B255" t="s">
+        <v>243</v>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>46102.5134359822</v>
+      </c>
+      <c r="E255" t="s">
+        <v>247</v>
+      </c>
+      <c r="F255" t="n">
+        <v>502</v>
+      </c>
+      <c r="G255" t="s">
+        <v>245</v>
+      </c>
+      <c r="H255" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>3</v>
+      </c>
+      <c r="B256" t="s">
+        <v>243</v>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>46102.5134768592</v>
+      </c>
+      <c r="E256" t="s">
+        <v>247</v>
+      </c>
+      <c r="F256" t="n">
+        <v>505</v>
+      </c>
+      <c r="G256" t="s">
+        <v>245</v>
+      </c>
+      <c r="H256" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>3</v>
+      </c>
+      <c r="B257" t="s">
+        <v>248</v>
+      </c>
+      <c r="C257" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>46102.5135731082</v>
+      </c>
+      <c r="E257" t="s">
+        <v>244</v>
+      </c>
+      <c r="F257" t="n">
+        <v>34</v>
+      </c>
+      <c r="G257" t="s">
+        <v>249</v>
+      </c>
+      <c r="H257" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>3</v>
+      </c>
+      <c r="B258" t="s">
+        <v>248</v>
+      </c>
+      <c r="C258" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>46102.5136335278</v>
+      </c>
+      <c r="E258" t="s">
+        <v>247</v>
+      </c>
+      <c r="F258" t="n">
+        <v>44</v>
+      </c>
+      <c r="G258" t="s">
+        <v>249</v>
+      </c>
+      <c r="H258" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>3</v>
+      </c>
+      <c r="B259" t="s">
+        <v>263</v>
+      </c>
+      <c r="C259" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>46102.514064989</v>
+      </c>
+      <c r="E259" t="s">
+        <v>264</v>
+      </c>
+      <c r="F259" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G259" t="s">
+        <v>265</v>
+      </c>
+      <c r="H259" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>3</v>
+      </c>
+      <c r="B260" t="s">
+        <v>250</v>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>46102.5143092947</v>
+      </c>
+      <c r="E260" t="s">
+        <v>244</v>
+      </c>
+      <c r="F260" t="n">
+        <v>8</v>
+      </c>
+      <c r="G260" t="s">
+        <v>251</v>
+      </c>
+      <c r="H260" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>3</v>
+      </c>
+      <c r="B261" t="s">
+        <v>250</v>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>46102.5143575572</v>
+      </c>
+      <c r="E261" t="s">
+        <v>247</v>
+      </c>
+      <c r="F261" t="n">
+        <v>15</v>
+      </c>
+      <c r="G261" t="s">
+        <v>251</v>
+      </c>
+      <c r="H261" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>3</v>
+      </c>
+      <c r="B262" t="s">
+        <v>252</v>
+      </c>
+      <c r="C262" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>46102.5145357721</v>
+      </c>
+      <c r="E262" t="s">
+        <v>244</v>
+      </c>
+      <c r="F262" t="n">
+        <v>10</v>
+      </c>
+      <c r="G262" t="s">
+        <v>251</v>
+      </c>
+      <c r="H262" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>3</v>
+      </c>
+      <c r="B263" t="s">
+        <v>252</v>
+      </c>
+      <c r="C263" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>46102.5145796891</v>
+      </c>
+      <c r="E263" t="s">
+        <v>247</v>
+      </c>
+      <c r="F263" t="n">
+        <v>15</v>
+      </c>
+      <c r="G263" t="s">
+        <v>251</v>
+      </c>
+      <c r="H263" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8996,6 +9511,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="267">
   <si>
     <t>Phase</t>
   </si>
@@ -812,6 +812,12 @@
   </si>
   <si>
     <t xml:space="preserve">kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-23 08:59:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-23</t>
   </si>
 </sst>
 </file>
@@ -9534,6 +9540,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>266</v>
+      </c>
+      <c r="B67" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="271">
   <si>
     <t>Phase</t>
   </si>
@@ -818,6 +818,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-25 14:36:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-30 09:35:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-30</t>
   </si>
 </sst>
 </file>
@@ -9563,6 +9575,52 @@
         <v>2</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>270</v>
+      </c>
+      <c r="B69" t="s">
+        <v>271</v>
+      </c>
+      <c r="C69" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="276">
   <si>
     <t>Phase</t>
   </si>
@@ -830,6 +830,21 @@
   </si>
   <si>
     <t xml:space="preserve">2026-03-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-09 09:39:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Postero-Medial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y-Balance (Postero-Lateral)</t>
   </si>
 </sst>
 </file>
@@ -8020,6 +8035,968 @@
         <v>246</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2</v>
+      </c>
+      <c r="B264" t="s">
+        <v>263</v>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>46121.414234145</v>
+      </c>
+      <c r="E264" t="s">
+        <v>264</v>
+      </c>
+      <c r="F264" t="n">
+        <v>110</v>
+      </c>
+      <c r="G264" t="s">
+        <v>265</v>
+      </c>
+      <c r="H264" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>3</v>
+      </c>
+      <c r="B265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C265" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>46121.4148473212</v>
+      </c>
+      <c r="E265" t="s">
+        <v>244</v>
+      </c>
+      <c r="F265" t="n">
+        <v>95</v>
+      </c>
+      <c r="G265" t="s">
+        <v>245</v>
+      </c>
+      <c r="H265" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>3</v>
+      </c>
+      <c r="B266" t="s">
+        <v>261</v>
+      </c>
+      <c r="C266" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>46121.414882379</v>
+      </c>
+      <c r="E266" t="s">
+        <v>244</v>
+      </c>
+      <c r="F266" t="n">
+        <v>97</v>
+      </c>
+      <c r="G266" t="s">
+        <v>245</v>
+      </c>
+      <c r="H266" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>3</v>
+      </c>
+      <c r="B267" t="s">
+        <v>261</v>
+      </c>
+      <c r="C267" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>46121.4149635886</v>
+      </c>
+      <c r="E267" t="s">
+        <v>247</v>
+      </c>
+      <c r="F267" t="n">
+        <v>128</v>
+      </c>
+      <c r="G267" t="s">
+        <v>245</v>
+      </c>
+      <c r="H267" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>3</v>
+      </c>
+      <c r="B268" t="s">
+        <v>261</v>
+      </c>
+      <c r="C268" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>46121.4150425474</v>
+      </c>
+      <c r="E268" t="s">
+        <v>247</v>
+      </c>
+      <c r="F268" t="n">
+        <v>130</v>
+      </c>
+      <c r="G268" t="s">
+        <v>245</v>
+      </c>
+      <c r="H268" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>3</v>
+      </c>
+      <c r="B269" t="s">
+        <v>262</v>
+      </c>
+      <c r="C269" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>46121.4153051885</v>
+      </c>
+      <c r="E269" t="s">
+        <v>244</v>
+      </c>
+      <c r="F269" t="n">
+        <v>500</v>
+      </c>
+      <c r="G269" t="s">
+        <v>245</v>
+      </c>
+      <c r="H269" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>3</v>
+      </c>
+      <c r="B270" t="s">
+        <v>262</v>
+      </c>
+      <c r="C270" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>46121.4153537579</v>
+      </c>
+      <c r="E270" t="s">
+        <v>244</v>
+      </c>
+      <c r="F270" t="n">
+        <v>506</v>
+      </c>
+      <c r="G270" t="s">
+        <v>245</v>
+      </c>
+      <c r="H270" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>3</v>
+      </c>
+      <c r="B271" t="s">
+        <v>262</v>
+      </c>
+      <c r="C271" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>46121.4154328088</v>
+      </c>
+      <c r="E271" t="s">
+        <v>247</v>
+      </c>
+      <c r="F271" t="n">
+        <v>550</v>
+      </c>
+      <c r="G271" t="s">
+        <v>245</v>
+      </c>
+      <c r="H271" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>3</v>
+      </c>
+      <c r="B272" t="s">
+        <v>262</v>
+      </c>
+      <c r="C272" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>46121.4154681662</v>
+      </c>
+      <c r="E272" t="s">
+        <v>247</v>
+      </c>
+      <c r="F272" t="n">
+        <v>552</v>
+      </c>
+      <c r="G272" t="s">
+        <v>245</v>
+      </c>
+      <c r="H272" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>3</v>
+      </c>
+      <c r="B273" t="s">
+        <v>243</v>
+      </c>
+      <c r="C273" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>46121.4157348934</v>
+      </c>
+      <c r="E273" t="s">
+        <v>244</v>
+      </c>
+      <c r="F273" t="n">
+        <v>444</v>
+      </c>
+      <c r="G273" t="s">
+        <v>245</v>
+      </c>
+      <c r="H273" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>3</v>
+      </c>
+      <c r="B274" t="s">
+        <v>243</v>
+      </c>
+      <c r="C274" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>46121.415766168</v>
+      </c>
+      <c r="E274" t="s">
+        <v>244</v>
+      </c>
+      <c r="F274" t="n">
+        <v>450</v>
+      </c>
+      <c r="G274" t="s">
+        <v>245</v>
+      </c>
+      <c r="H274" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>3</v>
+      </c>
+      <c r="B275" t="s">
+        <v>243</v>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>46121.4158275735</v>
+      </c>
+      <c r="E275" t="s">
+        <v>247</v>
+      </c>
+      <c r="F275" t="n">
+        <v>505</v>
+      </c>
+      <c r="G275" t="s">
+        <v>245</v>
+      </c>
+      <c r="H275" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>3</v>
+      </c>
+      <c r="B276" t="s">
+        <v>243</v>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>46121.4158663843</v>
+      </c>
+      <c r="E276" t="s">
+        <v>247</v>
+      </c>
+      <c r="F276" t="n">
+        <v>510</v>
+      </c>
+      <c r="G276" t="s">
+        <v>245</v>
+      </c>
+      <c r="H276" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>3</v>
+      </c>
+      <c r="B277" t="s">
+        <v>248</v>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>46121.4162217065</v>
+      </c>
+      <c r="E277" t="s">
+        <v>244</v>
+      </c>
+      <c r="F277" t="n">
+        <v>38</v>
+      </c>
+      <c r="G277" t="s">
+        <v>249</v>
+      </c>
+      <c r="H277" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>3</v>
+      </c>
+      <c r="B278" t="s">
+        <v>248</v>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>46121.4162680693</v>
+      </c>
+      <c r="E278" t="s">
+        <v>247</v>
+      </c>
+      <c r="F278" t="n">
+        <v>44</v>
+      </c>
+      <c r="G278" t="s">
+        <v>249</v>
+      </c>
+      <c r="H278" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>3</v>
+      </c>
+      <c r="B279" t="s">
+        <v>274</v>
+      </c>
+      <c r="C279" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>46121.4170161986</v>
+      </c>
+      <c r="E279" t="s">
+        <v>244</v>
+      </c>
+      <c r="F279" t="n">
+        <v>63</v>
+      </c>
+      <c r="G279" t="s">
+        <v>245</v>
+      </c>
+      <c r="H279" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>3</v>
+      </c>
+      <c r="B280" t="s">
+        <v>274</v>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>46121.4170551778</v>
+      </c>
+      <c r="E280" t="s">
+        <v>244</v>
+      </c>
+      <c r="F280" t="n">
+        <v>64</v>
+      </c>
+      <c r="G280" t="s">
+        <v>245</v>
+      </c>
+      <c r="H280" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>3</v>
+      </c>
+      <c r="B281" t="s">
+        <v>274</v>
+      </c>
+      <c r="C281" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>46121.4170887981</v>
+      </c>
+      <c r="E281" t="s">
+        <v>244</v>
+      </c>
+      <c r="F281" t="n">
+        <v>65</v>
+      </c>
+      <c r="G281" t="s">
+        <v>245</v>
+      </c>
+      <c r="H281" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>3</v>
+      </c>
+      <c r="B282" t="s">
+        <v>274</v>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>46121.4171635599</v>
+      </c>
+      <c r="E282" t="s">
+        <v>247</v>
+      </c>
+      <c r="F282" t="n">
+        <v>66</v>
+      </c>
+      <c r="G282" t="s">
+        <v>245</v>
+      </c>
+      <c r="H282" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>3</v>
+      </c>
+      <c r="B283" t="s">
+        <v>274</v>
+      </c>
+      <c r="C283" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>46121.4171970885</v>
+      </c>
+      <c r="E283" t="s">
+        <v>247</v>
+      </c>
+      <c r="F283" t="n">
+        <v>67</v>
+      </c>
+      <c r="G283" t="s">
+        <v>245</v>
+      </c>
+      <c r="H283" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>3</v>
+      </c>
+      <c r="B284" t="s">
+        <v>274</v>
+      </c>
+      <c r="C284" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>46121.417227802</v>
+      </c>
+      <c r="E284" t="s">
+        <v>247</v>
+      </c>
+      <c r="F284" t="n">
+        <v>68</v>
+      </c>
+      <c r="G284" t="s">
+        <v>245</v>
+      </c>
+      <c r="H284" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>3</v>
+      </c>
+      <c r="B285" t="s">
+        <v>275</v>
+      </c>
+      <c r="C285" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>46121.4174049122</v>
+      </c>
+      <c r="E285" t="s">
+        <v>244</v>
+      </c>
+      <c r="F285" t="n">
+        <v>97</v>
+      </c>
+      <c r="G285" t="s">
+        <v>245</v>
+      </c>
+      <c r="H285" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>3</v>
+      </c>
+      <c r="B286" t="s">
+        <v>275</v>
+      </c>
+      <c r="C286" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>46121.4174323628</v>
+      </c>
+      <c r="E286" t="s">
+        <v>244</v>
+      </c>
+      <c r="F286" t="n">
+        <v>98</v>
+      </c>
+      <c r="G286" t="s">
+        <v>245</v>
+      </c>
+      <c r="H286" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>3</v>
+      </c>
+      <c r="B287" t="s">
+        <v>275</v>
+      </c>
+      <c r="C287" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>46121.4174661364</v>
+      </c>
+      <c r="E287" t="s">
+        <v>244</v>
+      </c>
+      <c r="F287" t="n">
+        <v>99</v>
+      </c>
+      <c r="G287" t="s">
+        <v>245</v>
+      </c>
+      <c r="H287" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>3</v>
+      </c>
+      <c r="B288" t="s">
+        <v>275</v>
+      </c>
+      <c r="C288" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>46121.4175279553</v>
+      </c>
+      <c r="E288" t="s">
+        <v>247</v>
+      </c>
+      <c r="F288" t="n">
+        <v>101</v>
+      </c>
+      <c r="G288" t="s">
+        <v>245</v>
+      </c>
+      <c r="H288" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>3</v>
+      </c>
+      <c r="B289" t="s">
+        <v>275</v>
+      </c>
+      <c r="C289" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>46121.4175580494</v>
+      </c>
+      <c r="E289" t="s">
+        <v>247</v>
+      </c>
+      <c r="F289" t="n">
+        <v>102</v>
+      </c>
+      <c r="G289" t="s">
+        <v>245</v>
+      </c>
+      <c r="H289" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>3</v>
+      </c>
+      <c r="B290" t="s">
+        <v>275</v>
+      </c>
+      <c r="C290" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>46121.4175887931</v>
+      </c>
+      <c r="E290" t="s">
+        <v>247</v>
+      </c>
+      <c r="F290" t="n">
+        <v>103</v>
+      </c>
+      <c r="G290" t="s">
+        <v>245</v>
+      </c>
+      <c r="H290" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>3</v>
+      </c>
+      <c r="B291" t="s">
+        <v>276</v>
+      </c>
+      <c r="C291" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>46121.4177394025</v>
+      </c>
+      <c r="E291" t="s">
+        <v>244</v>
+      </c>
+      <c r="F291" t="n">
+        <v>86</v>
+      </c>
+      <c r="G291" t="s">
+        <v>245</v>
+      </c>
+      <c r="H291" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>3</v>
+      </c>
+      <c r="B292" t="s">
+        <v>276</v>
+      </c>
+      <c r="C292" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>46121.4177718403</v>
+      </c>
+      <c r="E292" t="s">
+        <v>244</v>
+      </c>
+      <c r="F292" t="n">
+        <v>87</v>
+      </c>
+      <c r="G292" t="s">
+        <v>245</v>
+      </c>
+      <c r="H292" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>3</v>
+      </c>
+      <c r="B293" t="s">
+        <v>276</v>
+      </c>
+      <c r="C293" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>46121.4178017793</v>
+      </c>
+      <c r="E293" t="s">
+        <v>244</v>
+      </c>
+      <c r="F293" t="n">
+        <v>88</v>
+      </c>
+      <c r="G293" t="s">
+        <v>245</v>
+      </c>
+      <c r="H293" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>3</v>
+      </c>
+      <c r="B294" t="s">
+        <v>276</v>
+      </c>
+      <c r="C294" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>46121.4180006801</v>
+      </c>
+      <c r="E294" t="s">
+        <v>247</v>
+      </c>
+      <c r="F294" t="n">
+        <v>89</v>
+      </c>
+      <c r="G294" t="s">
+        <v>245</v>
+      </c>
+      <c r="H294" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>3</v>
+      </c>
+      <c r="B295" t="s">
+        <v>276</v>
+      </c>
+      <c r="C295" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>46121.4180265623</v>
+      </c>
+      <c r="E295" t="s">
+        <v>247</v>
+      </c>
+      <c r="F295" t="n">
+        <v>90</v>
+      </c>
+      <c r="G295" t="s">
+        <v>245</v>
+      </c>
+      <c r="H295" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>3</v>
+      </c>
+      <c r="B296" t="s">
+        <v>276</v>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>46121.4180624839</v>
+      </c>
+      <c r="E296" t="s">
+        <v>247</v>
+      </c>
+      <c r="F296" t="n">
+        <v>91</v>
+      </c>
+      <c r="G296" t="s">
+        <v>245</v>
+      </c>
+      <c r="H296" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>3</v>
+      </c>
+      <c r="B297" t="s">
+        <v>252</v>
+      </c>
+      <c r="C297" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>46121.4184952048</v>
+      </c>
+      <c r="E297" t="s">
+        <v>244</v>
+      </c>
+      <c r="F297" t="n">
+        <v>15</v>
+      </c>
+      <c r="G297" t="s">
+        <v>251</v>
+      </c>
+      <c r="H297" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>3</v>
+      </c>
+      <c r="B298" t="s">
+        <v>252</v>
+      </c>
+      <c r="C298" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>46121.418536757</v>
+      </c>
+      <c r="E298" t="s">
+        <v>247</v>
+      </c>
+      <c r="F298" t="n">
+        <v>15</v>
+      </c>
+      <c r="G298" t="s">
+        <v>251</v>
+      </c>
+      <c r="H298" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>3</v>
+      </c>
+      <c r="B299" t="s">
+        <v>250</v>
+      </c>
+      <c r="C299" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>46121.4186393317</v>
+      </c>
+      <c r="E299" t="s">
+        <v>244</v>
+      </c>
+      <c r="F299" t="n">
+        <v>12</v>
+      </c>
+      <c r="G299" t="s">
+        <v>251</v>
+      </c>
+      <c r="H299" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>3</v>
+      </c>
+      <c r="B300" t="s">
+        <v>250</v>
+      </c>
+      <c r="C300" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>46121.4186860359</v>
+      </c>
+      <c r="E300" t="s">
+        <v>247</v>
+      </c>
+      <c r="F300" t="n">
+        <v>15</v>
+      </c>
+      <c r="G300" t="s">
+        <v>251</v>
+      </c>
+      <c r="H300" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9621,6 +10598,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>272</v>
+      </c>
+      <c r="B70" t="s">
+        <v>273</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="278">
   <si>
     <t>Phase</t>
   </si>
@@ -845,6 +845,12 @@
   </si>
   <si>
     <t xml:space="preserve">Y-Balance (Postero-Lateral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-14 09:51:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-14</t>
   </si>
 </sst>
 </file>
@@ -10621,6 +10627,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>277</v>
+      </c>
+      <c r="B71" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="280">
   <si>
     <t>Phase</t>
   </si>
@@ -851,6 +851,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-04-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-01 15:59:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-01</t>
   </si>
 </sst>
 </file>
@@ -10650,6 +10656,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>279</v>
+      </c>
+      <c r="B72" t="s">
+        <v>280</v>
+      </c>
+      <c r="C72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -9009,6 +9009,448 @@
         <v>246</v>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>3</v>
+      </c>
+      <c r="B301" t="s">
+        <v>261</v>
+      </c>
+      <c r="C301" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>46143.6793276597</v>
+      </c>
+      <c r="E301" t="s">
+        <v>244</v>
+      </c>
+      <c r="F301" t="n">
+        <v>117</v>
+      </c>
+      <c r="G301" t="s">
+        <v>245</v>
+      </c>
+      <c r="H301" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>3</v>
+      </c>
+      <c r="B302" t="s">
+        <v>261</v>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>46143.6793804742</v>
+      </c>
+      <c r="E302" t="s">
+        <v>244</v>
+      </c>
+      <c r="F302" t="n">
+        <v>119</v>
+      </c>
+      <c r="G302" t="s">
+        <v>245</v>
+      </c>
+      <c r="H302" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>3</v>
+      </c>
+      <c r="B303" t="s">
+        <v>261</v>
+      </c>
+      <c r="C303" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>46143.6794615428</v>
+      </c>
+      <c r="E303" t="s">
+        <v>247</v>
+      </c>
+      <c r="F303" t="n">
+        <v>126</v>
+      </c>
+      <c r="G303" t="s">
+        <v>245</v>
+      </c>
+      <c r="H303" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>3</v>
+      </c>
+      <c r="B304" t="s">
+        <v>261</v>
+      </c>
+      <c r="C304" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>46143.679513584</v>
+      </c>
+      <c r="E304" t="s">
+        <v>247</v>
+      </c>
+      <c r="F304" t="n">
+        <v>130</v>
+      </c>
+      <c r="G304" t="s">
+        <v>245</v>
+      </c>
+      <c r="H304" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>3</v>
+      </c>
+      <c r="B305" t="s">
+        <v>262</v>
+      </c>
+      <c r="C305" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>46143.6800708549</v>
+      </c>
+      <c r="E305" t="s">
+        <v>244</v>
+      </c>
+      <c r="F305" t="n">
+        <v>539</v>
+      </c>
+      <c r="G305" t="s">
+        <v>245</v>
+      </c>
+      <c r="H305" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>3</v>
+      </c>
+      <c r="B306" t="s">
+        <v>262</v>
+      </c>
+      <c r="C306" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>46143.680112204</v>
+      </c>
+      <c r="E306" t="s">
+        <v>244</v>
+      </c>
+      <c r="F306" t="n">
+        <v>541</v>
+      </c>
+      <c r="G306" t="s">
+        <v>245</v>
+      </c>
+      <c r="H306" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>3</v>
+      </c>
+      <c r="B307" t="s">
+        <v>262</v>
+      </c>
+      <c r="C307" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>46143.6801625616</v>
+      </c>
+      <c r="E307" t="s">
+        <v>247</v>
+      </c>
+      <c r="F307" t="n">
+        <v>560</v>
+      </c>
+      <c r="G307" t="s">
+        <v>245</v>
+      </c>
+      <c r="H307" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>3</v>
+      </c>
+      <c r="B308" t="s">
+        <v>262</v>
+      </c>
+      <c r="C308" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>46143.6802734163</v>
+      </c>
+      <c r="E308" t="s">
+        <v>247</v>
+      </c>
+      <c r="F308" t="n">
+        <v>562</v>
+      </c>
+      <c r="G308" t="s">
+        <v>245</v>
+      </c>
+      <c r="H308" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>3</v>
+      </c>
+      <c r="B309" t="s">
+        <v>243</v>
+      </c>
+      <c r="C309" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>46143.6804487589</v>
+      </c>
+      <c r="E309" t="s">
+        <v>244</v>
+      </c>
+      <c r="F309" t="n">
+        <v>480</v>
+      </c>
+      <c r="G309" t="s">
+        <v>245</v>
+      </c>
+      <c r="H309" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>3</v>
+      </c>
+      <c r="B310" t="s">
+        <v>243</v>
+      </c>
+      <c r="C310" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>46143.6804895137</v>
+      </c>
+      <c r="E310" t="s">
+        <v>244</v>
+      </c>
+      <c r="F310" t="n">
+        <v>484</v>
+      </c>
+      <c r="G310" t="s">
+        <v>245</v>
+      </c>
+      <c r="H310" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>3</v>
+      </c>
+      <c r="B311" t="s">
+        <v>243</v>
+      </c>
+      <c r="C311" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>46143.6805467703</v>
+      </c>
+      <c r="E311" t="s">
+        <v>247</v>
+      </c>
+      <c r="F311" t="n">
+        <v>512</v>
+      </c>
+      <c r="G311" t="s">
+        <v>245</v>
+      </c>
+      <c r="H311" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>3</v>
+      </c>
+      <c r="B312" t="s">
+        <v>243</v>
+      </c>
+      <c r="C312" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>46143.6806160115</v>
+      </c>
+      <c r="E312" t="s">
+        <v>247</v>
+      </c>
+      <c r="F312" t="n">
+        <v>506</v>
+      </c>
+      <c r="G312" t="s">
+        <v>245</v>
+      </c>
+      <c r="H312" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>3</v>
+      </c>
+      <c r="B313" t="s">
+        <v>248</v>
+      </c>
+      <c r="C313" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>46143.6807902012</v>
+      </c>
+      <c r="E313" t="s">
+        <v>244</v>
+      </c>
+      <c r="F313" t="n">
+        <v>41</v>
+      </c>
+      <c r="G313" t="s">
+        <v>249</v>
+      </c>
+      <c r="H313" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>3</v>
+      </c>
+      <c r="B314" t="s">
+        <v>248</v>
+      </c>
+      <c r="C314" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>46143.6808454038</v>
+      </c>
+      <c r="E314" t="s">
+        <v>247</v>
+      </c>
+      <c r="F314" t="n">
+        <v>46</v>
+      </c>
+      <c r="G314" t="s">
+        <v>249</v>
+      </c>
+      <c r="H314" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>3</v>
+      </c>
+      <c r="B315" t="s">
+        <v>263</v>
+      </c>
+      <c r="C315" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>46143.6816202449</v>
+      </c>
+      <c r="E315" t="s">
+        <v>264</v>
+      </c>
+      <c r="F315" t="n">
+        <v>126</v>
+      </c>
+      <c r="G315" t="s">
+        <v>265</v>
+      </c>
+      <c r="H315" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>3</v>
+      </c>
+      <c r="B316" t="s">
+        <v>250</v>
+      </c>
+      <c r="C316" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D316" s="3" t="n">
+        <v>46143.6818562279</v>
+      </c>
+      <c r="E316" t="s">
+        <v>244</v>
+      </c>
+      <c r="F316" t="n">
+        <v>15</v>
+      </c>
+      <c r="G316" t="s">
+        <v>251</v>
+      </c>
+      <c r="H316" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>3</v>
+      </c>
+      <c r="B317" t="s">
+        <v>250</v>
+      </c>
+      <c r="C317" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>46143.6818989909</v>
+      </c>
+      <c r="E317" t="s">
+        <v>247</v>
+      </c>
+      <c r="F317" t="n">
+        <v>15</v>
+      </c>
+      <c r="G317" t="s">
+        <v>251</v>
+      </c>
+      <c r="H317" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="287">
   <si>
     <t>Phase</t>
   </si>
@@ -857,6 +857,27 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-04 11:36:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistol Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06 21:52:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-07 10:45:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-07</t>
   </si>
 </sst>
 </file>
@@ -9451,6 +9472,58 @@
         <v>246</v>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>4</v>
+      </c>
+      <c r="B318" t="s">
+        <v>283</v>
+      </c>
+      <c r="C318" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>46146.4841866197</v>
+      </c>
+      <c r="E318" t="s">
+        <v>244</v>
+      </c>
+      <c r="F318" t="n">
+        <v>2</v>
+      </c>
+      <c r="G318" t="s">
+        <v>249</v>
+      </c>
+      <c r="H318" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>4</v>
+      </c>
+      <c r="B319" t="s">
+        <v>283</v>
+      </c>
+      <c r="C319" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>46146.4842539634</v>
+      </c>
+      <c r="E319" t="s">
+        <v>247</v>
+      </c>
+      <c r="F319" t="n">
+        <v>4</v>
+      </c>
+      <c r="G319" t="s">
+        <v>249</v>
+      </c>
+      <c r="H319" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11121,6 +11194,75 @@
         <v>1</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>281</v>
+      </c>
+      <c r="B73" t="s">
+        <v>282</v>
+      </c>
+      <c r="C73" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>284</v>
+      </c>
+      <c r="B74" t="s">
+        <v>285</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>286</v>
+      </c>
+      <c r="B75" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="292">
   <si>
     <t>Phase</t>
   </si>
@@ -878,6 +878,21 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-08 12:02:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-09 09:34:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Rise</t>
   </si>
 </sst>
 </file>
@@ -9524,6 +9539,344 @@
         <v>246</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>3</v>
+      </c>
+      <c r="B320" t="s">
+        <v>261</v>
+      </c>
+      <c r="C320" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>46151.399077282</v>
+      </c>
+      <c r="E320" t="s">
+        <v>244</v>
+      </c>
+      <c r="F320" t="n">
+        <v>123</v>
+      </c>
+      <c r="G320" t="s">
+        <v>245</v>
+      </c>
+      <c r="H320" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>3</v>
+      </c>
+      <c r="B321" t="s">
+        <v>261</v>
+      </c>
+      <c r="C321" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>46151.3991169937</v>
+      </c>
+      <c r="E321" t="s">
+        <v>244</v>
+      </c>
+      <c r="F321" t="n">
+        <v>124</v>
+      </c>
+      <c r="G321" t="s">
+        <v>245</v>
+      </c>
+      <c r="H321" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>3</v>
+      </c>
+      <c r="B322" t="s">
+        <v>261</v>
+      </c>
+      <c r="C322" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>46151.399211145</v>
+      </c>
+      <c r="E322" t="s">
+        <v>247</v>
+      </c>
+      <c r="F322" t="n">
+        <v>130</v>
+      </c>
+      <c r="G322" t="s">
+        <v>245</v>
+      </c>
+      <c r="H322" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>3</v>
+      </c>
+      <c r="B323" t="s">
+        <v>261</v>
+      </c>
+      <c r="C323" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D323" s="3" t="n">
+        <v>46151.3992582157</v>
+      </c>
+      <c r="E323" t="s">
+        <v>247</v>
+      </c>
+      <c r="F323" t="n">
+        <v>128</v>
+      </c>
+      <c r="G323" t="s">
+        <v>245</v>
+      </c>
+      <c r="H323" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>3</v>
+      </c>
+      <c r="B324" t="s">
+        <v>243</v>
+      </c>
+      <c r="C324" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D324" s="3" t="n">
+        <v>46151.3994486112</v>
+      </c>
+      <c r="E324" t="s">
+        <v>244</v>
+      </c>
+      <c r="F324" t="n">
+        <v>490</v>
+      </c>
+      <c r="G324" t="s">
+        <v>245</v>
+      </c>
+      <c r="H324" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>3</v>
+      </c>
+      <c r="B325" t="s">
+        <v>243</v>
+      </c>
+      <c r="C325" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>46151.3995213927</v>
+      </c>
+      <c r="E325" t="s">
+        <v>244</v>
+      </c>
+      <c r="F325" t="n">
+        <v>492</v>
+      </c>
+      <c r="G325" t="s">
+        <v>245</v>
+      </c>
+      <c r="H325" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>3</v>
+      </c>
+      <c r="B326" t="s">
+        <v>243</v>
+      </c>
+      <c r="C326" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D326" s="3" t="n">
+        <v>46151.3995953551</v>
+      </c>
+      <c r="E326" t="s">
+        <v>247</v>
+      </c>
+      <c r="F326" t="n">
+        <v>508</v>
+      </c>
+      <c r="G326" t="s">
+        <v>245</v>
+      </c>
+      <c r="H326" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3</v>
+      </c>
+      <c r="B327" t="s">
+        <v>243</v>
+      </c>
+      <c r="C327" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D327" s="3" t="n">
+        <v>46151.399632053</v>
+      </c>
+      <c r="E327" t="s">
+        <v>247</v>
+      </c>
+      <c r="F327" t="n">
+        <v>512</v>
+      </c>
+      <c r="G327" t="s">
+        <v>245</v>
+      </c>
+      <c r="H327" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>3</v>
+      </c>
+      <c r="B328" t="s">
+        <v>248</v>
+      </c>
+      <c r="C328" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D328" s="3" t="n">
+        <v>46151.4001652398</v>
+      </c>
+      <c r="E328" t="s">
+        <v>244</v>
+      </c>
+      <c r="F328" t="n">
+        <v>42</v>
+      </c>
+      <c r="G328" t="s">
+        <v>249</v>
+      </c>
+      <c r="H328" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>3</v>
+      </c>
+      <c r="B329" t="s">
+        <v>248</v>
+      </c>
+      <c r="C329" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D329" s="3" t="n">
+        <v>46151.400208664</v>
+      </c>
+      <c r="E329" t="s">
+        <v>247</v>
+      </c>
+      <c r="F329" t="n">
+        <v>48</v>
+      </c>
+      <c r="G329" t="s">
+        <v>249</v>
+      </c>
+      <c r="H329" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>3</v>
+      </c>
+      <c r="B330" t="s">
+        <v>292</v>
+      </c>
+      <c r="C330" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D330" s="3" t="n">
+        <v>46151.4004444843</v>
+      </c>
+      <c r="E330" t="s">
+        <v>244</v>
+      </c>
+      <c r="F330" t="n">
+        <v>15</v>
+      </c>
+      <c r="G330" t="s">
+        <v>249</v>
+      </c>
+      <c r="H330" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>3</v>
+      </c>
+      <c r="B331" t="s">
+        <v>292</v>
+      </c>
+      <c r="C331" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>46151.4004809826</v>
+      </c>
+      <c r="E331" t="s">
+        <v>247</v>
+      </c>
+      <c r="F331" t="n">
+        <v>17</v>
+      </c>
+      <c r="G331" t="s">
+        <v>249</v>
+      </c>
+      <c r="H331" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>3</v>
+      </c>
+      <c r="B332" t="s">
+        <v>263</v>
+      </c>
+      <c r="C332" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>46151.4005990214</v>
+      </c>
+      <c r="E332" t="s">
+        <v>264</v>
+      </c>
+      <c r="F332" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G332" t="s">
+        <v>265</v>
+      </c>
+      <c r="H332" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11263,6 +11616,52 @@
         <v>1</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>288</v>
+      </c>
+      <c r="B76" t="s">
+        <v>289</v>
+      </c>
+      <c r="C76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>290</v>
+      </c>
+      <c r="B77" t="s">
+        <v>291</v>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="294">
   <si>
     <t>Phase</t>
   </si>
@@ -893,6 +893,12 @@
   </si>
   <si>
     <t xml:space="preserve">Single Leg Rise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-10 10:23:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-10</t>
   </si>
 </sst>
 </file>
@@ -11662,6 +11668,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>293</v>
+      </c>
+      <c r="B78" t="s">
+        <v>294</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="acl_rsi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t>Phase</t>
   </si>
@@ -745,169 +746,219 @@
     <t>Triple Hop</t>
   </si>
   <si>
-    <t xml:space="preserve">Triple Cross Over Hop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side Hop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vestibular Balance (Horizontal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vestibular Balance (Vertical)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-17 15:01:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-18 08:38:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-19 16:24:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-21 12:16:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Hop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triple Hop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrapBar Deadlift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-23 08:59:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-25 14:36:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-30 09:35:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-09 09:39:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Anterior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Postero-Medial)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y-Balance (Postero-Lateral)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-14 09:51:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-01 15:59:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-04 11:36:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pistol Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-06 21:52:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-07 10:45:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-08 12:02:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-09 09:34:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Leg Rise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-10 10:23:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-10</t>
+    <t>Triple Cross Over Hop</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Side Hop</t>
+  </si>
+  <si>
+    <t>reps</t>
+  </si>
+  <si>
+    <t>Vestibular Balance (Horizontal)</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>Vestibular Balance (Vertical)</t>
+  </si>
+  <si>
+    <t>2026-03-17 15:01:24</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18 08:38:20</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19 16:24:54</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-21 12:16:48</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>Single Leg Hop</t>
+  </si>
+  <si>
+    <t>Triple Hop</t>
+  </si>
+  <si>
+    <t>TrapBar Deadlift</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>2026-03-23 08:59:27</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-25 14:36:55</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-30 09:35:25</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-04-09 09:39:22</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>Y-Balance (Anterior)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Postero-Medial)</t>
+  </si>
+  <si>
+    <t>Y-Balance (Postero-Lateral)</t>
+  </si>
+  <si>
+    <t>2026-04-14 09:51:39</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-05-01 15:59:27</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-04 11:36:55</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>Pistol Squat</t>
+  </si>
+  <si>
+    <t>2026-05-06 21:52:49</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07 10:45:49</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08 12:02:50</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-09 09:34:17</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>Single Leg Rise</t>
+  </si>
+  <si>
+    <t>2026-05-10 10:23:47</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>q1</t>
+  </si>
+  <si>
+    <t>q2</t>
+  </si>
+  <si>
+    <t>q3</t>
+  </si>
+  <si>
+    <t>q4</t>
+  </si>
+  <si>
+    <t>q5</t>
+  </si>
+  <si>
+    <t>q6</t>
+  </si>
+  <si>
+    <t>q7</t>
+  </si>
+  <si>
+    <t>q8</t>
+  </si>
+  <si>
+    <t>q9</t>
+  </si>
+  <si>
+    <t>q10</t>
+  </si>
+  <si>
+    <t>q11</t>
+  </si>
+  <si>
+    <t>q12</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:13:43</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:15:37</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -943,11 +994,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5988,7 +6038,7 @@
         <v>2</v>
       </c>
       <c r="B183" t="s">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="C183" s="1" t="n">
         <v>46083</v>
@@ -7345,7 +7395,7 @@
       <c r="C235" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D235" s="3" t="n">
+      <c r="D235" s="2" t="n">
         <v>46097.6012139835</v>
       </c>
       <c r="E235" t="s">
@@ -7371,8 +7421,8 @@
       <c r="C236" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D236" s="3" t="n">
-        <v>46097.6012609843</v>
+      <c r="D236" s="2" t="n">
+        <v>46097.601260984302</v>
       </c>
       <c r="E236" t="s">
         <v>244</v>
@@ -7397,8 +7447,8 @@
       <c r="C237" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D237" s="3" t="n">
-        <v>46097.6013430131</v>
+      <c r="D237" s="2" t="n">
+        <v>46097.601343013099</v>
       </c>
       <c r="E237" t="s">
         <v>247</v>
@@ -7423,8 +7473,8 @@
       <c r="C238" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D238" s="3" t="n">
-        <v>46097.6014109983</v>
+      <c r="D238" s="2" t="n">
+        <v>46097.601410998301</v>
       </c>
       <c r="E238" t="s">
         <v>247</v>
@@ -7449,8 +7499,8 @@
       <c r="C239" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D239" s="3" t="n">
-        <v>46097.6154524684</v>
+      <c r="D239" s="2" t="n">
+        <v>46097.615452468403</v>
       </c>
       <c r="E239" t="s">
         <v>244</v>
@@ -7475,8 +7525,8 @@
       <c r="C240" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D240" s="3" t="n">
-        <v>46097.6155898686</v>
+      <c r="D240" s="2" t="n">
+        <v>46097.615589868597</v>
       </c>
       <c r="E240" t="s">
         <v>247</v>
@@ -7501,8 +7551,8 @@
       <c r="C241" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D241" s="3" t="n">
-        <v>46097.6404911276</v>
+      <c r="D241" s="2" t="n">
+        <v>46097.640491127597</v>
       </c>
       <c r="E241" t="s">
         <v>244</v>
@@ -7527,8 +7577,8 @@
       <c r="C242" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D242" s="3" t="n">
-        <v>46097.6405362685</v>
+      <c r="D242" s="2" t="n">
+        <v>46097.640536268496</v>
       </c>
       <c r="E242" t="s">
         <v>247</v>
@@ -7553,7 +7603,7 @@
       <c r="C243" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D243" s="3" t="n">
+      <c r="D243" s="2" t="n">
         <v>46097.6405887152</v>
       </c>
       <c r="E243" t="s">
@@ -7579,8 +7629,8 @@
       <c r="C244" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="D244" s="3" t="n">
-        <v>46097.640626837</v>
+      <c r="D244" s="2" t="n">
+        <v>46097.640626836997</v>
       </c>
       <c r="E244" t="s">
         <v>247</v>
@@ -7605,8 +7655,8 @@
       <c r="C245" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D245" s="3" t="n">
-        <v>46102.5126323749</v>
+      <c r="D245" s="2" t="n">
+        <v>46102.512632374899</v>
       </c>
       <c r="E245" t="s">
         <v>244</v>
@@ -7631,8 +7681,8 @@
       <c r="C246" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D246" s="3" t="n">
-        <v>46102.5126703389</v>
+      <c r="D246" s="2" t="n">
+        <v>46102.512670338903</v>
       </c>
       <c r="E246" t="s">
         <v>244</v>
@@ -7657,8 +7707,8 @@
       <c r="C247" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D247" s="3" t="n">
-        <v>46102.5127515646</v>
+      <c r="D247" s="2" t="n">
+        <v>46102.512751564602</v>
       </c>
       <c r="E247" t="s">
         <v>247</v>
@@ -7683,8 +7733,8 @@
       <c r="C248" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D248" s="3" t="n">
-        <v>46102.5128015431</v>
+      <c r="D248" s="2" t="n">
+        <v>46102.512801543096</v>
       </c>
       <c r="E248" t="s">
         <v>247</v>
@@ -7709,8 +7759,8 @@
       <c r="C249" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D249" s="3" t="n">
-        <v>46102.5129456329</v>
+      <c r="D249" s="2" t="n">
+        <v>46102.512945632901</v>
       </c>
       <c r="E249" t="s">
         <v>244</v>
@@ -7735,8 +7785,8 @@
       <c r="C250" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D250" s="3" t="n">
-        <v>46102.5129859691</v>
+      <c r="D250" s="2" t="n">
+        <v>46102.512985969101</v>
       </c>
       <c r="E250" t="s">
         <v>244</v>
@@ -7761,8 +7811,8 @@
       <c r="C251" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D251" s="3" t="n">
-        <v>46102.5130910233</v>
+      <c r="D251" s="2" t="n">
+        <v>46102.513091023298</v>
       </c>
       <c r="E251" t="s">
         <v>247</v>
@@ -7787,8 +7837,8 @@
       <c r="C252" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D252" s="3" t="n">
-        <v>46102.5131404206</v>
+      <c r="D252" s="2" t="n">
+        <v>46102.513140420597</v>
       </c>
       <c r="E252" t="s">
         <v>247</v>
@@ -7813,7 +7863,7 @@
       <c r="C253" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D253" s="3" t="n">
+      <c r="D253" s="2" t="n">
         <v>46102.5133358003</v>
       </c>
       <c r="E253" t="s">
@@ -7839,8 +7889,8 @@
       <c r="C254" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D254" s="3" t="n">
-        <v>46102.5133780618</v>
+      <c r="D254" s="2" t="n">
+        <v>46102.513378061798</v>
       </c>
       <c r="E254" t="s">
         <v>244</v>
@@ -7865,8 +7915,8 @@
       <c r="C255" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D255" s="3" t="n">
-        <v>46102.5134359822</v>
+      <c r="D255" s="2" t="n">
+        <v>46102.513435982197</v>
       </c>
       <c r="E255" t="s">
         <v>247</v>
@@ -7891,8 +7941,8 @@
       <c r="C256" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D256" s="3" t="n">
-        <v>46102.5134768592</v>
+      <c r="D256" s="2" t="n">
+        <v>46102.513476859203</v>
       </c>
       <c r="E256" t="s">
         <v>247</v>
@@ -7917,8 +7967,8 @@
       <c r="C257" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D257" s="3" t="n">
-        <v>46102.5135731082</v>
+      <c r="D257" s="2" t="n">
+        <v>46102.513573108197</v>
       </c>
       <c r="E257" t="s">
         <v>244</v>
@@ -7943,7 +7993,7 @@
       <c r="C258" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D258" s="3" t="n">
+      <c r="D258" s="2" t="n">
         <v>46102.5136335278</v>
       </c>
       <c r="E258" t="s">
@@ -7969,8 +8019,8 @@
       <c r="C259" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D259" s="3" t="n">
-        <v>46102.514064989</v>
+      <c r="D259" s="2" t="n">
+        <v>46102.514064989002</v>
       </c>
       <c r="E259" t="s">
         <v>264</v>
@@ -7995,8 +8045,8 @@
       <c r="C260" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D260" s="3" t="n">
-        <v>46102.5143092947</v>
+      <c r="D260" s="2" t="n">
+        <v>46102.514309294696</v>
       </c>
       <c r="E260" t="s">
         <v>244</v>
@@ -8021,7 +8071,7 @@
       <c r="C261" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D261" s="3" t="n">
+      <c r="D261" s="2" t="n">
         <v>46102.5143575572</v>
       </c>
       <c r="E261" t="s">
@@ -8047,8 +8097,8 @@
       <c r="C262" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D262" s="3" t="n">
-        <v>46102.5145357721</v>
+      <c r="D262" s="2" t="n">
+        <v>46102.514535772098</v>
       </c>
       <c r="E262" t="s">
         <v>244</v>
@@ -8073,8 +8123,8 @@
       <c r="C263" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="D263" s="3" t="n">
-        <v>46102.5145796891</v>
+      <c r="D263" s="2" t="n">
+        <v>46102.514579689101</v>
       </c>
       <c r="E263" t="s">
         <v>247</v>
@@ -8099,8 +8149,8 @@
       <c r="C264" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D264" s="3" t="n">
-        <v>46121.414234145</v>
+      <c r="D264" s="2" t="n">
+        <v>46121.414234144999</v>
       </c>
       <c r="E264" t="s">
         <v>264</v>
@@ -8125,8 +8175,8 @@
       <c r="C265" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D265" s="3" t="n">
-        <v>46121.4148473212</v>
+      <c r="D265" s="2" t="n">
+        <v>46121.414847321197</v>
       </c>
       <c r="E265" t="s">
         <v>244</v>
@@ -8151,8 +8201,8 @@
       <c r="C266" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D266" s="3" t="n">
-        <v>46121.414882379</v>
+      <c r="D266" s="2" t="n">
+        <v>46121.414882379002</v>
       </c>
       <c r="E266" t="s">
         <v>244</v>
@@ -8177,8 +8227,8 @@
       <c r="C267" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D267" s="3" t="n">
-        <v>46121.4149635886</v>
+      <c r="D267" s="2" t="n">
+        <v>46121.414963588599</v>
       </c>
       <c r="E267" t="s">
         <v>247</v>
@@ -8203,7 +8253,7 @@
       <c r="C268" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D268" s="3" t="n">
+      <c r="D268" s="2" t="n">
         <v>46121.4150425474</v>
       </c>
       <c r="E268" t="s">
@@ -8229,7 +8279,7 @@
       <c r="C269" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D269" s="3" t="n">
+      <c r="D269" s="2" t="n">
         <v>46121.4153051885</v>
       </c>
       <c r="E269" t="s">
@@ -8255,8 +8305,8 @@
       <c r="C270" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D270" s="3" t="n">
-        <v>46121.4153537579</v>
+      <c r="D270" s="2" t="n">
+        <v>46121.415353757897</v>
       </c>
       <c r="E270" t="s">
         <v>244</v>
@@ -8281,8 +8331,8 @@
       <c r="C271" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D271" s="3" t="n">
-        <v>46121.4154328088</v>
+      <c r="D271" s="2" t="n">
+        <v>46121.415432808797</v>
       </c>
       <c r="E271" t="s">
         <v>247</v>
@@ -8307,8 +8357,8 @@
       <c r="C272" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D272" s="3" t="n">
-        <v>46121.4154681662</v>
+      <c r="D272" s="2" t="n">
+        <v>46121.415468166197</v>
       </c>
       <c r="E272" t="s">
         <v>247</v>
@@ -8333,8 +8383,8 @@
       <c r="C273" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D273" s="3" t="n">
-        <v>46121.4157348934</v>
+      <c r="D273" s="2" t="n">
+        <v>46121.415734893402</v>
       </c>
       <c r="E273" t="s">
         <v>244</v>
@@ -8359,7 +8409,7 @@
       <c r="C274" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D274" s="3" t="n">
+      <c r="D274" s="2" t="n">
         <v>46121.415766168</v>
       </c>
       <c r="E274" t="s">
@@ -8385,8 +8435,8 @@
       <c r="C275" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D275" s="3" t="n">
-        <v>46121.4158275735</v>
+      <c r="D275" s="2" t="n">
+        <v>46121.415827573503</v>
       </c>
       <c r="E275" t="s">
         <v>247</v>
@@ -8411,8 +8461,8 @@
       <c r="C276" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D276" s="3" t="n">
-        <v>46121.4158663843</v>
+      <c r="D276" s="2" t="n">
+        <v>46121.415866384297</v>
       </c>
       <c r="E276" t="s">
         <v>247</v>
@@ -8437,8 +8487,8 @@
       <c r="C277" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D277" s="3" t="n">
-        <v>46121.4162217065</v>
+      <c r="D277" s="2" t="n">
+        <v>46121.416221706502</v>
       </c>
       <c r="E277" t="s">
         <v>244</v>
@@ -8463,8 +8513,8 @@
       <c r="C278" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D278" s="3" t="n">
-        <v>46121.4162680693</v>
+      <c r="D278" s="2" t="n">
+        <v>46121.416268069297</v>
       </c>
       <c r="E278" t="s">
         <v>247</v>
@@ -8489,8 +8539,8 @@
       <c r="C279" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D279" s="3" t="n">
-        <v>46121.4170161986</v>
+      <c r="D279" s="2" t="n">
+        <v>46121.417016198597</v>
       </c>
       <c r="E279" t="s">
         <v>244</v>
@@ -8515,8 +8565,8 @@
       <c r="C280" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D280" s="3" t="n">
-        <v>46121.4170551778</v>
+      <c r="D280" s="2" t="n">
+        <v>46121.417055177801</v>
       </c>
       <c r="E280" t="s">
         <v>244</v>
@@ -8541,8 +8591,8 @@
       <c r="C281" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D281" s="3" t="n">
-        <v>46121.4170887981</v>
+      <c r="D281" s="2" t="n">
+        <v>46121.417088798102</v>
       </c>
       <c r="E281" t="s">
         <v>244</v>
@@ -8567,8 +8617,8 @@
       <c r="C282" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D282" s="3" t="n">
-        <v>46121.4171635599</v>
+      <c r="D282" s="2" t="n">
+        <v>46121.417163559898</v>
       </c>
       <c r="E282" t="s">
         <v>247</v>
@@ -8593,7 +8643,7 @@
       <c r="C283" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D283" s="3" t="n">
+      <c r="D283" s="2" t="n">
         <v>46121.4171970885</v>
       </c>
       <c r="E283" t="s">
@@ -8619,8 +8669,8 @@
       <c r="C284" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D284" s="3" t="n">
-        <v>46121.417227802</v>
+      <c r="D284" s="2" t="n">
+        <v>46121.417227801998</v>
       </c>
       <c r="E284" t="s">
         <v>247</v>
@@ -8645,8 +8695,8 @@
       <c r="C285" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D285" s="3" t="n">
-        <v>46121.4174049122</v>
+      <c r="D285" s="2" t="n">
+        <v>46121.417404912201</v>
       </c>
       <c r="E285" t="s">
         <v>244</v>
@@ -8671,8 +8721,8 @@
       <c r="C286" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D286" s="3" t="n">
-        <v>46121.4174323628</v>
+      <c r="D286" s="2" t="n">
+        <v>46121.417432362803</v>
       </c>
       <c r="E286" t="s">
         <v>244</v>
@@ -8697,8 +8747,8 @@
       <c r="C287" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D287" s="3" t="n">
-        <v>46121.4174661364</v>
+      <c r="D287" s="2" t="n">
+        <v>46121.417466136401</v>
       </c>
       <c r="E287" t="s">
         <v>244</v>
@@ -8723,8 +8773,8 @@
       <c r="C288" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D288" s="3" t="n">
-        <v>46121.4175279553</v>
+      <c r="D288" s="2" t="n">
+        <v>46121.417527955302</v>
       </c>
       <c r="E288" t="s">
         <v>247</v>
@@ -8749,8 +8799,8 @@
       <c r="C289" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D289" s="3" t="n">
-        <v>46121.4175580494</v>
+      <c r="D289" s="2" t="n">
+        <v>46121.417558049397</v>
       </c>
       <c r="E289" t="s">
         <v>247</v>
@@ -8775,8 +8825,8 @@
       <c r="C290" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D290" s="3" t="n">
-        <v>46121.4175887931</v>
+      <c r="D290" s="2" t="n">
+        <v>46121.417588793098</v>
       </c>
       <c r="E290" t="s">
         <v>247</v>
@@ -8801,8 +8851,8 @@
       <c r="C291" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D291" s="3" t="n">
-        <v>46121.4177394025</v>
+      <c r="D291" s="2" t="n">
+        <v>46121.417739402503</v>
       </c>
       <c r="E291" t="s">
         <v>244</v>
@@ -8827,8 +8877,8 @@
       <c r="C292" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D292" s="3" t="n">
-        <v>46121.4177718403</v>
+      <c r="D292" s="2" t="n">
+        <v>46121.417771840301</v>
       </c>
       <c r="E292" t="s">
         <v>244</v>
@@ -8853,8 +8903,8 @@
       <c r="C293" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D293" s="3" t="n">
-        <v>46121.4178017793</v>
+      <c r="D293" s="2" t="n">
+        <v>46121.417801779302</v>
       </c>
       <c r="E293" t="s">
         <v>244</v>
@@ -8879,8 +8929,8 @@
       <c r="C294" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D294" s="3" t="n">
-        <v>46121.4180006801</v>
+      <c r="D294" s="2" t="n">
+        <v>46121.418000680103</v>
       </c>
       <c r="E294" t="s">
         <v>247</v>
@@ -8905,7 +8955,7 @@
       <c r="C295" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D295" s="3" t="n">
+      <c r="D295" s="2" t="n">
         <v>46121.4180265623</v>
       </c>
       <c r="E295" t="s">
@@ -8931,8 +8981,8 @@
       <c r="C296" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D296" s="3" t="n">
-        <v>46121.4180624839</v>
+      <c r="D296" s="2" t="n">
+        <v>46121.418062483899</v>
       </c>
       <c r="E296" t="s">
         <v>247</v>
@@ -8957,8 +9007,8 @@
       <c r="C297" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D297" s="3" t="n">
-        <v>46121.4184952048</v>
+      <c r="D297" s="2" t="n">
+        <v>46121.418495204802</v>
       </c>
       <c r="E297" t="s">
         <v>244</v>
@@ -8983,8 +9033,8 @@
       <c r="C298" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D298" s="3" t="n">
-        <v>46121.418536757</v>
+      <c r="D298" s="2" t="n">
+        <v>46121.418536757003</v>
       </c>
       <c r="E298" t="s">
         <v>247</v>
@@ -9009,7 +9059,7 @@
       <c r="C299" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D299" s="3" t="n">
+      <c r="D299" s="2" t="n">
         <v>46121.4186393317</v>
       </c>
       <c r="E299" t="s">
@@ -9035,8 +9085,8 @@
       <c r="C300" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="D300" s="3" t="n">
-        <v>46121.4186860359</v>
+      <c r="D300" s="2" t="n">
+        <v>46121.418686035897</v>
       </c>
       <c r="E300" t="s">
         <v>247</v>
@@ -9061,8 +9111,8 @@
       <c r="C301" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D301" s="3" t="n">
-        <v>46143.6793276597</v>
+      <c r="D301" s="2" t="n">
+        <v>46143.679327659702</v>
       </c>
       <c r="E301" t="s">
         <v>244</v>
@@ -9087,8 +9137,8 @@
       <c r="C302" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D302" s="3" t="n">
-        <v>46143.6793804742</v>
+      <c r="D302" s="2" t="n">
+        <v>46143.679380474197</v>
       </c>
       <c r="E302" t="s">
         <v>244</v>
@@ -9113,8 +9163,8 @@
       <c r="C303" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D303" s="3" t="n">
-        <v>46143.6794615428</v>
+      <c r="D303" s="2" t="n">
+        <v>46143.679461542801</v>
       </c>
       <c r="E303" t="s">
         <v>247</v>
@@ -9139,7 +9189,7 @@
       <c r="C304" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D304" s="3" t="n">
+      <c r="D304" s="2" t="n">
         <v>46143.679513584</v>
       </c>
       <c r="E304" t="s">
@@ -9165,8 +9215,8 @@
       <c r="C305" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D305" s="3" t="n">
-        <v>46143.6800708549</v>
+      <c r="D305" s="2" t="n">
+        <v>46143.680070854898</v>
       </c>
       <c r="E305" t="s">
         <v>244</v>
@@ -9191,8 +9241,8 @@
       <c r="C306" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D306" s="3" t="n">
-        <v>46143.680112204</v>
+      <c r="D306" s="2" t="n">
+        <v>46143.680112203998</v>
       </c>
       <c r="E306" t="s">
         <v>244</v>
@@ -9217,8 +9267,8 @@
       <c r="C307" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D307" s="3" t="n">
-        <v>46143.6801625616</v>
+      <c r="D307" s="2" t="n">
+        <v>46143.680162561599</v>
       </c>
       <c r="E307" t="s">
         <v>247</v>
@@ -9243,8 +9293,8 @@
       <c r="C308" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D308" s="3" t="n">
-        <v>46143.6802734163</v>
+      <c r="D308" s="2" t="n">
+        <v>46143.680273416299</v>
       </c>
       <c r="E308" t="s">
         <v>247</v>
@@ -9269,8 +9319,8 @@
       <c r="C309" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D309" s="3" t="n">
-        <v>46143.6804487589</v>
+      <c r="D309" s="2" t="n">
+        <v>46143.680448758903</v>
       </c>
       <c r="E309" t="s">
         <v>244</v>
@@ -9295,8 +9345,8 @@
       <c r="C310" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D310" s="3" t="n">
-        <v>46143.6804895137</v>
+      <c r="D310" s="2" t="n">
+        <v>46143.680489513703</v>
       </c>
       <c r="E310" t="s">
         <v>244</v>
@@ -9321,8 +9371,8 @@
       <c r="C311" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D311" s="3" t="n">
-        <v>46143.6805467703</v>
+      <c r="D311" s="2" t="n">
+        <v>46143.680546770302</v>
       </c>
       <c r="E311" t="s">
         <v>247</v>
@@ -9347,8 +9397,8 @@
       <c r="C312" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D312" s="3" t="n">
-        <v>46143.6806160115</v>
+      <c r="D312" s="2" t="n">
+        <v>46143.680616011501</v>
       </c>
       <c r="E312" t="s">
         <v>247</v>
@@ -9373,8 +9423,8 @@
       <c r="C313" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D313" s="3" t="n">
-        <v>46143.6807902012</v>
+      <c r="D313" s="2" t="n">
+        <v>46143.680790201201</v>
       </c>
       <c r="E313" t="s">
         <v>244</v>
@@ -9399,8 +9449,8 @@
       <c r="C314" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D314" s="3" t="n">
-        <v>46143.6808454038</v>
+      <c r="D314" s="2" t="n">
+        <v>46143.680845403796</v>
       </c>
       <c r="E314" t="s">
         <v>247</v>
@@ -9425,8 +9475,8 @@
       <c r="C315" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D315" s="3" t="n">
-        <v>46143.6816202449</v>
+      <c r="D315" s="2" t="n">
+        <v>46143.681620244897</v>
       </c>
       <c r="E315" t="s">
         <v>264</v>
@@ -9451,7 +9501,7 @@
       <c r="C316" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D316" s="3" t="n">
+      <c r="D316" s="2" t="n">
         <v>46143.6818562279</v>
       </c>
       <c r="E316" t="s">
@@ -9477,8 +9527,8 @@
       <c r="C317" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D317" s="3" t="n">
-        <v>46143.6818989909</v>
+      <c r="D317" s="2" t="n">
+        <v>46143.681898990901</v>
       </c>
       <c r="E317" t="s">
         <v>247</v>
@@ -9503,8 +9553,8 @@
       <c r="C318" s="1" t="n">
         <v>46146</v>
       </c>
-      <c r="D318" s="3" t="n">
-        <v>46146.4841866197</v>
+      <c r="D318" s="2" t="n">
+        <v>46146.484186619702</v>
       </c>
       <c r="E318" t="s">
         <v>244</v>
@@ -9529,8 +9579,8 @@
       <c r="C319" s="1" t="n">
         <v>46146</v>
       </c>
-      <c r="D319" s="3" t="n">
-        <v>46146.4842539634</v>
+      <c r="D319" s="2" t="n">
+        <v>46146.484253963397</v>
       </c>
       <c r="E319" t="s">
         <v>247</v>
@@ -9555,8 +9605,8 @@
       <c r="C320" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D320" s="3" t="n">
-        <v>46151.399077282</v>
+      <c r="D320" s="2" t="n">
+        <v>46151.399077282003</v>
       </c>
       <c r="E320" t="s">
         <v>244</v>
@@ -9581,7 +9631,7 @@
       <c r="C321" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D321" s="3" t="n">
+      <c r="D321" s="2" t="n">
         <v>46151.3991169937</v>
       </c>
       <c r="E321" t="s">
@@ -9607,8 +9657,8 @@
       <c r="C322" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D322" s="3" t="n">
-        <v>46151.399211145</v>
+      <c r="D322" s="2" t="n">
+        <v>46151.399211144999</v>
       </c>
       <c r="E322" t="s">
         <v>247</v>
@@ -9633,8 +9683,8 @@
       <c r="C323" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D323" s="3" t="n">
-        <v>46151.3992582157</v>
+      <c r="D323" s="2" t="n">
+        <v>46151.399258215701</v>
       </c>
       <c r="E323" t="s">
         <v>247</v>
@@ -9659,8 +9709,8 @@
       <c r="C324" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D324" s="3" t="n">
-        <v>46151.3994486112</v>
+      <c r="D324" s="2" t="n">
+        <v>46151.399448611199</v>
       </c>
       <c r="E324" t="s">
         <v>244</v>
@@ -9685,8 +9735,8 @@
       <c r="C325" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D325" s="3" t="n">
-        <v>46151.3995213927</v>
+      <c r="D325" s="2" t="n">
+        <v>46151.399521392697</v>
       </c>
       <c r="E325" t="s">
         <v>244</v>
@@ -9711,8 +9761,8 @@
       <c r="C326" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D326" s="3" t="n">
-        <v>46151.3995953551</v>
+      <c r="D326" s="2" t="n">
+        <v>46151.399595355098</v>
       </c>
       <c r="E326" t="s">
         <v>247</v>
@@ -9737,8 +9787,8 @@
       <c r="C327" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D327" s="3" t="n">
-        <v>46151.399632053</v>
+      <c r="D327" s="2" t="n">
+        <v>46151.399632052999</v>
       </c>
       <c r="E327" t="s">
         <v>247</v>
@@ -9763,7 +9813,7 @@
       <c r="C328" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D328" s="3" t="n">
+      <c r="D328" s="2" t="n">
         <v>46151.4001652398</v>
       </c>
       <c r="E328" t="s">
@@ -9789,8 +9839,8 @@
       <c r="C329" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D329" s="3" t="n">
-        <v>46151.400208664</v>
+      <c r="D329" s="2" t="n">
+        <v>46151.400208664003</v>
       </c>
       <c r="E329" t="s">
         <v>247</v>
@@ -9815,8 +9865,8 @@
       <c r="C330" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D330" s="3" t="n">
-        <v>46151.4004444843</v>
+      <c r="D330" s="2" t="n">
+        <v>46151.400444484301</v>
       </c>
       <c r="E330" t="s">
         <v>244</v>
@@ -9841,7 +9891,7 @@
       <c r="C331" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D331" s="3" t="n">
+      <c r="D331" s="2" t="n">
         <v>46151.4004809826</v>
       </c>
       <c r="E331" t="s">
@@ -9867,8 +9917,8 @@
       <c r="C332" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="D332" s="3" t="n">
-        <v>46151.4005990214</v>
+      <c r="D332" s="2" t="n">
+        <v>46151.400599021399</v>
       </c>
       <c r="E332" t="s">
         <v>264</v>
@@ -11691,6 +11741,128 @@
         <v>1</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" t="s">
+        <v>310</v>
+      </c>
+      <c r="C79" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K1" t="s">
+        <v>305</v>
+      </c>
+      <c r="L1" t="s">
+        <v>306</v>
+      </c>
+      <c r="M1" t="s">
+        <v>307</v>
+      </c>
+      <c r="N1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" t="n">
+        <v>40</v>
+      </c>
+      <c r="N2" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
   <si>
     <t>Phase</t>
   </si>
@@ -951,6 +951,30 @@
   </si>
   <si>
     <t>2026-05-11 10:15:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-12 13:05:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-13 16:18:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-14 11:02:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-16 08:53:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-16</t>
   </si>
 </sst>
 </file>
@@ -11764,6 +11788,98 @@
         <v>2</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>312</v>
+      </c>
+      <c r="B80" t="s">
+        <v>313</v>
+      </c>
+      <c r="C80" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" t="s">
+        <v>315</v>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>316</v>
+      </c>
+      <c r="B82" t="s">
+        <v>317</v>
+      </c>
+      <c r="C82" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>318</v>
+      </c>
+      <c r="B83" t="s">
+        <v>319</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
   <si>
     <t>Phase</t>
   </si>
@@ -975,14 +975,36 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistol Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reps</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18 10:55:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -1018,10 +1040,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9957,6 +9980,58 @@
         <v>246</v>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>4</v>
+      </c>
+      <c r="B333" t="s">
+        <v>320</v>
+      </c>
+      <c r="C333" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>46158.5344336176</v>
+      </c>
+      <c r="E333" t="s">
+        <v>321</v>
+      </c>
+      <c r="F333" t="n">
+        <v>3</v>
+      </c>
+      <c r="G333" t="s">
+        <v>322</v>
+      </c>
+      <c r="H333" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>4</v>
+      </c>
+      <c r="B334" t="s">
+        <v>320</v>
+      </c>
+      <c r="C334" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>46158.5344759407</v>
+      </c>
+      <c r="E334" t="s">
+        <v>324</v>
+      </c>
+      <c r="F334" t="n">
+        <v>5</v>
+      </c>
+      <c r="G334" t="s">
+        <v>322</v>
+      </c>
+      <c r="H334" t="s">
+        <v>323</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11880,6 +11955,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>325</v>
+      </c>
+      <c r="B84" t="s">
+        <v>326</v>
+      </c>
+      <c r="C84" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
   <si>
     <t>Phase</t>
   </si>
@@ -996,6 +996,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19 09:22:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
   </si>
 </sst>
 </file>
@@ -11978,6 +11984,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>327</v>
+      </c>
+      <c r="B85" t="s">
+        <v>328</v>
+      </c>
+      <c r="C85" t="n">
+        <v>6</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="331">
   <si>
     <t>Phase</t>
   </si>
@@ -1002,6 +1002,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25 09:19:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
   </si>
 </sst>
 </file>
@@ -12007,6 +12013,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>329</v>
+      </c>
+      <c r="B86" t="s">
+        <v>330</v>
+      </c>
+      <c r="C86" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t>Phase</t>
   </si>
@@ -1008,6 +1008,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26 09:30:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
   </si>
 </sst>
 </file>
@@ -12036,6 +12042,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>331</v>
+      </c>
+      <c r="B87" t="s">
+        <v>332</v>
+      </c>
+      <c r="C87" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="337">
   <si>
     <t>Phase</t>
   </si>
@@ -1014,6 +1014,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28 09:47:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Leg Rise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Hop</t>
   </si>
 </sst>
 </file>
@@ -10050,6 +10062,162 @@
         <v>323</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>3</v>
+      </c>
+      <c r="B335" t="s">
+        <v>335</v>
+      </c>
+      <c r="C335" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>46170.600427899</v>
+      </c>
+      <c r="E335" t="s">
+        <v>321</v>
+      </c>
+      <c r="F335" t="n">
+        <v>18</v>
+      </c>
+      <c r="G335" t="s">
+        <v>322</v>
+      </c>
+      <c r="H335" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>3</v>
+      </c>
+      <c r="B336" t="s">
+        <v>335</v>
+      </c>
+      <c r="C336" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D336" s="3" t="n">
+        <v>46170.6005354636</v>
+      </c>
+      <c r="E336" t="s">
+        <v>324</v>
+      </c>
+      <c r="F336" t="n">
+        <v>22</v>
+      </c>
+      <c r="G336" t="s">
+        <v>322</v>
+      </c>
+      <c r="H336" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>4</v>
+      </c>
+      <c r="B337" t="s">
+        <v>320</v>
+      </c>
+      <c r="C337" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>46170.6008229468</v>
+      </c>
+      <c r="E337" t="s">
+        <v>321</v>
+      </c>
+      <c r="F337" t="n">
+        <v>5</v>
+      </c>
+      <c r="G337" t="s">
+        <v>322</v>
+      </c>
+      <c r="H337" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>4</v>
+      </c>
+      <c r="B338" t="s">
+        <v>320</v>
+      </c>
+      <c r="C338" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>46170.60087171</v>
+      </c>
+      <c r="E338" t="s">
+        <v>324</v>
+      </c>
+      <c r="F338" t="n">
+        <v>5</v>
+      </c>
+      <c r="G338" t="s">
+        <v>322</v>
+      </c>
+      <c r="H338" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>4</v>
+      </c>
+      <c r="B339" t="s">
+        <v>336</v>
+      </c>
+      <c r="C339" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>46170.6011411885</v>
+      </c>
+      <c r="E339" t="s">
+        <v>321</v>
+      </c>
+      <c r="F339" t="n">
+        <v>44</v>
+      </c>
+      <c r="G339" t="s">
+        <v>322</v>
+      </c>
+      <c r="H339" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>4</v>
+      </c>
+      <c r="B340" t="s">
+        <v>336</v>
+      </c>
+      <c r="C340" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D340" s="3" t="n">
+        <v>46170.6011881534</v>
+      </c>
+      <c r="E340" t="s">
+        <v>324</v>
+      </c>
+      <c r="F340" t="n">
+        <v>46</v>
+      </c>
+      <c r="G340" t="s">
+        <v>322</v>
+      </c>
+      <c r="H340" t="s">
+        <v>323</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12065,6 +12233,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>333</v>
+      </c>
+      <c r="B88" t="s">
+        <v>334</v>
+      </c>
+      <c r="C88" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
   <si>
     <t>Phase</t>
   </si>
@@ -1026,6 +1026,18 @@
   </si>
   <si>
     <t xml:space="preserve">Side Hop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01 09:30:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 14:55:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
   </si>
 </sst>
 </file>
@@ -12256,6 +12268,52 @@
         <v>2</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>337</v>
+      </c>
+      <c r="B89" t="s">
+        <v>338</v>
+      </c>
+      <c r="C89" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>339</v>
+      </c>
+      <c r="B90" t="s">
+        <v>340</v>
+      </c>
+      <c r="C90" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -9,13 +9,14 @@
     <sheet name="Phase_data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="daily" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="acl_rsi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="tsk_11" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
   <si>
     <t>Phase</t>
   </si>
@@ -1038,6 +1039,54 @@
   </si>
   <si>
     <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05 11:43:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timestamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05 14:14:28</t>
   </si>
 </sst>
 </file>
@@ -12314,6 +12363,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>341</v>
+      </c>
+      <c r="B91" t="s">
+        <v>342</v>
+      </c>
+      <c r="C91" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12417,4 +12489,97 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K1" t="s">
+        <v>353</v>
+      </c>
+      <c r="L1" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
     <t>Phase</t>
   </si>
@@ -1087,6 +1087,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026-06-05 14:14:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08 09:34:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
   </si>
 </sst>
 </file>
@@ -12386,6 +12392,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>357</v>
+      </c>
+      <c r="B92" t="s">
+        <v>358</v>
+      </c>
+      <c r="C92" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
   <si>
     <t>Phase</t>
   </si>
@@ -1093,6 +1093,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 09:43:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 09:44:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 09:51:43</t>
   </si>
 </sst>
 </file>
@@ -12415,6 +12427,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>359</v>
+      </c>
+      <c r="B93" t="s">
+        <v>360</v>
+      </c>
+      <c r="C93" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12514,6 +12549,50 @@
         <v>60</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" t="n">
+        <v>70</v>
+      </c>
+      <c r="M3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N3" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12607,6 +12686,47 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/sample_data/outcome_data.xlsx
+++ b/sample_data/outcome_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
   <si>
     <t>Phase</t>
   </si>
@@ -1105,6 +1105,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-06-09 09:51:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10 08:21:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17 15:41:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
   </si>
 </sst>
 </file>
@@ -12450,6 +12462,52 @@
         <v>2</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>363</v>
+      </c>
+      <c r="B94" t="s">
+        <v>364</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" t="s">
+        <v>366</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
